--- a/thaco/color/Viet/1_MID_Office_Viet.xlsx
+++ b/thaco/color/Viet/1_MID_Office_Viet.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/Viet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{444F2411-DC71-7343-9A82-A6DD7F6C39FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE6548FC-A438-A142-892D-5147B1D834E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="35720" windowHeight="18900" tabRatio="761" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4545,7 +4545,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="237">
   <si>
     <t>COMPANY …..............</t>
   </si>
@@ -5270,6 +5270,9 @@
   </si>
   <si>
     <t>Các khoản trừ</t>
+  </si>
+  <si>
+    <t>H</t>
   </si>
 </sst>
 </file>
@@ -5283,7 +5286,7 @@
     <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="76">
+  <fonts count="77">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5756,6 +5759,13 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <i/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -6075,7 +6085,7 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="516">
+  <cellXfs count="521">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -6855,15 +6865,6 @@
     <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -6982,30 +6983,80 @@
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="64" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="52" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="52" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="54" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="52" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="54" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="14" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="29" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="23" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="56" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="53" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="48" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -7013,11 +7064,21 @@
     <xf numFmtId="164" fontId="8" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="48" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="45" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7028,14 +7089,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="29" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7059,102 +7112,51 @@
     <xf numFmtId="0" fontId="37" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="37" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="37" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="45" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="54" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="53" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="54" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="23" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="56" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="52" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="4" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="10" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -7163,13 +7165,10 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7177,267 +7176,293 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="71" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="71" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="71" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="53" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="53" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="53" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="70" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="70" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="70" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="75" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="75" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="75" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="56" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="56" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="56" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="72" fillId="0" borderId="22" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="72" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="72" fillId="0" borderId="19" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="72" fillId="0" borderId="16" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="74" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="74" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="74" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="74" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="74" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="64" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="26" fillId="6" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="26" fillId="6" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="26" fillId="6" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="26" fillId="6" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="26" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="26" fillId="6" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="26" fillId="6" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="26" fillId="6" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="26" fillId="6" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="15" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="6" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="64" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="26" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="6" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="64" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="76" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="64" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="64" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="70" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="53" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="71" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="70" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="53" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="71" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="70" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="53" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="71" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="72" fillId="0" borderId="22" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="72" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="72" fillId="0" borderId="19" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="72" fillId="0" borderId="16" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="74" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="75" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="56" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="74" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="75" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="56" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="74" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="75" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="56" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="26" fillId="6" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="26" fillId="6" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="26" fillId="6" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="26" fillId="6" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="26" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="26" fillId="6" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="26" fillId="6" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="26" fillId="6" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="26" fillId="6" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="74" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="74" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="6" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="6" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="6" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="6" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="64" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7452,7 +7477,37 @@
     <cellStyle name="Per cent" xfId="2" builtinId="5"/>
     <cellStyle name="Percent 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="29">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -8226,88 +8281,88 @@
       <c r="CD2" s="203"/>
     </row>
     <row r="3" spans="1:87" s="2" customFormat="1" ht="24" customHeight="1" outlineLevel="1">
-      <c r="A3" s="359"/>
-      <c r="B3" s="354"/>
-      <c r="C3" s="354"/>
-      <c r="D3" s="354"/>
-      <c r="E3" s="354"/>
-      <c r="F3" s="354"/>
-      <c r="G3" s="354"/>
-      <c r="H3" s="354"/>
-      <c r="I3" s="354"/>
-      <c r="J3" s="354"/>
-      <c r="K3" s="354"/>
-      <c r="L3" s="354"/>
-      <c r="M3" s="354"/>
-      <c r="N3" s="354"/>
-      <c r="O3" s="354"/>
-      <c r="P3" s="354"/>
-      <c r="Q3" s="354"/>
-      <c r="R3" s="354"/>
-      <c r="S3" s="354"/>
-      <c r="T3" s="354"/>
-      <c r="U3" s="354"/>
-      <c r="V3" s="354"/>
-      <c r="W3" s="354"/>
-      <c r="X3" s="354"/>
-      <c r="Y3" s="354"/>
-      <c r="Z3" s="354"/>
-      <c r="AA3" s="354"/>
-      <c r="AB3" s="354"/>
-      <c r="AC3" s="354"/>
-      <c r="AD3" s="354"/>
-      <c r="AE3" s="354"/>
-      <c r="AF3" s="354"/>
-      <c r="AG3" s="354"/>
-      <c r="AH3" s="354"/>
-      <c r="AI3" s="354"/>
-      <c r="AJ3" s="354"/>
-      <c r="AK3" s="354"/>
-      <c r="AL3" s="354"/>
-      <c r="AM3" s="354"/>
-      <c r="AN3" s="354"/>
-      <c r="AO3" s="354"/>
-      <c r="AP3" s="354"/>
-      <c r="AQ3" s="354"/>
-      <c r="AR3" s="354"/>
-      <c r="AS3" s="354"/>
-      <c r="AT3" s="354"/>
-      <c r="AU3" s="354"/>
-      <c r="AV3" s="354"/>
-      <c r="AW3" s="354"/>
-      <c r="AX3" s="354"/>
-      <c r="AY3" s="354"/>
-      <c r="AZ3" s="354"/>
-      <c r="BA3" s="354"/>
-      <c r="BB3" s="354"/>
-      <c r="BC3" s="354"/>
-      <c r="BD3" s="354"/>
-      <c r="BE3" s="354"/>
-      <c r="BF3" s="354"/>
-      <c r="BG3" s="354"/>
-      <c r="BH3" s="354"/>
-      <c r="BI3" s="354"/>
-      <c r="BJ3" s="354"/>
-      <c r="BK3" s="354"/>
-      <c r="BL3" s="354"/>
-      <c r="BM3" s="354"/>
-      <c r="BN3" s="354"/>
-      <c r="BO3" s="354"/>
-      <c r="BP3" s="354"/>
-      <c r="BQ3" s="354"/>
-      <c r="BR3" s="354"/>
-      <c r="BS3" s="354"/>
-      <c r="BT3" s="354"/>
-      <c r="BU3" s="354"/>
+      <c r="A3" s="380"/>
+      <c r="B3" s="379"/>
+      <c r="C3" s="379"/>
+      <c r="D3" s="379"/>
+      <c r="E3" s="379"/>
+      <c r="F3" s="379"/>
+      <c r="G3" s="379"/>
+      <c r="H3" s="379"/>
+      <c r="I3" s="379"/>
+      <c r="J3" s="379"/>
+      <c r="K3" s="379"/>
+      <c r="L3" s="379"/>
+      <c r="M3" s="379"/>
+      <c r="N3" s="379"/>
+      <c r="O3" s="379"/>
+      <c r="P3" s="379"/>
+      <c r="Q3" s="379"/>
+      <c r="R3" s="379"/>
+      <c r="S3" s="379"/>
+      <c r="T3" s="379"/>
+      <c r="U3" s="379"/>
+      <c r="V3" s="379"/>
+      <c r="W3" s="379"/>
+      <c r="X3" s="379"/>
+      <c r="Y3" s="379"/>
+      <c r="Z3" s="379"/>
+      <c r="AA3" s="379"/>
+      <c r="AB3" s="379"/>
+      <c r="AC3" s="379"/>
+      <c r="AD3" s="379"/>
+      <c r="AE3" s="379"/>
+      <c r="AF3" s="379"/>
+      <c r="AG3" s="379"/>
+      <c r="AH3" s="379"/>
+      <c r="AI3" s="379"/>
+      <c r="AJ3" s="379"/>
+      <c r="AK3" s="379"/>
+      <c r="AL3" s="379"/>
+      <c r="AM3" s="379"/>
+      <c r="AN3" s="379"/>
+      <c r="AO3" s="379"/>
+      <c r="AP3" s="379"/>
+      <c r="AQ3" s="379"/>
+      <c r="AR3" s="379"/>
+      <c r="AS3" s="379"/>
+      <c r="AT3" s="379"/>
+      <c r="AU3" s="379"/>
+      <c r="AV3" s="379"/>
+      <c r="AW3" s="379"/>
+      <c r="AX3" s="379"/>
+      <c r="AY3" s="379"/>
+      <c r="AZ3" s="379"/>
+      <c r="BA3" s="379"/>
+      <c r="BB3" s="379"/>
+      <c r="BC3" s="379"/>
+      <c r="BD3" s="379"/>
+      <c r="BE3" s="379"/>
+      <c r="BF3" s="379"/>
+      <c r="BG3" s="379"/>
+      <c r="BH3" s="379"/>
+      <c r="BI3" s="379"/>
+      <c r="BJ3" s="379"/>
+      <c r="BK3" s="379"/>
+      <c r="BL3" s="379"/>
+      <c r="BM3" s="379"/>
+      <c r="BN3" s="379"/>
+      <c r="BO3" s="379"/>
+      <c r="BP3" s="379"/>
+      <c r="BQ3" s="379"/>
+      <c r="BR3" s="379"/>
+      <c r="BS3" s="379"/>
+      <c r="BT3" s="379"/>
+      <c r="BU3" s="379"/>
       <c r="BV3" s="205"/>
-      <c r="BW3" s="353" t="s">
+      <c r="BW3" s="378" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="354"/>
-      <c r="BY3" s="354"/>
-      <c r="BZ3" s="354"/>
-      <c r="CA3" s="354"/>
-      <c r="CB3" s="354"/>
+      <c r="BX3" s="379"/>
+      <c r="BY3" s="379"/>
+      <c r="BZ3" s="379"/>
+      <c r="CA3" s="379"/>
+      <c r="CB3" s="379"/>
       <c r="CC3" s="207"/>
       <c r="CD3" s="207"/>
     </row>
@@ -8385,12 +8440,12 @@
       <c r="BT4" s="208"/>
       <c r="BU4" s="208"/>
       <c r="BV4" s="208"/>
-      <c r="BW4" s="354"/>
-      <c r="BX4" s="354"/>
-      <c r="BY4" s="354"/>
-      <c r="BZ4" s="354"/>
-      <c r="CA4" s="354"/>
-      <c r="CB4" s="354"/>
+      <c r="BW4" s="379"/>
+      <c r="BX4" s="379"/>
+      <c r="BY4" s="379"/>
+      <c r="BZ4" s="379"/>
+      <c r="CA4" s="379"/>
+      <c r="CB4" s="379"/>
       <c r="CC4" s="207"/>
       <c r="CD4" s="207"/>
     </row>
@@ -8468,12 +8523,12 @@
       <c r="BT5" s="208"/>
       <c r="BU5" s="208"/>
       <c r="BV5" s="208"/>
-      <c r="BW5" s="354"/>
-      <c r="BX5" s="354"/>
-      <c r="BY5" s="354"/>
-      <c r="BZ5" s="354"/>
-      <c r="CA5" s="354"/>
-      <c r="CB5" s="354"/>
+      <c r="BW5" s="379"/>
+      <c r="BX5" s="379"/>
+      <c r="BY5" s="379"/>
+      <c r="BZ5" s="379"/>
+      <c r="CA5" s="379"/>
+      <c r="CB5" s="379"/>
       <c r="CC5" s="207"/>
       <c r="CD5" s="207"/>
     </row>
@@ -8549,12 +8604,12 @@
       <c r="BT6" s="210"/>
       <c r="BU6" s="210"/>
       <c r="BV6" s="210"/>
-      <c r="BW6" s="354"/>
-      <c r="BX6" s="354"/>
-      <c r="BY6" s="354"/>
-      <c r="BZ6" s="354"/>
-      <c r="CA6" s="354"/>
-      <c r="CB6" s="354"/>
+      <c r="BW6" s="379"/>
+      <c r="BX6" s="379"/>
+      <c r="BY6" s="379"/>
+      <c r="BZ6" s="379"/>
+      <c r="CA6" s="379"/>
+      <c r="CB6" s="379"/>
       <c r="CC6" s="207"/>
       <c r="CD6" s="207"/>
     </row>
@@ -8694,356 +8749,356 @@
       </c>
     </row>
     <row r="8" spans="1:87" s="213" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A8" s="352" t="s">
+      <c r="A8" s="377" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="361" t="s">
+      <c r="B8" s="382" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="334" t="s">
+      <c r="C8" s="352" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="341" t="s">
+      <c r="D8" s="364" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="341" t="s">
+      <c r="E8" s="364" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="334" t="s">
+      <c r="F8" s="352" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="379" t="s">
+      <c r="G8" s="365" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="382" t="s">
+      <c r="H8" s="366" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="382" t="s">
+      <c r="I8" s="366" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="349" t="s">
+      <c r="J8" s="359" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="377" t="s">
+      <c r="K8" s="376" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="378"/>
-      <c r="M8" s="378"/>
-      <c r="N8" s="378"/>
-      <c r="O8" s="378"/>
-      <c r="P8" s="378"/>
-      <c r="Q8" s="378"/>
-      <c r="R8" s="378"/>
-      <c r="S8" s="378"/>
-      <c r="T8" s="378"/>
-      <c r="U8" s="378"/>
-      <c r="V8" s="378"/>
-      <c r="W8" s="378"/>
-      <c r="X8" s="378"/>
-      <c r="Y8" s="383" t="s">
+      <c r="L8" s="356"/>
+      <c r="M8" s="356"/>
+      <c r="N8" s="356"/>
+      <c r="O8" s="356"/>
+      <c r="P8" s="356"/>
+      <c r="Q8" s="356"/>
+      <c r="R8" s="356"/>
+      <c r="S8" s="356"/>
+      <c r="T8" s="356"/>
+      <c r="U8" s="356"/>
+      <c r="V8" s="356"/>
+      <c r="W8" s="356"/>
+      <c r="X8" s="356"/>
+      <c r="Y8" s="355" t="s">
         <v>15</v>
       </c>
-      <c r="Z8" s="378"/>
-      <c r="AA8" s="378"/>
-      <c r="AB8" s="378"/>
-      <c r="AC8" s="378"/>
-      <c r="AD8" s="378"/>
-      <c r="AE8" s="378"/>
-      <c r="AF8" s="378"/>
-      <c r="AG8" s="378"/>
-      <c r="AH8" s="378"/>
-      <c r="AI8" s="378"/>
-      <c r="AJ8" s="378"/>
-      <c r="AK8" s="378"/>
-      <c r="AL8" s="378"/>
-      <c r="AM8" s="378"/>
-      <c r="AN8" s="378"/>
-      <c r="AO8" s="384"/>
-      <c r="AP8" s="349" t="s">
+      <c r="Z8" s="356"/>
+      <c r="AA8" s="356"/>
+      <c r="AB8" s="356"/>
+      <c r="AC8" s="356"/>
+      <c r="AD8" s="356"/>
+      <c r="AE8" s="356"/>
+      <c r="AF8" s="356"/>
+      <c r="AG8" s="356"/>
+      <c r="AH8" s="356"/>
+      <c r="AI8" s="356"/>
+      <c r="AJ8" s="356"/>
+      <c r="AK8" s="356"/>
+      <c r="AL8" s="356"/>
+      <c r="AM8" s="356"/>
+      <c r="AN8" s="356"/>
+      <c r="AO8" s="357"/>
+      <c r="AP8" s="359" t="s">
         <v>16</v>
       </c>
-      <c r="AQ8" s="349" t="s">
+      <c r="AQ8" s="359" t="s">
         <v>17</v>
       </c>
-      <c r="AR8" s="349" t="s">
+      <c r="AR8" s="359" t="s">
         <v>18</v>
       </c>
-      <c r="AS8" s="349" t="s">
+      <c r="AS8" s="359" t="s">
         <v>19</v>
       </c>
-      <c r="AT8" s="349" t="s">
+      <c r="AT8" s="359" t="s">
         <v>20</v>
       </c>
-      <c r="AU8" s="349" t="s">
+      <c r="AU8" s="359" t="s">
         <v>21</v>
       </c>
-      <c r="AV8" s="334" t="s">
+      <c r="AV8" s="352" t="s">
         <v>22</v>
       </c>
-      <c r="AW8" s="358" t="s">
+      <c r="AW8" s="353" t="s">
         <v>23</v>
       </c>
-      <c r="AX8" s="390" t="s">
+      <c r="AX8" s="342" t="s">
         <v>24</v>
       </c>
-      <c r="AY8" s="386" t="s">
+      <c r="AY8" s="362" t="s">
         <v>25</v>
       </c>
-      <c r="AZ8" s="378"/>
-      <c r="BA8" s="378"/>
-      <c r="BB8" s="378"/>
-      <c r="BC8" s="378"/>
-      <c r="BD8" s="378"/>
-      <c r="BE8" s="378"/>
-      <c r="BF8" s="378"/>
-      <c r="BG8" s="378"/>
-      <c r="BH8" s="378"/>
-      <c r="BI8" s="378"/>
-      <c r="BJ8" s="378"/>
-      <c r="BK8" s="378"/>
-      <c r="BL8" s="378"/>
-      <c r="BM8" s="378"/>
-      <c r="BN8" s="378"/>
-      <c r="BO8" s="378"/>
-      <c r="BP8" s="378"/>
-      <c r="BQ8" s="384"/>
-      <c r="BR8" s="391" t="s">
+      <c r="AZ8" s="356"/>
+      <c r="BA8" s="356"/>
+      <c r="BB8" s="356"/>
+      <c r="BC8" s="356"/>
+      <c r="BD8" s="356"/>
+      <c r="BE8" s="356"/>
+      <c r="BF8" s="356"/>
+      <c r="BG8" s="356"/>
+      <c r="BH8" s="356"/>
+      <c r="BI8" s="356"/>
+      <c r="BJ8" s="356"/>
+      <c r="BK8" s="356"/>
+      <c r="BL8" s="356"/>
+      <c r="BM8" s="356"/>
+      <c r="BN8" s="356"/>
+      <c r="BO8" s="356"/>
+      <c r="BP8" s="356"/>
+      <c r="BQ8" s="357"/>
+      <c r="BR8" s="345" t="s">
         <v>26</v>
       </c>
-      <c r="BS8" s="372"/>
-      <c r="BT8" s="334" t="s">
+      <c r="BS8" s="346"/>
+      <c r="BT8" s="352" t="s">
         <v>27</v>
       </c>
-      <c r="BU8" s="387" t="s">
+      <c r="BU8" s="339" t="s">
         <v>28</v>
       </c>
       <c r="BV8" s="3"/>
-      <c r="BW8" s="337" t="s">
+      <c r="BW8" s="392" t="s">
         <v>29</v>
       </c>
-      <c r="BX8" s="362" t="s">
+      <c r="BX8" s="383" t="s">
         <v>30</v>
       </c>
-      <c r="BY8" s="363"/>
-      <c r="BZ8" s="363"/>
-      <c r="CA8" s="364"/>
-      <c r="CB8" s="392" t="s">
+      <c r="BY8" s="384"/>
+      <c r="BZ8" s="384"/>
+      <c r="CA8" s="385"/>
+      <c r="CB8" s="347" t="s">
         <v>31</v>
       </c>
-      <c r="CC8" s="355" t="s">
+      <c r="CC8" s="333" t="s">
         <v>32</v>
       </c>
-      <c r="CD8" s="355" t="s">
+      <c r="CD8" s="333" t="s">
         <v>33</v>
       </c>
       <c r="CH8" s="150"/>
       <c r="CI8" s="150"/>
     </row>
     <row r="9" spans="1:87" s="213" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A9" s="346"/>
-      <c r="B9" s="335"/>
-      <c r="C9" s="335"/>
-      <c r="D9" s="335"/>
-      <c r="E9" s="335"/>
-      <c r="F9" s="335"/>
-      <c r="G9" s="380"/>
-      <c r="H9" s="346"/>
-      <c r="I9" s="346"/>
-      <c r="J9" s="350"/>
-      <c r="K9" s="345" t="s">
+      <c r="A9" s="367"/>
+      <c r="B9" s="337"/>
+      <c r="C9" s="337"/>
+      <c r="D9" s="337"/>
+      <c r="E9" s="337"/>
+      <c r="F9" s="337"/>
+      <c r="G9" s="343"/>
+      <c r="H9" s="367"/>
+      <c r="I9" s="367"/>
+      <c r="J9" s="360"/>
+      <c r="K9" s="370" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="345" t="s">
+      <c r="L9" s="370" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="345" t="s">
+      <c r="M9" s="370" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="345" t="s">
+      <c r="N9" s="370" t="s">
         <v>37</v>
       </c>
-      <c r="O9" s="345" t="s">
+      <c r="O9" s="370" t="s">
         <v>38</v>
       </c>
-      <c r="P9" s="345" t="s">
+      <c r="P9" s="370" t="s">
         <v>39</v>
       </c>
-      <c r="Q9" s="345" t="s">
+      <c r="Q9" s="370" t="s">
         <v>40</v>
       </c>
-      <c r="R9" s="345" t="s">
+      <c r="R9" s="370" t="s">
         <v>41</v>
       </c>
-      <c r="S9" s="345" t="s">
+      <c r="S9" s="370" t="s">
         <v>42</v>
       </c>
-      <c r="T9" s="345" t="s">
+      <c r="T9" s="370" t="s">
         <v>43</v>
       </c>
-      <c r="U9" s="345" t="s">
+      <c r="U9" s="370" t="s">
         <v>44</v>
       </c>
       <c r="V9" s="371" t="s">
         <v>45</v>
       </c>
-      <c r="W9" s="372"/>
-      <c r="X9" s="345" t="s">
+      <c r="W9" s="346"/>
+      <c r="X9" s="370" t="s">
         <v>46</v>
       </c>
-      <c r="Y9" s="340" t="s">
+      <c r="Y9" s="336" t="s">
         <v>154</v>
       </c>
-      <c r="Z9" s="340" t="s">
+      <c r="Z9" s="336" t="s">
         <v>48</v>
       </c>
-      <c r="AA9" s="340" t="s">
+      <c r="AA9" s="336" t="s">
         <v>49</v>
       </c>
-      <c r="AB9" s="340" t="s">
+      <c r="AB9" s="336" t="s">
         <v>50</v>
       </c>
-      <c r="AC9" s="340" t="s">
+      <c r="AC9" s="336" t="s">
         <v>51</v>
       </c>
-      <c r="AD9" s="340" t="s">
+      <c r="AD9" s="336" t="s">
         <v>52</v>
       </c>
-      <c r="AE9" s="340" t="s">
+      <c r="AE9" s="336" t="s">
         <v>53</v>
       </c>
-      <c r="AF9" s="340" t="s">
+      <c r="AF9" s="336" t="s">
         <v>54</v>
       </c>
-      <c r="AG9" s="340" t="s">
+      <c r="AG9" s="336" t="s">
         <v>55</v>
       </c>
-      <c r="AH9" s="340" t="s">
+      <c r="AH9" s="336" t="s">
         <v>56</v>
       </c>
-      <c r="AI9" s="340" t="s">
+      <c r="AI9" s="336" t="s">
         <v>57</v>
       </c>
-      <c r="AJ9" s="385" t="s">
+      <c r="AJ9" s="361" t="s">
         <v>58</v>
       </c>
-      <c r="AK9" s="387" t="s">
+      <c r="AK9" s="339" t="s">
         <v>59</v>
       </c>
-      <c r="AL9" s="390" t="s">
+      <c r="AL9" s="342" t="s">
         <v>60</v>
       </c>
-      <c r="AM9" s="340" t="s">
+      <c r="AM9" s="336" t="s">
         <v>61</v>
       </c>
-      <c r="AN9" s="334" t="s">
+      <c r="AN9" s="352" t="s">
         <v>62</v>
       </c>
-      <c r="AO9" s="334" t="s">
+      <c r="AO9" s="352" t="s">
         <v>63</v>
       </c>
-      <c r="AP9" s="350"/>
-      <c r="AQ9" s="350"/>
-      <c r="AR9" s="350"/>
-      <c r="AS9" s="350"/>
-      <c r="AT9" s="350"/>
-      <c r="AU9" s="350"/>
-      <c r="AV9" s="335"/>
-      <c r="AW9" s="350"/>
-      <c r="AX9" s="380"/>
-      <c r="AY9" s="394" t="s">
+      <c r="AP9" s="360"/>
+      <c r="AQ9" s="360"/>
+      <c r="AR9" s="360"/>
+      <c r="AS9" s="360"/>
+      <c r="AT9" s="360"/>
+      <c r="AU9" s="360"/>
+      <c r="AV9" s="337"/>
+      <c r="AW9" s="360"/>
+      <c r="AX9" s="343"/>
+      <c r="AY9" s="349" t="s">
         <v>25</v>
       </c>
-      <c r="AZ9" s="395"/>
-      <c r="BA9" s="395"/>
-      <c r="BB9" s="395"/>
-      <c r="BC9" s="395"/>
-      <c r="BD9" s="395"/>
-      <c r="BE9" s="395"/>
-      <c r="BF9" s="395"/>
-      <c r="BG9" s="395"/>
-      <c r="BH9" s="395"/>
-      <c r="BI9" s="395"/>
-      <c r="BJ9" s="395"/>
-      <c r="BK9" s="395"/>
-      <c r="BL9" s="396"/>
-      <c r="BM9" s="394" t="s">
+      <c r="AZ9" s="350"/>
+      <c r="BA9" s="350"/>
+      <c r="BB9" s="350"/>
+      <c r="BC9" s="350"/>
+      <c r="BD9" s="350"/>
+      <c r="BE9" s="350"/>
+      <c r="BF9" s="350"/>
+      <c r="BG9" s="350"/>
+      <c r="BH9" s="350"/>
+      <c r="BI9" s="350"/>
+      <c r="BJ9" s="350"/>
+      <c r="BK9" s="350"/>
+      <c r="BL9" s="351"/>
+      <c r="BM9" s="349" t="s">
         <v>64</v>
       </c>
-      <c r="BN9" s="395"/>
-      <c r="BO9" s="395"/>
-      <c r="BP9" s="395"/>
-      <c r="BQ9" s="396"/>
-      <c r="BR9" s="348" t="s">
+      <c r="BN9" s="350"/>
+      <c r="BO9" s="350"/>
+      <c r="BP9" s="350"/>
+      <c r="BQ9" s="351"/>
+      <c r="BR9" s="369" t="s">
         <v>65</v>
       </c>
-      <c r="BS9" s="348" t="s">
+      <c r="BS9" s="369" t="s">
         <v>66</v>
       </c>
-      <c r="BT9" s="335"/>
-      <c r="BU9" s="388"/>
+      <c r="BT9" s="337"/>
+      <c r="BU9" s="340"/>
       <c r="BV9" s="3"/>
-      <c r="BW9" s="338"/>
-      <c r="BX9" s="365"/>
-      <c r="BY9" s="366"/>
-      <c r="BZ9" s="366"/>
-      <c r="CA9" s="367"/>
-      <c r="CB9" s="335"/>
-      <c r="CC9" s="356"/>
-      <c r="CD9" s="356"/>
+      <c r="BW9" s="393"/>
+      <c r="BX9" s="386"/>
+      <c r="BY9" s="387"/>
+      <c r="BZ9" s="387"/>
+      <c r="CA9" s="388"/>
+      <c r="CB9" s="337"/>
+      <c r="CC9" s="334"/>
+      <c r="CD9" s="334"/>
       <c r="CH9" s="150"/>
       <c r="CI9" s="150"/>
     </row>
     <row r="10" spans="1:87" s="214" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A10" s="346"/>
-      <c r="B10" s="335"/>
-      <c r="C10" s="335"/>
-      <c r="D10" s="335"/>
-      <c r="E10" s="335"/>
-      <c r="F10" s="335"/>
-      <c r="G10" s="380"/>
-      <c r="H10" s="346"/>
-      <c r="I10" s="346"/>
-      <c r="J10" s="350"/>
-      <c r="K10" s="346"/>
-      <c r="L10" s="346"/>
-      <c r="M10" s="346"/>
-      <c r="N10" s="346"/>
-      <c r="O10" s="346"/>
-      <c r="P10" s="346"/>
-      <c r="Q10" s="346"/>
-      <c r="R10" s="346"/>
-      <c r="S10" s="346"/>
-      <c r="T10" s="346"/>
-      <c r="U10" s="346"/>
-      <c r="V10" s="373"/>
-      <c r="W10" s="374"/>
-      <c r="X10" s="346"/>
-      <c r="Y10" s="335"/>
-      <c r="Z10" s="335"/>
-      <c r="AA10" s="335"/>
-      <c r="AB10" s="335"/>
-      <c r="AC10" s="335"/>
-      <c r="AD10" s="335"/>
-      <c r="AE10" s="335"/>
-      <c r="AF10" s="335"/>
-      <c r="AG10" s="335"/>
-      <c r="AH10" s="335"/>
-      <c r="AI10" s="335"/>
-      <c r="AJ10" s="380"/>
-      <c r="AK10" s="388"/>
-      <c r="AL10" s="380"/>
-      <c r="AM10" s="335"/>
-      <c r="AN10" s="335"/>
-      <c r="AO10" s="335"/>
-      <c r="AP10" s="350"/>
-      <c r="AQ10" s="350"/>
-      <c r="AR10" s="350"/>
-      <c r="AS10" s="350"/>
-      <c r="AT10" s="350"/>
-      <c r="AU10" s="350"/>
-      <c r="AV10" s="335"/>
-      <c r="AW10" s="350"/>
-      <c r="AX10" s="380"/>
+      <c r="A10" s="367"/>
+      <c r="B10" s="337"/>
+      <c r="C10" s="337"/>
+      <c r="D10" s="337"/>
+      <c r="E10" s="337"/>
+      <c r="F10" s="337"/>
+      <c r="G10" s="343"/>
+      <c r="H10" s="367"/>
+      <c r="I10" s="367"/>
+      <c r="J10" s="360"/>
+      <c r="K10" s="367"/>
+      <c r="L10" s="367"/>
+      <c r="M10" s="367"/>
+      <c r="N10" s="367"/>
+      <c r="O10" s="367"/>
+      <c r="P10" s="367"/>
+      <c r="Q10" s="367"/>
+      <c r="R10" s="367"/>
+      <c r="S10" s="367"/>
+      <c r="T10" s="367"/>
+      <c r="U10" s="367"/>
+      <c r="V10" s="372"/>
+      <c r="W10" s="373"/>
+      <c r="X10" s="367"/>
+      <c r="Y10" s="337"/>
+      <c r="Z10" s="337"/>
+      <c r="AA10" s="337"/>
+      <c r="AB10" s="337"/>
+      <c r="AC10" s="337"/>
+      <c r="AD10" s="337"/>
+      <c r="AE10" s="337"/>
+      <c r="AF10" s="337"/>
+      <c r="AG10" s="337"/>
+      <c r="AH10" s="337"/>
+      <c r="AI10" s="337"/>
+      <c r="AJ10" s="343"/>
+      <c r="AK10" s="340"/>
+      <c r="AL10" s="343"/>
+      <c r="AM10" s="337"/>
+      <c r="AN10" s="337"/>
+      <c r="AO10" s="337"/>
+      <c r="AP10" s="360"/>
+      <c r="AQ10" s="360"/>
+      <c r="AR10" s="360"/>
+      <c r="AS10" s="360"/>
+      <c r="AT10" s="360"/>
+      <c r="AU10" s="360"/>
+      <c r="AV10" s="337"/>
+      <c r="AW10" s="360"/>
+      <c r="AX10" s="343"/>
       <c r="AY10" s="29" t="s">
         <v>67</v>
       </c>
@@ -9053,67 +9108,67 @@
       <c r="BA10" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="BB10" s="360" t="s">
+      <c r="BB10" s="381" t="s">
         <v>70</v>
       </c>
-      <c r="BC10" s="343" t="s">
+      <c r="BC10" s="363" t="s">
         <v>71</v>
       </c>
-      <c r="BD10" s="343" t="s">
+      <c r="BD10" s="363" t="s">
         <v>72</v>
       </c>
-      <c r="BE10" s="342" t="s">
+      <c r="BE10" s="358" t="s">
         <v>73</v>
       </c>
-      <c r="BF10" s="342" t="s">
+      <c r="BF10" s="358" t="s">
         <v>74</v>
       </c>
-      <c r="BG10" s="351" t="s">
+      <c r="BG10" s="395" t="s">
         <v>75</v>
       </c>
-      <c r="BH10" s="343" t="s">
+      <c r="BH10" s="363" t="s">
         <v>76</v>
       </c>
-      <c r="BI10" s="375" t="s">
+      <c r="BI10" s="374" t="s">
         <v>77</v>
       </c>
-      <c r="BJ10" s="342" t="s">
+      <c r="BJ10" s="358" t="s">
         <v>78</v>
       </c>
-      <c r="BK10" s="342" t="s">
+      <c r="BK10" s="358" t="s">
         <v>79</v>
       </c>
-      <c r="BL10" s="334" t="s">
+      <c r="BL10" s="352" t="s">
         <v>80</v>
       </c>
-      <c r="BM10" s="343" t="s">
+      <c r="BM10" s="363" t="s">
         <v>81</v>
       </c>
-      <c r="BN10" s="358" t="s">
+      <c r="BN10" s="353" t="s">
         <v>82</v>
       </c>
-      <c r="BO10" s="343" t="s">
+      <c r="BO10" s="363" t="s">
         <v>83</v>
       </c>
-      <c r="BP10" s="358" t="s">
+      <c r="BP10" s="353" t="s">
         <v>84</v>
       </c>
-      <c r="BQ10" s="358" t="s">
+      <c r="BQ10" s="353" t="s">
         <v>85</v>
       </c>
-      <c r="BR10" s="346"/>
-      <c r="BS10" s="346"/>
-      <c r="BT10" s="335"/>
-      <c r="BU10" s="388"/>
+      <c r="BR10" s="367"/>
+      <c r="BS10" s="367"/>
+      <c r="BT10" s="337"/>
+      <c r="BU10" s="340"/>
       <c r="BV10" s="3"/>
-      <c r="BW10" s="338"/>
-      <c r="BX10" s="368"/>
-      <c r="BY10" s="369"/>
-      <c r="BZ10" s="369"/>
-      <c r="CA10" s="370"/>
-      <c r="CB10" s="335"/>
-      <c r="CC10" s="356"/>
-      <c r="CD10" s="356"/>
+      <c r="BW10" s="393"/>
+      <c r="BX10" s="389"/>
+      <c r="BY10" s="390"/>
+      <c r="BZ10" s="390"/>
+      <c r="CA10" s="391"/>
+      <c r="CB10" s="337"/>
+      <c r="CC10" s="334"/>
+      <c r="CD10" s="334"/>
       <c r="CE10" s="228" t="s">
         <v>3</v>
       </c>
@@ -9121,60 +9176,60 @@
       <c r="CI10" s="150"/>
     </row>
     <row r="11" spans="1:87" s="214" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A11" s="347"/>
-      <c r="B11" s="336"/>
-      <c r="C11" s="336"/>
-      <c r="D11" s="336"/>
-      <c r="E11" s="336"/>
-      <c r="F11" s="336"/>
-      <c r="G11" s="381"/>
-      <c r="H11" s="347"/>
-      <c r="I11" s="347"/>
-      <c r="J11" s="344"/>
-      <c r="K11" s="347"/>
-      <c r="L11" s="347"/>
-      <c r="M11" s="347"/>
-      <c r="N11" s="347"/>
-      <c r="O11" s="347"/>
-      <c r="P11" s="347"/>
-      <c r="Q11" s="347"/>
-      <c r="R11" s="347"/>
-      <c r="S11" s="347"/>
-      <c r="T11" s="347"/>
-      <c r="U11" s="347"/>
+      <c r="A11" s="368"/>
+      <c r="B11" s="338"/>
+      <c r="C11" s="338"/>
+      <c r="D11" s="338"/>
+      <c r="E11" s="338"/>
+      <c r="F11" s="338"/>
+      <c r="G11" s="344"/>
+      <c r="H11" s="368"/>
+      <c r="I11" s="368"/>
+      <c r="J11" s="354"/>
+      <c r="K11" s="368"/>
+      <c r="L11" s="368"/>
+      <c r="M11" s="368"/>
+      <c r="N11" s="368"/>
+      <c r="O11" s="368"/>
+      <c r="P11" s="368"/>
+      <c r="Q11" s="368"/>
+      <c r="R11" s="368"/>
+      <c r="S11" s="368"/>
+      <c r="T11" s="368"/>
+      <c r="U11" s="368"/>
       <c r="V11" s="178" t="s">
         <v>86</v>
       </c>
       <c r="W11" s="178" t="s">
         <v>87</v>
       </c>
-      <c r="X11" s="347"/>
-      <c r="Y11" s="336"/>
-      <c r="Z11" s="336"/>
-      <c r="AA11" s="336"/>
-      <c r="AB11" s="336"/>
-      <c r="AC11" s="336"/>
-      <c r="AD11" s="336"/>
-      <c r="AE11" s="336"/>
-      <c r="AF11" s="336"/>
-      <c r="AG11" s="336"/>
-      <c r="AH11" s="336"/>
-      <c r="AI11" s="336"/>
-      <c r="AJ11" s="381"/>
-      <c r="AK11" s="389"/>
-      <c r="AL11" s="381"/>
-      <c r="AM11" s="336"/>
-      <c r="AN11" s="336"/>
-      <c r="AO11" s="336"/>
-      <c r="AP11" s="344"/>
-      <c r="AQ11" s="344"/>
-      <c r="AR11" s="344"/>
-      <c r="AS11" s="344"/>
-      <c r="AT11" s="344"/>
-      <c r="AU11" s="344"/>
-      <c r="AV11" s="336"/>
-      <c r="AW11" s="344"/>
-      <c r="AX11" s="381"/>
+      <c r="X11" s="368"/>
+      <c r="Y11" s="338"/>
+      <c r="Z11" s="338"/>
+      <c r="AA11" s="338"/>
+      <c r="AB11" s="338"/>
+      <c r="AC11" s="338"/>
+      <c r="AD11" s="338"/>
+      <c r="AE11" s="338"/>
+      <c r="AF11" s="338"/>
+      <c r="AG11" s="338"/>
+      <c r="AH11" s="338"/>
+      <c r="AI11" s="338"/>
+      <c r="AJ11" s="344"/>
+      <c r="AK11" s="341"/>
+      <c r="AL11" s="344"/>
+      <c r="AM11" s="338"/>
+      <c r="AN11" s="338"/>
+      <c r="AO11" s="338"/>
+      <c r="AP11" s="354"/>
+      <c r="AQ11" s="354"/>
+      <c r="AR11" s="354"/>
+      <c r="AS11" s="354"/>
+      <c r="AT11" s="354"/>
+      <c r="AU11" s="354"/>
+      <c r="AV11" s="338"/>
+      <c r="AW11" s="354"/>
+      <c r="AX11" s="344"/>
       <c r="AY11" s="229" t="s">
         <v>88</v>
       </c>
@@ -9184,28 +9239,28 @@
       <c r="BA11" s="229" t="s">
         <v>90</v>
       </c>
-      <c r="BB11" s="336"/>
-      <c r="BC11" s="344"/>
-      <c r="BD11" s="344"/>
-      <c r="BE11" s="336"/>
-      <c r="BF11" s="336"/>
-      <c r="BG11" s="347"/>
-      <c r="BH11" s="344"/>
-      <c r="BI11" s="376"/>
-      <c r="BJ11" s="336"/>
-      <c r="BK11" s="336"/>
-      <c r="BL11" s="336"/>
-      <c r="BM11" s="344"/>
-      <c r="BN11" s="344"/>
-      <c r="BO11" s="344"/>
-      <c r="BP11" s="344"/>
-      <c r="BQ11" s="344"/>
-      <c r="BR11" s="347"/>
-      <c r="BS11" s="347"/>
-      <c r="BT11" s="336"/>
-      <c r="BU11" s="389"/>
+      <c r="BB11" s="338"/>
+      <c r="BC11" s="354"/>
+      <c r="BD11" s="354"/>
+      <c r="BE11" s="338"/>
+      <c r="BF11" s="338"/>
+      <c r="BG11" s="368"/>
+      <c r="BH11" s="354"/>
+      <c r="BI11" s="375"/>
+      <c r="BJ11" s="338"/>
+      <c r="BK11" s="338"/>
+      <c r="BL11" s="338"/>
+      <c r="BM11" s="354"/>
+      <c r="BN11" s="354"/>
+      <c r="BO11" s="354"/>
+      <c r="BP11" s="354"/>
+      <c r="BQ11" s="354"/>
+      <c r="BR11" s="368"/>
+      <c r="BS11" s="368"/>
+      <c r="BT11" s="338"/>
+      <c r="BU11" s="341"/>
       <c r="BV11" s="3"/>
-      <c r="BW11" s="339"/>
+      <c r="BW11" s="394"/>
       <c r="BX11" s="237" t="s">
         <v>91</v>
       </c>
@@ -9218,9 +9273,9 @@
       <c r="CA11" s="238" t="s">
         <v>94</v>
       </c>
-      <c r="CB11" s="393"/>
-      <c r="CC11" s="357"/>
-      <c r="CD11" s="357"/>
+      <c r="CB11" s="348"/>
+      <c r="CC11" s="335"/>
+      <c r="CD11" s="335"/>
       <c r="CE11" s="227">
         <v>26</v>
       </c>
@@ -11694,6 +11749,72 @@
   </sheetData>
   <autoFilter ref="A12:CI21" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="82">
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="BW8:BW11"/>
+    <mergeCell ref="AI9:AI11"/>
+    <mergeCell ref="D8:D11"/>
+    <mergeCell ref="BF10:BF11"/>
+    <mergeCell ref="BO10:BO11"/>
+    <mergeCell ref="Q9:Q11"/>
+    <mergeCell ref="S9:S11"/>
+    <mergeCell ref="BL10:BL11"/>
+    <mergeCell ref="BS9:BS11"/>
+    <mergeCell ref="AC9:AC11"/>
+    <mergeCell ref="AP8:AP11"/>
+    <mergeCell ref="N9:N11"/>
+    <mergeCell ref="BG10:BG11"/>
+    <mergeCell ref="AF9:AF11"/>
+    <mergeCell ref="R9:R11"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="BW3:CB6"/>
+    <mergeCell ref="CC8:CC11"/>
+    <mergeCell ref="AU8:AU11"/>
+    <mergeCell ref="AW8:AW11"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="AE9:AE11"/>
+    <mergeCell ref="AO9:AO11"/>
+    <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="BD10:BD11"/>
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="M9:M11"/>
+    <mergeCell ref="O9:O11"/>
+    <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BX8:CA10"/>
+    <mergeCell ref="BR9:BR11"/>
+    <mergeCell ref="BM10:BM11"/>
+    <mergeCell ref="AQ8:AQ11"/>
+    <mergeCell ref="U9:U11"/>
+    <mergeCell ref="BN10:BN11"/>
+    <mergeCell ref="BP10:BP11"/>
+    <mergeCell ref="AG9:AG11"/>
+    <mergeCell ref="V9:W10"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="X9:X11"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="K8:X8"/>
+    <mergeCell ref="AH9:AH11"/>
+    <mergeCell ref="P9:P11"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="T9:T11"/>
+    <mergeCell ref="E8:E11"/>
+    <mergeCell ref="G8:G11"/>
+    <mergeCell ref="H8:H11"/>
+    <mergeCell ref="J8:J11"/>
+    <mergeCell ref="I8:I11"/>
+    <mergeCell ref="F8:F11"/>
+    <mergeCell ref="Y8:AO8"/>
+    <mergeCell ref="BJ10:BJ11"/>
+    <mergeCell ref="AS8:AS11"/>
+    <mergeCell ref="AV8:AV11"/>
+    <mergeCell ref="AJ9:AJ11"/>
+    <mergeCell ref="AY8:BQ8"/>
+    <mergeCell ref="BC10:BC11"/>
+    <mergeCell ref="Z9:Z11"/>
+    <mergeCell ref="AD9:AD11"/>
+    <mergeCell ref="BE10:BE11"/>
+    <mergeCell ref="AR8:AR11"/>
+    <mergeCell ref="AT8:AT11"/>
     <mergeCell ref="CD8:CD11"/>
     <mergeCell ref="Y9:Y11"/>
     <mergeCell ref="AA9:AA11"/>
@@ -11710,82 +11831,16 @@
     <mergeCell ref="BU8:BU11"/>
     <mergeCell ref="BQ10:BQ11"/>
     <mergeCell ref="AB9:AB11"/>
-    <mergeCell ref="Y8:AO8"/>
-    <mergeCell ref="BJ10:BJ11"/>
-    <mergeCell ref="AS8:AS11"/>
-    <mergeCell ref="AV8:AV11"/>
-    <mergeCell ref="AJ9:AJ11"/>
-    <mergeCell ref="AY8:BQ8"/>
-    <mergeCell ref="BC10:BC11"/>
-    <mergeCell ref="Z9:Z11"/>
-    <mergeCell ref="AD9:AD11"/>
-    <mergeCell ref="BE10:BE11"/>
-    <mergeCell ref="AR8:AR11"/>
-    <mergeCell ref="AT8:AT11"/>
-    <mergeCell ref="E8:E11"/>
-    <mergeCell ref="G8:G11"/>
-    <mergeCell ref="H8:H11"/>
-    <mergeCell ref="J8:J11"/>
-    <mergeCell ref="I8:I11"/>
-    <mergeCell ref="F8:F11"/>
-    <mergeCell ref="BR9:BR11"/>
-    <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="AQ8:AQ11"/>
-    <mergeCell ref="U9:U11"/>
-    <mergeCell ref="BN10:BN11"/>
-    <mergeCell ref="BP10:BP11"/>
-    <mergeCell ref="AG9:AG11"/>
-    <mergeCell ref="V9:W10"/>
-    <mergeCell ref="BI10:BI11"/>
-    <mergeCell ref="X9:X11"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="K8:X8"/>
-    <mergeCell ref="AH9:AH11"/>
-    <mergeCell ref="P9:P11"/>
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="T9:T11"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="BW3:CB6"/>
-    <mergeCell ref="CC8:CC11"/>
-    <mergeCell ref="AU8:AU11"/>
-    <mergeCell ref="AW8:AW11"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="AE9:AE11"/>
-    <mergeCell ref="AO9:AO11"/>
-    <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="M9:M11"/>
-    <mergeCell ref="O9:O11"/>
-    <mergeCell ref="BH10:BH11"/>
-    <mergeCell ref="BX8:CA10"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="BW8:BW11"/>
-    <mergeCell ref="AI9:AI11"/>
-    <mergeCell ref="D8:D11"/>
-    <mergeCell ref="BF10:BF11"/>
-    <mergeCell ref="BO10:BO11"/>
-    <mergeCell ref="Q9:Q11"/>
-    <mergeCell ref="S9:S11"/>
-    <mergeCell ref="BL10:BL11"/>
-    <mergeCell ref="BS9:BS11"/>
-    <mergeCell ref="AC9:AC11"/>
-    <mergeCell ref="AP8:AP11"/>
-    <mergeCell ref="N9:N11"/>
-    <mergeCell ref="BG10:BG11"/>
-    <mergeCell ref="AF9:AF11"/>
-    <mergeCell ref="R9:R11"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B5 B7:B12 B15:B25 C12:BU12 B37:B1048576 B27:B35">
-    <cfRule type="duplicateValues" dxfId="25" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B5 B7:B12 B15:B25 C12:CD12 D13:F13 J13:BK13 BM13:CD13 B37:B1048576 B27:B35">
-    <cfRule type="duplicateValues" dxfId="23" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="94"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="BL13">
-    <cfRule type="duplicateValues" dxfId="22" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="2"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.21" bottom="0.17" header="0.196850393700787" footer="0.196850393700787"/>
@@ -11984,87 +12039,87 @@
       <c r="CD2" s="41"/>
     </row>
     <row r="3" spans="1:87" s="43" customFormat="1" ht="11" outlineLevel="1">
-      <c r="A3" s="430"/>
-      <c r="B3" s="418"/>
-      <c r="C3" s="418"/>
-      <c r="D3" s="418"/>
-      <c r="E3" s="418"/>
-      <c r="F3" s="418"/>
-      <c r="G3" s="418"/>
-      <c r="H3" s="418"/>
-      <c r="I3" s="418"/>
-      <c r="J3" s="418"/>
-      <c r="K3" s="418"/>
-      <c r="L3" s="418"/>
-      <c r="M3" s="418"/>
-      <c r="N3" s="418"/>
-      <c r="O3" s="418"/>
-      <c r="P3" s="418"/>
-      <c r="Q3" s="418"/>
-      <c r="R3" s="418"/>
-      <c r="S3" s="418"/>
-      <c r="T3" s="418"/>
-      <c r="U3" s="418"/>
-      <c r="V3" s="418"/>
-      <c r="W3" s="418"/>
-      <c r="X3" s="418"/>
-      <c r="Y3" s="418"/>
-      <c r="Z3" s="418"/>
-      <c r="AA3" s="418"/>
-      <c r="AB3" s="418"/>
-      <c r="AC3" s="418"/>
-      <c r="AD3" s="418"/>
-      <c r="AE3" s="418"/>
-      <c r="AF3" s="418"/>
-      <c r="AG3" s="418"/>
-      <c r="AH3" s="418"/>
-      <c r="AI3" s="418"/>
-      <c r="AJ3" s="418"/>
-      <c r="AK3" s="418"/>
-      <c r="AL3" s="418"/>
-      <c r="AM3" s="418"/>
-      <c r="AN3" s="418"/>
-      <c r="AO3" s="418"/>
-      <c r="AP3" s="418"/>
-      <c r="AQ3" s="418"/>
-      <c r="AR3" s="418"/>
-      <c r="AS3" s="418"/>
-      <c r="AT3" s="418"/>
-      <c r="AU3" s="418"/>
-      <c r="AV3" s="418"/>
-      <c r="AW3" s="418"/>
-      <c r="AX3" s="418"/>
-      <c r="AY3" s="418"/>
-      <c r="AZ3" s="418"/>
-      <c r="BA3" s="418"/>
-      <c r="BB3" s="418"/>
-      <c r="BC3" s="418"/>
-      <c r="BD3" s="418"/>
-      <c r="BE3" s="418"/>
-      <c r="BF3" s="418"/>
-      <c r="BG3" s="418"/>
-      <c r="BH3" s="418"/>
-      <c r="BI3" s="418"/>
-      <c r="BJ3" s="418"/>
-      <c r="BK3" s="418"/>
-      <c r="BL3" s="418"/>
-      <c r="BM3" s="418"/>
-      <c r="BN3" s="418"/>
-      <c r="BO3" s="418"/>
-      <c r="BP3" s="418"/>
-      <c r="BQ3" s="418"/>
-      <c r="BR3" s="418"/>
-      <c r="BS3" s="418"/>
-      <c r="BT3" s="418"/>
-      <c r="BU3" s="418"/>
-      <c r="BW3" s="417" t="s">
+      <c r="A3" s="425"/>
+      <c r="B3" s="416"/>
+      <c r="C3" s="416"/>
+      <c r="D3" s="416"/>
+      <c r="E3" s="416"/>
+      <c r="F3" s="416"/>
+      <c r="G3" s="416"/>
+      <c r="H3" s="416"/>
+      <c r="I3" s="416"/>
+      <c r="J3" s="416"/>
+      <c r="K3" s="416"/>
+      <c r="L3" s="416"/>
+      <c r="M3" s="416"/>
+      <c r="N3" s="416"/>
+      <c r="O3" s="416"/>
+      <c r="P3" s="416"/>
+      <c r="Q3" s="416"/>
+      <c r="R3" s="416"/>
+      <c r="S3" s="416"/>
+      <c r="T3" s="416"/>
+      <c r="U3" s="416"/>
+      <c r="V3" s="416"/>
+      <c r="W3" s="416"/>
+      <c r="X3" s="416"/>
+      <c r="Y3" s="416"/>
+      <c r="Z3" s="416"/>
+      <c r="AA3" s="416"/>
+      <c r="AB3" s="416"/>
+      <c r="AC3" s="416"/>
+      <c r="AD3" s="416"/>
+      <c r="AE3" s="416"/>
+      <c r="AF3" s="416"/>
+      <c r="AG3" s="416"/>
+      <c r="AH3" s="416"/>
+      <c r="AI3" s="416"/>
+      <c r="AJ3" s="416"/>
+      <c r="AK3" s="416"/>
+      <c r="AL3" s="416"/>
+      <c r="AM3" s="416"/>
+      <c r="AN3" s="416"/>
+      <c r="AO3" s="416"/>
+      <c r="AP3" s="416"/>
+      <c r="AQ3" s="416"/>
+      <c r="AR3" s="416"/>
+      <c r="AS3" s="416"/>
+      <c r="AT3" s="416"/>
+      <c r="AU3" s="416"/>
+      <c r="AV3" s="416"/>
+      <c r="AW3" s="416"/>
+      <c r="AX3" s="416"/>
+      <c r="AY3" s="416"/>
+      <c r="AZ3" s="416"/>
+      <c r="BA3" s="416"/>
+      <c r="BB3" s="416"/>
+      <c r="BC3" s="416"/>
+      <c r="BD3" s="416"/>
+      <c r="BE3" s="416"/>
+      <c r="BF3" s="416"/>
+      <c r="BG3" s="416"/>
+      <c r="BH3" s="416"/>
+      <c r="BI3" s="416"/>
+      <c r="BJ3" s="416"/>
+      <c r="BK3" s="416"/>
+      <c r="BL3" s="416"/>
+      <c r="BM3" s="416"/>
+      <c r="BN3" s="416"/>
+      <c r="BO3" s="416"/>
+      <c r="BP3" s="416"/>
+      <c r="BQ3" s="416"/>
+      <c r="BR3" s="416"/>
+      <c r="BS3" s="416"/>
+      <c r="BT3" s="416"/>
+      <c r="BU3" s="416"/>
+      <c r="BW3" s="415" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="418"/>
-      <c r="BY3" s="418"/>
-      <c r="BZ3" s="418"/>
-      <c r="CA3" s="418"/>
-      <c r="CB3" s="418"/>
+      <c r="BX3" s="416"/>
+      <c r="BY3" s="416"/>
+      <c r="BZ3" s="416"/>
+      <c r="CA3" s="416"/>
+      <c r="CB3" s="416"/>
       <c r="CC3" s="42"/>
       <c r="CD3" s="42"/>
       <c r="CE3" s="43" t="s">
@@ -12147,364 +12202,364 @@
       <c r="BS4" s="44"/>
       <c r="BT4" s="44"/>
       <c r="BU4" s="44"/>
-      <c r="BW4" s="418"/>
-      <c r="BX4" s="418"/>
-      <c r="BY4" s="418"/>
-      <c r="BZ4" s="418"/>
-      <c r="CA4" s="418"/>
-      <c r="CB4" s="418"/>
+      <c r="BW4" s="416"/>
+      <c r="BX4" s="416"/>
+      <c r="BY4" s="416"/>
+      <c r="BZ4" s="416"/>
+      <c r="CA4" s="416"/>
+      <c r="CB4" s="416"/>
       <c r="CC4" s="42"/>
       <c r="CD4" s="42"/>
     </row>
     <row r="5" spans="1:87" s="45" customFormat="1">
-      <c r="A5" s="405" t="s">
+      <c r="A5" s="428" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="416" t="s">
+      <c r="B5" s="427" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="404" t="s">
+      <c r="C5" s="401" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="411" t="s">
+      <c r="D5" s="426" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="411" t="s">
+      <c r="E5" s="426" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="404" t="s">
+      <c r="F5" s="401" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="404" t="s">
+      <c r="G5" s="401" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="334" t="s">
+      <c r="H5" s="352" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="334" t="s">
+      <c r="I5" s="352" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="404" t="s">
+      <c r="J5" s="401" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="409" t="s">
+      <c r="K5" s="430" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="401"/>
-      <c r="M5" s="401"/>
-      <c r="N5" s="401"/>
-      <c r="O5" s="401"/>
-      <c r="P5" s="401"/>
-      <c r="Q5" s="401"/>
-      <c r="R5" s="401"/>
-      <c r="S5" s="401"/>
-      <c r="T5" s="401"/>
-      <c r="U5" s="401"/>
-      <c r="V5" s="401"/>
-      <c r="W5" s="401"/>
-      <c r="X5" s="401"/>
-      <c r="Y5" s="404" t="s">
+      <c r="L5" s="412"/>
+      <c r="M5" s="412"/>
+      <c r="N5" s="412"/>
+      <c r="O5" s="412"/>
+      <c r="P5" s="412"/>
+      <c r="Q5" s="412"/>
+      <c r="R5" s="412"/>
+      <c r="S5" s="412"/>
+      <c r="T5" s="412"/>
+      <c r="U5" s="412"/>
+      <c r="V5" s="412"/>
+      <c r="W5" s="412"/>
+      <c r="X5" s="412"/>
+      <c r="Y5" s="401" t="s">
         <v>15</v>
       </c>
-      <c r="Z5" s="401"/>
-      <c r="AA5" s="401"/>
-      <c r="AB5" s="401"/>
-      <c r="AC5" s="401"/>
-      <c r="AD5" s="401"/>
-      <c r="AE5" s="401"/>
-      <c r="AF5" s="401"/>
-      <c r="AG5" s="401"/>
-      <c r="AH5" s="401"/>
-      <c r="AI5" s="401"/>
-      <c r="AJ5" s="401"/>
-      <c r="AK5" s="401"/>
-      <c r="AL5" s="401"/>
-      <c r="AM5" s="401"/>
-      <c r="AN5" s="401"/>
-      <c r="AO5" s="402"/>
-      <c r="AP5" s="404" t="s">
+      <c r="Z5" s="412"/>
+      <c r="AA5" s="412"/>
+      <c r="AB5" s="412"/>
+      <c r="AC5" s="412"/>
+      <c r="AD5" s="412"/>
+      <c r="AE5" s="412"/>
+      <c r="AF5" s="412"/>
+      <c r="AG5" s="412"/>
+      <c r="AH5" s="412"/>
+      <c r="AI5" s="412"/>
+      <c r="AJ5" s="412"/>
+      <c r="AK5" s="412"/>
+      <c r="AL5" s="412"/>
+      <c r="AM5" s="412"/>
+      <c r="AN5" s="412"/>
+      <c r="AO5" s="413"/>
+      <c r="AP5" s="401" t="s">
         <v>16</v>
       </c>
-      <c r="AQ5" s="404" t="s">
+      <c r="AQ5" s="401" t="s">
         <v>17</v>
       </c>
-      <c r="AR5" s="404" t="s">
+      <c r="AR5" s="401" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="404" t="s">
+      <c r="AS5" s="401" t="s">
         <v>19</v>
       </c>
-      <c r="AT5" s="404" t="s">
+      <c r="AT5" s="401" t="s">
         <v>20</v>
       </c>
-      <c r="AU5" s="404" t="s">
+      <c r="AU5" s="401" t="s">
         <v>21</v>
       </c>
-      <c r="AV5" s="404" t="s">
+      <c r="AV5" s="401" t="s">
         <v>22</v>
       </c>
-      <c r="AW5" s="404" t="s">
+      <c r="AW5" s="401" t="s">
         <v>23</v>
       </c>
-      <c r="AX5" s="404" t="s">
+      <c r="AX5" s="401" t="s">
         <v>24</v>
       </c>
-      <c r="AY5" s="400" t="s">
+      <c r="AY5" s="411" t="s">
         <v>25</v>
       </c>
-      <c r="AZ5" s="401"/>
-      <c r="BA5" s="401"/>
-      <c r="BB5" s="401"/>
-      <c r="BC5" s="401"/>
-      <c r="BD5" s="401"/>
-      <c r="BE5" s="401"/>
-      <c r="BF5" s="401"/>
-      <c r="BG5" s="401"/>
-      <c r="BH5" s="401"/>
-      <c r="BI5" s="401"/>
-      <c r="BJ5" s="401"/>
-      <c r="BK5" s="401"/>
-      <c r="BL5" s="401"/>
-      <c r="BM5" s="401"/>
-      <c r="BN5" s="401"/>
-      <c r="BO5" s="401"/>
-      <c r="BP5" s="401"/>
-      <c r="BQ5" s="402"/>
-      <c r="BR5" s="421" t="s">
+      <c r="AZ5" s="412"/>
+      <c r="BA5" s="412"/>
+      <c r="BB5" s="412"/>
+      <c r="BC5" s="412"/>
+      <c r="BD5" s="412"/>
+      <c r="BE5" s="412"/>
+      <c r="BF5" s="412"/>
+      <c r="BG5" s="412"/>
+      <c r="BH5" s="412"/>
+      <c r="BI5" s="412"/>
+      <c r="BJ5" s="412"/>
+      <c r="BK5" s="412"/>
+      <c r="BL5" s="412"/>
+      <c r="BM5" s="412"/>
+      <c r="BN5" s="412"/>
+      <c r="BO5" s="412"/>
+      <c r="BP5" s="412"/>
+      <c r="BQ5" s="413"/>
+      <c r="BR5" s="417" t="s">
         <v>26</v>
       </c>
-      <c r="BS5" s="414"/>
-      <c r="BT5" s="400" t="s">
+      <c r="BS5" s="418"/>
+      <c r="BT5" s="411" t="s">
         <v>27</v>
       </c>
-      <c r="BU5" s="432" t="s">
+      <c r="BU5" s="405" t="s">
         <v>28</v>
       </c>
-      <c r="BW5" s="433" t="s">
+      <c r="BW5" s="408" t="s">
         <v>29</v>
       </c>
-      <c r="BX5" s="422" t="s">
+      <c r="BX5" s="419" t="s">
         <v>30</v>
       </c>
-      <c r="BY5" s="423"/>
-      <c r="BZ5" s="423"/>
-      <c r="CA5" s="414"/>
-      <c r="CB5" s="434" t="s">
+      <c r="BY5" s="420"/>
+      <c r="BZ5" s="420"/>
+      <c r="CA5" s="418"/>
+      <c r="CB5" s="414" t="s">
         <v>31</v>
       </c>
-      <c r="CC5" s="419" t="s">
+      <c r="CC5" s="396" t="s">
         <v>32</v>
       </c>
-      <c r="CD5" s="419" t="s">
+      <c r="CD5" s="396" t="s">
         <v>33</v>
       </c>
       <c r="CH5" s="46"/>
       <c r="CI5" s="47"/>
     </row>
     <row r="6" spans="1:87" s="45" customFormat="1">
-      <c r="A6" s="398"/>
-      <c r="B6" s="398"/>
-      <c r="C6" s="398"/>
-      <c r="D6" s="398"/>
-      <c r="E6" s="398"/>
-      <c r="F6" s="398"/>
-      <c r="G6" s="398"/>
-      <c r="H6" s="398"/>
-      <c r="I6" s="398"/>
-      <c r="J6" s="398"/>
-      <c r="K6" s="412" t="s">
+      <c r="A6" s="397"/>
+      <c r="B6" s="397"/>
+      <c r="C6" s="397"/>
+      <c r="D6" s="397"/>
+      <c r="E6" s="397"/>
+      <c r="F6" s="397"/>
+      <c r="G6" s="397"/>
+      <c r="H6" s="397"/>
+      <c r="I6" s="397"/>
+      <c r="J6" s="397"/>
+      <c r="K6" s="402" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="412" t="s">
+      <c r="L6" s="402" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="412" t="s">
+      <c r="M6" s="402" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="412" t="s">
+      <c r="N6" s="402" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="412" t="s">
+      <c r="O6" s="402" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="412" t="s">
+      <c r="P6" s="402" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="412" t="s">
+      <c r="Q6" s="402" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="412" t="s">
+      <c r="R6" s="402" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="412" t="s">
+      <c r="S6" s="402" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="412" t="s">
+      <c r="T6" s="402" t="s">
         <v>43</v>
       </c>
-      <c r="U6" s="412" t="s">
+      <c r="U6" s="402" t="s">
         <v>44</v>
       </c>
-      <c r="V6" s="413" t="s">
+      <c r="V6" s="432" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="414"/>
-      <c r="X6" s="412" t="s">
+      <c r="W6" s="418"/>
+      <c r="X6" s="402" t="s">
         <v>46</v>
       </c>
-      <c r="Y6" s="404" t="s">
+      <c r="Y6" s="401" t="s">
         <v>47</v>
       </c>
-      <c r="Z6" s="404" t="s">
+      <c r="Z6" s="401" t="s">
         <v>48</v>
       </c>
-      <c r="AA6" s="404" t="s">
+      <c r="AA6" s="401" t="s">
         <v>49</v>
       </c>
-      <c r="AB6" s="404" t="s">
+      <c r="AB6" s="401" t="s">
         <v>50</v>
       </c>
-      <c r="AC6" s="334" t="s">
+      <c r="AC6" s="352" t="s">
         <v>51</v>
       </c>
-      <c r="AD6" s="334" t="s">
+      <c r="AD6" s="352" t="s">
         <v>52</v>
       </c>
-      <c r="AE6" s="334" t="s">
+      <c r="AE6" s="352" t="s">
         <v>53</v>
       </c>
-      <c r="AF6" s="334" t="s">
+      <c r="AF6" s="352" t="s">
         <v>54</v>
       </c>
-      <c r="AG6" s="404" t="s">
+      <c r="AG6" s="401" t="s">
         <v>55</v>
       </c>
-      <c r="AH6" s="334" t="s">
+      <c r="AH6" s="352" t="s">
         <v>56</v>
       </c>
-      <c r="AI6" s="334" t="s">
+      <c r="AI6" s="352" t="s">
         <v>57</v>
       </c>
-      <c r="AJ6" s="404" t="s">
+      <c r="AJ6" s="401" t="s">
         <v>58</v>
       </c>
-      <c r="AK6" s="406" t="s">
+      <c r="AK6" s="429" t="s">
         <v>59</v>
       </c>
-      <c r="AL6" s="404" t="s">
+      <c r="AL6" s="401" t="s">
         <v>60</v>
       </c>
-      <c r="AM6" s="404" t="s">
+      <c r="AM6" s="401" t="s">
         <v>61</v>
       </c>
-      <c r="AN6" s="410" t="s">
+      <c r="AN6" s="431" t="s">
         <v>62</v>
       </c>
-      <c r="AO6" s="404" t="s">
+      <c r="AO6" s="401" t="s">
         <v>63</v>
       </c>
-      <c r="AP6" s="398"/>
-      <c r="AQ6" s="398"/>
-      <c r="AR6" s="398"/>
-      <c r="AS6" s="398"/>
-      <c r="AT6" s="398"/>
-      <c r="AU6" s="398"/>
-      <c r="AV6" s="398"/>
-      <c r="AW6" s="398"/>
-      <c r="AX6" s="398"/>
-      <c r="AY6" s="400" t="s">
+      <c r="AP6" s="397"/>
+      <c r="AQ6" s="397"/>
+      <c r="AR6" s="397"/>
+      <c r="AS6" s="397"/>
+      <c r="AT6" s="397"/>
+      <c r="AU6" s="397"/>
+      <c r="AV6" s="397"/>
+      <c r="AW6" s="397"/>
+      <c r="AX6" s="397"/>
+      <c r="AY6" s="411" t="s">
         <v>25</v>
       </c>
-      <c r="AZ6" s="401"/>
-      <c r="BA6" s="401"/>
-      <c r="BB6" s="401"/>
-      <c r="BC6" s="401"/>
-      <c r="BD6" s="401"/>
-      <c r="BE6" s="401"/>
-      <c r="BF6" s="401"/>
-      <c r="BG6" s="401"/>
-      <c r="BH6" s="401"/>
-      <c r="BI6" s="401"/>
-      <c r="BJ6" s="401"/>
-      <c r="BK6" s="401"/>
-      <c r="BL6" s="402"/>
-      <c r="BM6" s="400" t="s">
+      <c r="AZ6" s="412"/>
+      <c r="BA6" s="412"/>
+      <c r="BB6" s="412"/>
+      <c r="BC6" s="412"/>
+      <c r="BD6" s="412"/>
+      <c r="BE6" s="412"/>
+      <c r="BF6" s="412"/>
+      <c r="BG6" s="412"/>
+      <c r="BH6" s="412"/>
+      <c r="BI6" s="412"/>
+      <c r="BJ6" s="412"/>
+      <c r="BK6" s="412"/>
+      <c r="BL6" s="413"/>
+      <c r="BM6" s="411" t="s">
         <v>64</v>
       </c>
-      <c r="BN6" s="401"/>
-      <c r="BO6" s="401"/>
-      <c r="BP6" s="401"/>
-      <c r="BQ6" s="402"/>
-      <c r="BR6" s="397" t="s">
+      <c r="BN6" s="412"/>
+      <c r="BO6" s="412"/>
+      <c r="BP6" s="412"/>
+      <c r="BQ6" s="413"/>
+      <c r="BR6" s="399" t="s">
         <v>65</v>
       </c>
-      <c r="BS6" s="397" t="s">
+      <c r="BS6" s="399" t="s">
         <v>66</v>
       </c>
-      <c r="BT6" s="398"/>
-      <c r="BU6" s="407"/>
-      <c r="BW6" s="425"/>
-      <c r="BX6" s="407"/>
-      <c r="BY6" s="424"/>
-      <c r="BZ6" s="424"/>
-      <c r="CA6" s="425"/>
-      <c r="CB6" s="398"/>
-      <c r="CC6" s="398"/>
-      <c r="CD6" s="398"/>
+      <c r="BT6" s="397"/>
+      <c r="BU6" s="406"/>
+      <c r="BW6" s="409"/>
+      <c r="BX6" s="406"/>
+      <c r="BY6" s="421"/>
+      <c r="BZ6" s="421"/>
+      <c r="CA6" s="409"/>
+      <c r="CB6" s="397"/>
+      <c r="CC6" s="397"/>
+      <c r="CD6" s="397"/>
       <c r="CH6" s="46"/>
       <c r="CI6" s="47"/>
     </row>
     <row r="7" spans="1:87" s="48" customFormat="1" ht="12">
-      <c r="A7" s="398"/>
-      <c r="B7" s="398"/>
-      <c r="C7" s="398"/>
-      <c r="D7" s="398"/>
-      <c r="E7" s="398"/>
-      <c r="F7" s="398"/>
-      <c r="G7" s="398"/>
-      <c r="H7" s="398"/>
-      <c r="I7" s="398"/>
-      <c r="J7" s="398"/>
-      <c r="K7" s="398"/>
-      <c r="L7" s="398"/>
-      <c r="M7" s="398"/>
-      <c r="N7" s="398"/>
-      <c r="O7" s="398"/>
-      <c r="P7" s="398"/>
-      <c r="Q7" s="398"/>
-      <c r="R7" s="398"/>
-      <c r="S7" s="398"/>
-      <c r="T7" s="398"/>
-      <c r="U7" s="398"/>
-      <c r="V7" s="408"/>
-      <c r="W7" s="415"/>
-      <c r="X7" s="398"/>
-      <c r="Y7" s="398"/>
-      <c r="Z7" s="398"/>
-      <c r="AA7" s="398"/>
-      <c r="AB7" s="398"/>
-      <c r="AC7" s="398"/>
-      <c r="AD7" s="398"/>
-      <c r="AE7" s="398"/>
-      <c r="AF7" s="398"/>
-      <c r="AG7" s="398"/>
-      <c r="AH7" s="398"/>
-      <c r="AI7" s="398"/>
-      <c r="AJ7" s="398"/>
-      <c r="AK7" s="407"/>
-      <c r="AL7" s="398"/>
-      <c r="AM7" s="398"/>
-      <c r="AN7" s="398"/>
-      <c r="AO7" s="398"/>
-      <c r="AP7" s="398"/>
-      <c r="AQ7" s="398"/>
-      <c r="AR7" s="398"/>
-      <c r="AS7" s="398"/>
-      <c r="AT7" s="398"/>
-      <c r="AU7" s="398"/>
-      <c r="AV7" s="398"/>
-      <c r="AW7" s="398"/>
-      <c r="AX7" s="398"/>
+      <c r="A7" s="397"/>
+      <c r="B7" s="397"/>
+      <c r="C7" s="397"/>
+      <c r="D7" s="397"/>
+      <c r="E7" s="397"/>
+      <c r="F7" s="397"/>
+      <c r="G7" s="397"/>
+      <c r="H7" s="397"/>
+      <c r="I7" s="397"/>
+      <c r="J7" s="397"/>
+      <c r="K7" s="397"/>
+      <c r="L7" s="397"/>
+      <c r="M7" s="397"/>
+      <c r="N7" s="397"/>
+      <c r="O7" s="397"/>
+      <c r="P7" s="397"/>
+      <c r="Q7" s="397"/>
+      <c r="R7" s="397"/>
+      <c r="S7" s="397"/>
+      <c r="T7" s="397"/>
+      <c r="U7" s="397"/>
+      <c r="V7" s="407"/>
+      <c r="W7" s="433"/>
+      <c r="X7" s="397"/>
+      <c r="Y7" s="397"/>
+      <c r="Z7" s="397"/>
+      <c r="AA7" s="397"/>
+      <c r="AB7" s="397"/>
+      <c r="AC7" s="397"/>
+      <c r="AD7" s="397"/>
+      <c r="AE7" s="397"/>
+      <c r="AF7" s="397"/>
+      <c r="AG7" s="397"/>
+      <c r="AH7" s="397"/>
+      <c r="AI7" s="397"/>
+      <c r="AJ7" s="397"/>
+      <c r="AK7" s="406"/>
+      <c r="AL7" s="397"/>
+      <c r="AM7" s="397"/>
+      <c r="AN7" s="397"/>
+      <c r="AO7" s="397"/>
+      <c r="AP7" s="397"/>
+      <c r="AQ7" s="397"/>
+      <c r="AR7" s="397"/>
+      <c r="AS7" s="397"/>
+      <c r="AT7" s="397"/>
+      <c r="AU7" s="397"/>
+      <c r="AV7" s="397"/>
+      <c r="AW7" s="397"/>
+      <c r="AX7" s="397"/>
       <c r="AY7" s="29" t="s">
         <v>67</v>
       </c>
@@ -12514,7 +12569,7 @@
       <c r="BA7" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="BB7" s="400" t="s">
+      <c r="BB7" s="411" t="s">
         <v>70</v>
       </c>
       <c r="BC7" s="403" t="s">
@@ -12523,7 +12578,7 @@
       <c r="BD7" s="403" t="s">
         <v>72</v>
       </c>
-      <c r="BE7" s="429" t="s">
+      <c r="BE7" s="424" t="s">
         <v>73</v>
       </c>
       <c r="BF7" s="403" t="s">
@@ -12544,94 +12599,94 @@
       <c r="BK7" s="403" t="s">
         <v>79</v>
       </c>
-      <c r="BL7" s="431" t="s">
+      <c r="BL7" s="404" t="s">
         <v>80</v>
       </c>
       <c r="BM7" s="403" t="s">
         <v>81</v>
       </c>
-      <c r="BN7" s="400" t="s">
+      <c r="BN7" s="411" t="s">
         <v>82</v>
       </c>
       <c r="BO7" s="403" t="s">
         <v>83</v>
       </c>
-      <c r="BP7" s="400" t="s">
+      <c r="BP7" s="411" t="s">
         <v>84</v>
       </c>
-      <c r="BQ7" s="400" t="s">
+      <c r="BQ7" s="411" t="s">
         <v>85</v>
       </c>
-      <c r="BR7" s="398"/>
-      <c r="BS7" s="398"/>
-      <c r="BT7" s="398"/>
-      <c r="BU7" s="407"/>
-      <c r="BW7" s="425"/>
-      <c r="BX7" s="426"/>
-      <c r="BY7" s="427"/>
-      <c r="BZ7" s="427"/>
-      <c r="CA7" s="428"/>
-      <c r="CB7" s="398"/>
-      <c r="CC7" s="398"/>
-      <c r="CD7" s="398"/>
+      <c r="BR7" s="397"/>
+      <c r="BS7" s="397"/>
+      <c r="BT7" s="397"/>
+      <c r="BU7" s="406"/>
+      <c r="BW7" s="409"/>
+      <c r="BX7" s="422"/>
+      <c r="BY7" s="423"/>
+      <c r="BZ7" s="423"/>
+      <c r="CA7" s="410"/>
+      <c r="CB7" s="397"/>
+      <c r="CC7" s="397"/>
+      <c r="CD7" s="397"/>
       <c r="CH7" s="46"/>
       <c r="CI7" s="47"/>
     </row>
     <row r="8" spans="1:87" s="48" customFormat="1" ht="12">
-      <c r="A8" s="399"/>
-      <c r="B8" s="399"/>
-      <c r="C8" s="399"/>
-      <c r="D8" s="399"/>
-      <c r="E8" s="399"/>
-      <c r="F8" s="399"/>
-      <c r="G8" s="399"/>
-      <c r="H8" s="399"/>
-      <c r="I8" s="399"/>
-      <c r="J8" s="399"/>
-      <c r="K8" s="399"/>
-      <c r="L8" s="399"/>
-      <c r="M8" s="399"/>
-      <c r="N8" s="399"/>
-      <c r="O8" s="399"/>
-      <c r="P8" s="399"/>
-      <c r="Q8" s="399"/>
-      <c r="R8" s="399"/>
-      <c r="S8" s="399"/>
-      <c r="T8" s="399"/>
-      <c r="U8" s="399"/>
+      <c r="A8" s="400"/>
+      <c r="B8" s="400"/>
+      <c r="C8" s="400"/>
+      <c r="D8" s="400"/>
+      <c r="E8" s="400"/>
+      <c r="F8" s="400"/>
+      <c r="G8" s="400"/>
+      <c r="H8" s="400"/>
+      <c r="I8" s="400"/>
+      <c r="J8" s="400"/>
+      <c r="K8" s="400"/>
+      <c r="L8" s="400"/>
+      <c r="M8" s="400"/>
+      <c r="N8" s="400"/>
+      <c r="O8" s="400"/>
+      <c r="P8" s="400"/>
+      <c r="Q8" s="400"/>
+      <c r="R8" s="400"/>
+      <c r="S8" s="400"/>
+      <c r="T8" s="400"/>
+      <c r="U8" s="400"/>
       <c r="V8" s="49" t="s">
         <v>86</v>
       </c>
       <c r="W8" s="49" t="s">
         <v>87</v>
       </c>
-      <c r="X8" s="399"/>
-      <c r="Y8" s="399"/>
-      <c r="Z8" s="399"/>
-      <c r="AA8" s="399"/>
-      <c r="AB8" s="399"/>
-      <c r="AC8" s="399"/>
-      <c r="AD8" s="399"/>
-      <c r="AE8" s="399"/>
-      <c r="AF8" s="399"/>
-      <c r="AG8" s="399"/>
-      <c r="AH8" s="399"/>
-      <c r="AI8" s="399"/>
-      <c r="AJ8" s="399"/>
-      <c r="AK8" s="408"/>
-      <c r="AL8" s="399"/>
-      <c r="AM8" s="399"/>
-      <c r="AN8" s="399"/>
-      <c r="AO8" s="399"/>
-      <c r="AP8" s="399"/>
-      <c r="AQ8" s="399"/>
-      <c r="AR8" s="399"/>
-      <c r="AS8" s="399"/>
-      <c r="AT8" s="399"/>
-      <c r="AU8" s="399"/>
-      <c r="AV8" s="399"/>
-      <c r="AW8" s="399"/>
-      <c r="AX8" s="399"/>
+      <c r="X8" s="400"/>
+      <c r="Y8" s="400"/>
+      <c r="Z8" s="400"/>
+      <c r="AA8" s="400"/>
+      <c r="AB8" s="400"/>
+      <c r="AC8" s="400"/>
+      <c r="AD8" s="400"/>
+      <c r="AE8" s="400"/>
+      <c r="AF8" s="400"/>
+      <c r="AG8" s="400"/>
+      <c r="AH8" s="400"/>
+      <c r="AI8" s="400"/>
+      <c r="AJ8" s="400"/>
+      <c r="AK8" s="407"/>
+      <c r="AL8" s="400"/>
+      <c r="AM8" s="400"/>
+      <c r="AN8" s="400"/>
+      <c r="AO8" s="400"/>
+      <c r="AP8" s="400"/>
+      <c r="AQ8" s="400"/>
+      <c r="AR8" s="400"/>
+      <c r="AS8" s="400"/>
+      <c r="AT8" s="400"/>
+      <c r="AU8" s="400"/>
+      <c r="AV8" s="400"/>
+      <c r="AW8" s="400"/>
+      <c r="AX8" s="400"/>
       <c r="AY8" s="30" t="s">
         <v>88</v>
       </c>
@@ -12641,27 +12696,27 @@
       <c r="BA8" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="BB8" s="399"/>
-      <c r="BC8" s="399"/>
-      <c r="BD8" s="399"/>
-      <c r="BE8" s="399"/>
-      <c r="BF8" s="399"/>
-      <c r="BG8" s="399"/>
-      <c r="BH8" s="399"/>
-      <c r="BI8" s="399"/>
-      <c r="BJ8" s="399"/>
-      <c r="BK8" s="399"/>
-      <c r="BL8" s="399"/>
-      <c r="BM8" s="399"/>
-      <c r="BN8" s="399"/>
-      <c r="BO8" s="399"/>
-      <c r="BP8" s="399"/>
-      <c r="BQ8" s="399"/>
-      <c r="BR8" s="399"/>
-      <c r="BS8" s="399"/>
-      <c r="BT8" s="399"/>
-      <c r="BU8" s="408"/>
-      <c r="BW8" s="428"/>
+      <c r="BB8" s="400"/>
+      <c r="BC8" s="400"/>
+      <c r="BD8" s="400"/>
+      <c r="BE8" s="400"/>
+      <c r="BF8" s="400"/>
+      <c r="BG8" s="400"/>
+      <c r="BH8" s="400"/>
+      <c r="BI8" s="400"/>
+      <c r="BJ8" s="400"/>
+      <c r="BK8" s="400"/>
+      <c r="BL8" s="400"/>
+      <c r="BM8" s="400"/>
+      <c r="BN8" s="400"/>
+      <c r="BO8" s="400"/>
+      <c r="BP8" s="400"/>
+      <c r="BQ8" s="400"/>
+      <c r="BR8" s="400"/>
+      <c r="BS8" s="400"/>
+      <c r="BT8" s="400"/>
+      <c r="BU8" s="407"/>
+      <c r="BW8" s="410"/>
       <c r="BX8" s="23" t="s">
         <v>91</v>
       </c>
@@ -12674,9 +12729,9 @@
       <c r="CA8" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="CB8" s="420"/>
-      <c r="CC8" s="420"/>
-      <c r="CD8" s="420"/>
+      <c r="CB8" s="398"/>
+      <c r="CC8" s="398"/>
+      <c r="CD8" s="398"/>
       <c r="CE8" s="45"/>
       <c r="CF8" s="50"/>
       <c r="CH8" s="46"/>
@@ -15134,6 +15189,72 @@
   </sheetData>
   <autoFilter ref="A9:CI14" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="82">
+    <mergeCell ref="BS6:BS8"/>
+    <mergeCell ref="BM6:BQ6"/>
+    <mergeCell ref="AC6:AC8"/>
+    <mergeCell ref="BC7:BC8"/>
+    <mergeCell ref="AE6:AE8"/>
+    <mergeCell ref="BK7:BK8"/>
+    <mergeCell ref="BQ7:BQ8"/>
+    <mergeCell ref="BN7:BN8"/>
+    <mergeCell ref="BP7:BP8"/>
+    <mergeCell ref="AM6:AM8"/>
+    <mergeCell ref="AP5:AP8"/>
+    <mergeCell ref="BO7:BO8"/>
+    <mergeCell ref="BB7:BB8"/>
+    <mergeCell ref="BD7:BD8"/>
+    <mergeCell ref="BF7:BF8"/>
+    <mergeCell ref="BH7:BH8"/>
+    <mergeCell ref="AS5:AS8"/>
+    <mergeCell ref="AU5:AU8"/>
+    <mergeCell ref="AB6:AB8"/>
+    <mergeCell ref="AH6:AH8"/>
+    <mergeCell ref="AJ6:AJ8"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="C5:C8"/>
+    <mergeCell ref="AK6:AK8"/>
+    <mergeCell ref="BI7:BI8"/>
+    <mergeCell ref="K5:X5"/>
+    <mergeCell ref="AO6:AO8"/>
+    <mergeCell ref="Y5:AO5"/>
+    <mergeCell ref="AN6:AN8"/>
+    <mergeCell ref="AR5:AR8"/>
+    <mergeCell ref="AA6:AA8"/>
+    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="X6:X8"/>
+    <mergeCell ref="AV5:AV8"/>
+    <mergeCell ref="AX5:AX8"/>
+    <mergeCell ref="V6:W7"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="G5:G8"/>
+    <mergeCell ref="AQ5:AQ8"/>
+    <mergeCell ref="I5:I8"/>
+    <mergeCell ref="R6:R8"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="AL6:AL8"/>
+    <mergeCell ref="P6:P8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="F5:F8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="Q6:Q8"/>
+    <mergeCell ref="S6:S8"/>
+    <mergeCell ref="T6:T8"/>
+    <mergeCell ref="BW3:CB4"/>
+    <mergeCell ref="CC5:CC8"/>
+    <mergeCell ref="AY6:BL6"/>
+    <mergeCell ref="H5:H8"/>
+    <mergeCell ref="BR5:BS5"/>
+    <mergeCell ref="J5:J8"/>
+    <mergeCell ref="BX5:CA7"/>
+    <mergeCell ref="U6:U8"/>
+    <mergeCell ref="AG6:AG8"/>
+    <mergeCell ref="BE7:BE8"/>
+    <mergeCell ref="BG7:BG8"/>
+    <mergeCell ref="AD6:AD8"/>
+    <mergeCell ref="AF6:AF8"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="K6:K8"/>
     <mergeCell ref="CD5:CD8"/>
     <mergeCell ref="BR6:BR8"/>
     <mergeCell ref="AT5:AT8"/>
@@ -15150,87 +15271,21 @@
     <mergeCell ref="AY5:BQ5"/>
     <mergeCell ref="CB5:CB8"/>
     <mergeCell ref="BT5:BT8"/>
-    <mergeCell ref="BW3:CB4"/>
-    <mergeCell ref="CC5:CC8"/>
-    <mergeCell ref="AY6:BL6"/>
-    <mergeCell ref="H5:H8"/>
-    <mergeCell ref="BR5:BS5"/>
-    <mergeCell ref="J5:J8"/>
-    <mergeCell ref="BX5:CA7"/>
-    <mergeCell ref="U6:U8"/>
-    <mergeCell ref="AG6:AG8"/>
-    <mergeCell ref="BE7:BE8"/>
-    <mergeCell ref="BG7:BG8"/>
-    <mergeCell ref="AD6:AD8"/>
-    <mergeCell ref="AF6:AF8"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="E5:E8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="G5:G8"/>
-    <mergeCell ref="AQ5:AQ8"/>
-    <mergeCell ref="I5:I8"/>
-    <mergeCell ref="R6:R8"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="AL6:AL8"/>
-    <mergeCell ref="P6:P8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="F5:F8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="Q6:Q8"/>
-    <mergeCell ref="S6:S8"/>
-    <mergeCell ref="T6:T8"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="C5:C8"/>
-    <mergeCell ref="AK6:AK8"/>
-    <mergeCell ref="BI7:BI8"/>
-    <mergeCell ref="K5:X5"/>
-    <mergeCell ref="AO6:AO8"/>
-    <mergeCell ref="Y5:AO5"/>
-    <mergeCell ref="AN6:AN8"/>
-    <mergeCell ref="AR5:AR8"/>
-    <mergeCell ref="AA6:AA8"/>
-    <mergeCell ref="D5:D8"/>
-    <mergeCell ref="X6:X8"/>
-    <mergeCell ref="AV5:AV8"/>
-    <mergeCell ref="AX5:AX8"/>
-    <mergeCell ref="V6:W7"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="AS5:AS8"/>
-    <mergeCell ref="AU5:AU8"/>
-    <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="AH6:AH8"/>
-    <mergeCell ref="AJ6:AJ8"/>
-    <mergeCell ref="BS6:BS8"/>
-    <mergeCell ref="BM6:BQ6"/>
-    <mergeCell ref="AC6:AC8"/>
-    <mergeCell ref="BC7:BC8"/>
-    <mergeCell ref="AE6:AE8"/>
-    <mergeCell ref="BK7:BK8"/>
-    <mergeCell ref="BQ7:BQ8"/>
-    <mergeCell ref="BN7:BN8"/>
-    <mergeCell ref="BP7:BP8"/>
-    <mergeCell ref="AM6:AM8"/>
-    <mergeCell ref="AP5:AP8"/>
-    <mergeCell ref="BO7:BO8"/>
-    <mergeCell ref="BB7:BB8"/>
-    <mergeCell ref="BD7:BD8"/>
-    <mergeCell ref="BF7:BF8"/>
-    <mergeCell ref="BH7:BH8"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B9 B12:B16 B20:B1048576 C9:BU9 D10:F10 J10:BK10 BM10:BU10 BW9:CD10">
-    <cfRule type="duplicateValues" dxfId="21" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B9 B12:B16 B20:B1048576 C9:BU9">
-    <cfRule type="duplicateValues" dxfId="20" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19:C19">
-    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="BL10">
-    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="4"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.21" bottom="0.17" header="0.196850393700787" footer="0.196850393700787"/>
@@ -15247,16 +15302,16 @@
   <dimension ref="A1:CG26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" outlineLevelRow="1" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="5.5" style="309" customWidth="1"/>
-    <col min="2" max="2" width="8.5" style="310" customWidth="1"/>
-    <col min="3" max="3" width="18.1640625" style="311" customWidth="1"/>
+    <col min="1" max="1" width="5.5" style="306" customWidth="1"/>
+    <col min="2" max="2" width="8.5" style="307" customWidth="1"/>
+    <col min="3" max="3" width="18.1640625" style="308" customWidth="1"/>
     <col min="4" max="4" width="19.6640625" style="255" customWidth="1" outlineLevel="1"/>
     <col min="5" max="5" width="19.83203125" style="255" customWidth="1" outlineLevel="1"/>
     <col min="6" max="6" width="5.5" style="256" bestFit="1" customWidth="1" outlineLevel="1"/>
     <col min="7" max="7" width="13.6640625" style="258" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.5" style="258" customWidth="1"/>
-    <col min="9" max="9" width="12.5" style="314" customWidth="1"/>
-    <col min="10" max="10" width="7.5" style="314" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="12.5" style="311" customWidth="1"/>
+    <col min="10" max="10" width="7.5" style="311" customWidth="1" outlineLevel="1"/>
     <col min="11" max="24" width="7.1640625" style="257" customWidth="1"/>
     <col min="25" max="47" width="12.33203125" style="258" customWidth="1"/>
     <col min="48" max="49" width="13" style="258" customWidth="1"/>
@@ -15265,14 +15320,14 @@
     <col min="54" max="71" width="10.5" style="258" customWidth="1"/>
     <col min="72" max="72" width="12.5" style="258" customWidth="1"/>
     <col min="73" max="77" width="12.6640625" style="258" customWidth="1" outlineLevel="1"/>
-    <col min="78" max="78" width="12.6640625" style="315" customWidth="1" outlineLevel="1"/>
-    <col min="79" max="80" width="10.6640625" style="315" customWidth="1" outlineLevel="1"/>
-    <col min="81" max="81" width="19.5" style="316" customWidth="1"/>
-    <col min="82" max="82" width="12.33203125" style="316" customWidth="1"/>
-    <col min="83" max="83" width="12.5" style="316" customWidth="1"/>
-    <col min="84" max="84" width="11.6640625" style="316" customWidth="1"/>
-    <col min="85" max="85" width="9.1640625" style="316" customWidth="1"/>
-    <col min="86" max="16384" width="9.1640625" style="316"/>
+    <col min="78" max="78" width="12.6640625" style="312" customWidth="1" outlineLevel="1"/>
+    <col min="79" max="80" width="10.6640625" style="312" customWidth="1" outlineLevel="1"/>
+    <col min="81" max="81" width="19.5" style="313" customWidth="1"/>
+    <col min="82" max="82" width="12.33203125" style="313" customWidth="1"/>
+    <col min="83" max="83" width="12.5" style="313" customWidth="1"/>
+    <col min="84" max="84" width="11.6640625" style="313" customWidth="1"/>
+    <col min="85" max="85" width="9.1640625" style="313" customWidth="1"/>
+    <col min="86" max="16384" width="9.1640625" style="313"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:85" s="239" customFormat="1" ht="23.25" customHeight="1" outlineLevel="1">
@@ -15437,90 +15492,90 @@
       <c r="CB2" s="268"/>
     </row>
     <row r="3" spans="1:85" s="240" customFormat="1" ht="24" customHeight="1" outlineLevel="1">
-      <c r="A3" s="440"/>
-      <c r="B3" s="439"/>
-      <c r="C3" s="439"/>
-      <c r="D3" s="439"/>
-      <c r="E3" s="439"/>
-      <c r="F3" s="439"/>
-      <c r="G3" s="439"/>
-      <c r="H3" s="439"/>
-      <c r="I3" s="439"/>
-      <c r="J3" s="439"/>
-      <c r="K3" s="439"/>
-      <c r="L3" s="439"/>
-      <c r="M3" s="439"/>
-      <c r="N3" s="439"/>
-      <c r="O3" s="439"/>
-      <c r="P3" s="439"/>
-      <c r="Q3" s="439"/>
-      <c r="R3" s="439"/>
-      <c r="S3" s="439"/>
-      <c r="T3" s="439"/>
-      <c r="U3" s="439"/>
-      <c r="V3" s="439"/>
-      <c r="W3" s="439"/>
-      <c r="X3" s="439"/>
-      <c r="Y3" s="439"/>
-      <c r="Z3" s="439"/>
-      <c r="AA3" s="439"/>
-      <c r="AB3" s="439"/>
-      <c r="AC3" s="439"/>
-      <c r="AD3" s="439"/>
-      <c r="AE3" s="439"/>
-      <c r="AF3" s="439"/>
-      <c r="AG3" s="439"/>
-      <c r="AH3" s="439"/>
-      <c r="AI3" s="439"/>
-      <c r="AJ3" s="439"/>
-      <c r="AK3" s="439"/>
-      <c r="AL3" s="439"/>
-      <c r="AM3" s="439"/>
-      <c r="AN3" s="439"/>
-      <c r="AO3" s="439"/>
-      <c r="AP3" s="439"/>
-      <c r="AQ3" s="439"/>
-      <c r="AR3" s="439"/>
-      <c r="AS3" s="439"/>
-      <c r="AT3" s="439"/>
-      <c r="AU3" s="439"/>
-      <c r="AV3" s="439"/>
-      <c r="AW3" s="439"/>
-      <c r="AX3" s="439"/>
-      <c r="AY3" s="439"/>
-      <c r="AZ3" s="439"/>
-      <c r="BA3" s="439"/>
-      <c r="BB3" s="439"/>
-      <c r="BC3" s="439"/>
-      <c r="BD3" s="439"/>
-      <c r="BE3" s="439"/>
-      <c r="BF3" s="439"/>
-      <c r="BG3" s="439"/>
-      <c r="BH3" s="439"/>
-      <c r="BI3" s="439"/>
-      <c r="BJ3" s="439"/>
-      <c r="BK3" s="439"/>
-      <c r="BL3" s="439"/>
-      <c r="BM3" s="439"/>
-      <c r="BN3" s="439"/>
-      <c r="BO3" s="439"/>
-      <c r="BP3" s="439"/>
-      <c r="BQ3" s="439"/>
-      <c r="BR3" s="439"/>
-      <c r="BS3" s="439"/>
-      <c r="BT3" s="439"/>
-      <c r="BU3" s="438" t="s">
+      <c r="A3" s="474"/>
+      <c r="B3" s="475"/>
+      <c r="C3" s="475"/>
+      <c r="D3" s="475"/>
+      <c r="E3" s="475"/>
+      <c r="F3" s="475"/>
+      <c r="G3" s="475"/>
+      <c r="H3" s="475"/>
+      <c r="I3" s="475"/>
+      <c r="J3" s="475"/>
+      <c r="K3" s="475"/>
+      <c r="L3" s="475"/>
+      <c r="M3" s="475"/>
+      <c r="N3" s="475"/>
+      <c r="O3" s="475"/>
+      <c r="P3" s="475"/>
+      <c r="Q3" s="475"/>
+      <c r="R3" s="475"/>
+      <c r="S3" s="475"/>
+      <c r="T3" s="475"/>
+      <c r="U3" s="475"/>
+      <c r="V3" s="475"/>
+      <c r="W3" s="475"/>
+      <c r="X3" s="475"/>
+      <c r="Y3" s="475"/>
+      <c r="Z3" s="475"/>
+      <c r="AA3" s="475"/>
+      <c r="AB3" s="475"/>
+      <c r="AC3" s="475"/>
+      <c r="AD3" s="475"/>
+      <c r="AE3" s="475"/>
+      <c r="AF3" s="475"/>
+      <c r="AG3" s="475"/>
+      <c r="AH3" s="475"/>
+      <c r="AI3" s="475"/>
+      <c r="AJ3" s="475"/>
+      <c r="AK3" s="475"/>
+      <c r="AL3" s="475"/>
+      <c r="AM3" s="475"/>
+      <c r="AN3" s="475"/>
+      <c r="AO3" s="475"/>
+      <c r="AP3" s="475"/>
+      <c r="AQ3" s="475"/>
+      <c r="AR3" s="475"/>
+      <c r="AS3" s="475"/>
+      <c r="AT3" s="475"/>
+      <c r="AU3" s="475"/>
+      <c r="AV3" s="475"/>
+      <c r="AW3" s="475"/>
+      <c r="AX3" s="475"/>
+      <c r="AY3" s="475"/>
+      <c r="AZ3" s="475"/>
+      <c r="BA3" s="475"/>
+      <c r="BB3" s="475"/>
+      <c r="BC3" s="475"/>
+      <c r="BD3" s="475"/>
+      <c r="BE3" s="475"/>
+      <c r="BF3" s="475"/>
+      <c r="BG3" s="475"/>
+      <c r="BH3" s="475"/>
+      <c r="BI3" s="475"/>
+      <c r="BJ3" s="475"/>
+      <c r="BK3" s="475"/>
+      <c r="BL3" s="475"/>
+      <c r="BM3" s="475"/>
+      <c r="BN3" s="475"/>
+      <c r="BO3" s="475"/>
+      <c r="BP3" s="475"/>
+      <c r="BQ3" s="475"/>
+      <c r="BR3" s="475"/>
+      <c r="BS3" s="475"/>
+      <c r="BT3" s="475"/>
+      <c r="BU3" s="489" t="s">
         <v>2</v>
       </c>
-      <c r="BV3" s="439"/>
-      <c r="BW3" s="439"/>
-      <c r="BX3" s="439"/>
-      <c r="BY3" s="439"/>
-      <c r="BZ3" s="439"/>
+      <c r="BV3" s="475"/>
+      <c r="BW3" s="475"/>
+      <c r="BX3" s="475"/>
+      <c r="BY3" s="475"/>
+      <c r="BZ3" s="475"/>
       <c r="CA3" s="270"/>
       <c r="CB3" s="270"/>
     </row>
-    <row r="4" spans="1:85" s="240" customFormat="1" ht="21.5" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="4" spans="1:85" s="240" customFormat="1" ht="21.5" customHeight="1" outlineLevel="1">
       <c r="A4" s="271"/>
       <c r="B4" s="271"/>
       <c r="C4" s="271"/>
@@ -15592,16 +15647,16 @@
       <c r="BR4" s="271"/>
       <c r="BS4" s="271"/>
       <c r="BT4" s="271"/>
-      <c r="BU4" s="439"/>
-      <c r="BV4" s="439"/>
-      <c r="BW4" s="439"/>
-      <c r="BX4" s="439"/>
-      <c r="BY4" s="439"/>
-      <c r="BZ4" s="439"/>
+      <c r="BU4" s="475"/>
+      <c r="BV4" s="475"/>
+      <c r="BW4" s="475"/>
+      <c r="BX4" s="475"/>
+      <c r="BY4" s="475"/>
+      <c r="BZ4" s="475"/>
       <c r="CA4" s="270"/>
       <c r="CB4" s="270"/>
     </row>
-    <row r="5" spans="1:85" s="240" customFormat="1" ht="20.25" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="5" spans="1:85" s="240" customFormat="1" ht="20.25" customHeight="1" outlineLevel="1">
       <c r="A5" s="271"/>
       <c r="B5" s="271"/>
       <c r="C5" s="271"/>
@@ -15673,16 +15728,16 @@
       <c r="BR5" s="271"/>
       <c r="BS5" s="271"/>
       <c r="BT5" s="271"/>
-      <c r="BU5" s="439"/>
-      <c r="BV5" s="439"/>
-      <c r="BW5" s="439"/>
-      <c r="BX5" s="439"/>
-      <c r="BY5" s="439"/>
-      <c r="BZ5" s="439"/>
+      <c r="BU5" s="475"/>
+      <c r="BV5" s="475"/>
+      <c r="BW5" s="475"/>
+      <c r="BX5" s="475"/>
+      <c r="BY5" s="475"/>
+      <c r="BZ5" s="475"/>
       <c r="CA5" s="270"/>
       <c r="CB5" s="270"/>
     </row>
-    <row r="6" spans="1:85" s="240" customFormat="1" ht="18.75" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="6" spans="1:85" s="240" customFormat="1" ht="18.75" customHeight="1" outlineLevel="1">
       <c r="A6" s="273"/>
       <c r="B6" s="273"/>
       <c r="C6" s="273"/>
@@ -15754,187 +15809,236 @@
       <c r="BR6" s="273"/>
       <c r="BS6" s="273"/>
       <c r="BT6" s="273"/>
-      <c r="BU6" s="439"/>
-      <c r="BV6" s="439"/>
-      <c r="BW6" s="439"/>
-      <c r="BX6" s="439"/>
-      <c r="BY6" s="439"/>
-      <c r="BZ6" s="439"/>
+      <c r="BU6" s="475"/>
+      <c r="BV6" s="475"/>
+      <c r="BW6" s="475"/>
+      <c r="BX6" s="475"/>
+      <c r="BY6" s="475"/>
+      <c r="BZ6" s="475"/>
       <c r="CA6" s="270"/>
       <c r="CB6" s="270"/>
     </row>
-    <row r="7" spans="1:85" s="240" customFormat="1" ht="12.75" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A7" s="43"/>
-      <c r="B7" s="281"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="281"/>
-      <c r="E7" s="281"/>
-      <c r="F7" s="282"/>
-      <c r="G7" s="281"/>
-      <c r="H7" s="281"/>
-      <c r="I7" s="280"/>
-      <c r="K7" s="130"/>
-      <c r="L7" s="130"/>
-      <c r="M7" s="130"/>
-      <c r="N7" s="130"/>
-      <c r="O7" s="130"/>
-      <c r="P7" s="130"/>
-      <c r="Q7" s="130"/>
-      <c r="R7" s="130"/>
-      <c r="S7" s="130"/>
-      <c r="T7" s="130"/>
-      <c r="U7" s="283"/>
-      <c r="V7" s="130"/>
-      <c r="W7" s="130"/>
-      <c r="X7" s="130"/>
-      <c r="Y7" s="275"/>
-      <c r="Z7" s="275"/>
-      <c r="AA7" s="275"/>
-      <c r="AB7" s="275"/>
-      <c r="AC7" s="271"/>
-      <c r="AD7" s="271"/>
-      <c r="AE7" s="271"/>
-      <c r="AF7" s="271"/>
-      <c r="AG7" s="271"/>
-      <c r="AH7" s="271"/>
-      <c r="AI7" s="271"/>
-      <c r="AJ7" s="271"/>
-      <c r="AK7" s="271"/>
-      <c r="AL7" s="271"/>
-      <c r="AM7" s="271"/>
-      <c r="AN7" s="271"/>
-      <c r="AO7" s="271"/>
-      <c r="AP7" s="271"/>
-      <c r="AQ7" s="271"/>
-      <c r="AR7" s="271"/>
-      <c r="AS7" s="271"/>
-      <c r="AT7" s="271"/>
-      <c r="AU7" s="271"/>
-      <c r="AV7" s="43"/>
-      <c r="AW7" s="43"/>
-      <c r="AX7" s="43"/>
-      <c r="AY7" s="281"/>
-      <c r="AZ7" s="43"/>
-      <c r="BA7" s="281"/>
-      <c r="BB7" s="281"/>
-      <c r="BC7" s="43"/>
-      <c r="BD7" s="43"/>
-      <c r="BE7" s="281"/>
-      <c r="BF7" s="281"/>
-      <c r="BG7" s="281"/>
-      <c r="BH7" s="281"/>
-      <c r="BI7" s="281"/>
-      <c r="BJ7" s="43"/>
-      <c r="BK7" s="43"/>
-      <c r="BL7" s="281"/>
-      <c r="BM7" s="43"/>
-      <c r="BN7" s="281"/>
-      <c r="BO7" s="281"/>
-      <c r="BP7" s="43"/>
-      <c r="BQ7" s="43"/>
-      <c r="BR7" s="43"/>
-      <c r="BS7" s="43"/>
-      <c r="BT7" s="281"/>
-      <c r="BU7" s="127"/>
-      <c r="BV7" s="127"/>
-      <c r="BW7" s="127"/>
-      <c r="BX7" s="127"/>
-      <c r="BY7" s="127"/>
-      <c r="BZ7" s="283"/>
-      <c r="CA7" s="283"/>
-      <c r="CB7" s="283"/>
+    <row r="7" spans="1:85" s="514" customFormat="1" ht="31" outlineLevel="1">
+      <c r="B7" s="273" t="s">
+        <v>236</v>
+      </c>
+      <c r="C7" s="273" t="s">
+        <v>236</v>
+      </c>
+      <c r="D7" s="515"/>
+      <c r="E7" s="515" t="s">
+        <v>156</v>
+      </c>
+      <c r="F7" s="516"/>
+      <c r="G7" s="515" t="s">
+        <v>156</v>
+      </c>
+      <c r="H7" s="515"/>
+      <c r="I7" s="517" t="s">
+        <v>158</v>
+      </c>
+      <c r="J7" s="514" t="s">
+        <v>157</v>
+      </c>
+      <c r="K7" s="519"/>
+      <c r="L7" s="519"/>
+      <c r="M7" s="519"/>
+      <c r="N7" s="519"/>
+      <c r="O7" s="519"/>
+      <c r="P7" s="519"/>
+      <c r="Q7" s="519"/>
+      <c r="R7" s="519"/>
+      <c r="S7" s="519"/>
+      <c r="T7" s="519"/>
+      <c r="U7" s="520"/>
+      <c r="V7" s="519"/>
+      <c r="W7" s="519"/>
+      <c r="X7" s="519"/>
+      <c r="Y7" s="518" t="s">
+        <v>158</v>
+      </c>
+      <c r="Z7" s="518" t="s">
+        <v>158</v>
+      </c>
+      <c r="AA7" s="518" t="s">
+        <v>158</v>
+      </c>
+      <c r="AB7" s="518"/>
+      <c r="AC7" s="519" t="s">
+        <v>158</v>
+      </c>
+      <c r="AD7" s="273" t="s">
+        <v>158</v>
+      </c>
+      <c r="AE7" s="273" t="s">
+        <v>158</v>
+      </c>
+      <c r="AF7" s="273"/>
+      <c r="AG7" s="273"/>
+      <c r="AH7" s="273" t="s">
+        <v>158</v>
+      </c>
+      <c r="AI7" s="273" t="s">
+        <v>158</v>
+      </c>
+      <c r="AJ7" s="273"/>
+      <c r="AK7" s="273"/>
+      <c r="AL7" s="273" t="s">
+        <v>158</v>
+      </c>
+      <c r="AM7" s="273" t="s">
+        <v>158</v>
+      </c>
+      <c r="AN7" s="273" t="s">
+        <v>158</v>
+      </c>
+      <c r="AO7" s="273" t="s">
+        <v>158</v>
+      </c>
+      <c r="AP7" s="273" t="s">
+        <v>159</v>
+      </c>
+      <c r="AQ7" s="273"/>
+      <c r="AR7" s="273" t="s">
+        <v>159</v>
+      </c>
+      <c r="AS7" s="273" t="s">
+        <v>159</v>
+      </c>
+      <c r="AT7" s="273" t="s">
+        <v>156</v>
+      </c>
+      <c r="AU7" s="273" t="s">
+        <v>159</v>
+      </c>
+      <c r="AY7" s="515"/>
+      <c r="BA7" s="515"/>
+      <c r="BB7" s="273" t="s">
+        <v>160</v>
+      </c>
+      <c r="BE7" s="515"/>
+      <c r="BF7" s="515"/>
+      <c r="BG7" s="515"/>
+      <c r="BH7" s="515"/>
+      <c r="BI7" s="273"/>
+      <c r="BJ7" s="514" t="s">
+        <v>160</v>
+      </c>
+      <c r="BL7" s="515"/>
+      <c r="BN7" s="515"/>
+      <c r="BO7" s="515"/>
+      <c r="BT7" s="515" t="s">
+        <v>161</v>
+      </c>
+      <c r="BU7" s="331"/>
+      <c r="BV7" s="331" t="s">
+        <v>156</v>
+      </c>
+      <c r="BW7" s="331" t="s">
+        <v>156</v>
+      </c>
+      <c r="BX7" s="331"/>
+      <c r="BY7" s="331" t="s">
+        <v>156</v>
+      </c>
+      <c r="BZ7" s="520"/>
+      <c r="CA7" s="520"/>
+      <c r="CB7" s="520"/>
+      <c r="CC7" s="514" t="s">
+        <v>236</v>
+      </c>
     </row>
-    <row r="8" spans="1:85" s="330" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A8" s="442" t="s">
+    <row r="8" spans="1:85" s="327" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A8" s="505" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="443" t="s">
+      <c r="B8" s="476" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="444" t="s">
+      <c r="C8" s="451" t="s">
         <v>162</v>
       </c>
-      <c r="D8" s="445" t="s">
+      <c r="D8" s="486" t="s">
         <v>163</v>
       </c>
-      <c r="E8" s="445" t="s">
+      <c r="E8" s="486" t="s">
         <v>164</v>
       </c>
-      <c r="F8" s="446" t="s">
+      <c r="F8" s="440" t="s">
         <v>142</v>
       </c>
-      <c r="G8" s="447" t="s">
+      <c r="G8" s="437" t="s">
         <v>165</v>
       </c>
-      <c r="H8" s="448" t="s">
+      <c r="H8" s="434" t="s">
         <v>166</v>
       </c>
-      <c r="I8" s="448" t="s">
+      <c r="I8" s="434" t="s">
         <v>167</v>
       </c>
-      <c r="J8" s="447" t="s">
+      <c r="J8" s="437" t="s">
         <v>168</v>
       </c>
-      <c r="K8" s="435" t="s">
+      <c r="K8" s="508" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="436"/>
-      <c r="M8" s="436"/>
-      <c r="N8" s="436"/>
-      <c r="O8" s="436"/>
-      <c r="P8" s="436"/>
-      <c r="Q8" s="436"/>
-      <c r="R8" s="436"/>
-      <c r="S8" s="436"/>
-      <c r="T8" s="436"/>
-      <c r="U8" s="436"/>
-      <c r="V8" s="436"/>
-      <c r="W8" s="436"/>
-      <c r="X8" s="436"/>
-      <c r="Y8" s="513" t="s">
+      <c r="L8" s="509"/>
+      <c r="M8" s="509"/>
+      <c r="N8" s="509"/>
+      <c r="O8" s="509"/>
+      <c r="P8" s="509"/>
+      <c r="Q8" s="509"/>
+      <c r="R8" s="509"/>
+      <c r="S8" s="509"/>
+      <c r="T8" s="509"/>
+      <c r="U8" s="509"/>
+      <c r="V8" s="509"/>
+      <c r="W8" s="509"/>
+      <c r="X8" s="509"/>
+      <c r="Y8" s="454" t="s">
         <v>200</v>
       </c>
-      <c r="Z8" s="514"/>
-      <c r="AA8" s="514"/>
-      <c r="AB8" s="514"/>
-      <c r="AC8" s="514"/>
-      <c r="AD8" s="514"/>
-      <c r="AE8" s="514"/>
-      <c r="AF8" s="514"/>
-      <c r="AG8" s="514"/>
-      <c r="AH8" s="514"/>
-      <c r="AI8" s="514"/>
-      <c r="AJ8" s="514"/>
-      <c r="AK8" s="514"/>
-      <c r="AL8" s="514"/>
-      <c r="AM8" s="514"/>
-      <c r="AN8" s="514"/>
-      <c r="AO8" s="515"/>
-      <c r="AP8" s="447" t="s">
+      <c r="Z8" s="455"/>
+      <c r="AA8" s="455"/>
+      <c r="AB8" s="455"/>
+      <c r="AC8" s="455"/>
+      <c r="AD8" s="455"/>
+      <c r="AE8" s="455"/>
+      <c r="AF8" s="455"/>
+      <c r="AG8" s="455"/>
+      <c r="AH8" s="455"/>
+      <c r="AI8" s="455"/>
+      <c r="AJ8" s="455"/>
+      <c r="AK8" s="455"/>
+      <c r="AL8" s="455"/>
+      <c r="AM8" s="455"/>
+      <c r="AN8" s="455"/>
+      <c r="AO8" s="456"/>
+      <c r="AP8" s="437" t="s">
         <v>201</v>
       </c>
-      <c r="AQ8" s="447" t="s">
+      <c r="AQ8" s="437" t="s">
         <v>202</v>
       </c>
-      <c r="AR8" s="447" t="s">
+      <c r="AR8" s="437" t="s">
         <v>203</v>
       </c>
-      <c r="AS8" s="447" t="s">
+      <c r="AS8" s="437" t="s">
         <v>204</v>
       </c>
-      <c r="AT8" s="447" t="s">
+      <c r="AT8" s="437" t="s">
         <v>205</v>
       </c>
-      <c r="AU8" s="447" t="s">
+      <c r="AU8" s="437" t="s">
         <v>206</v>
       </c>
-      <c r="AV8" s="444" t="s">
+      <c r="AV8" s="451" t="s">
         <v>207</v>
       </c>
-      <c r="AW8" s="470" t="s">
+      <c r="AW8" s="462" t="s">
         <v>208</v>
       </c>
-      <c r="AX8" s="444" t="s">
+      <c r="AX8" s="451" t="s">
         <v>24</v>
       </c>
       <c r="AY8" s="510" t="s">
@@ -15961,363 +16065,363 @@
         <v>220</v>
       </c>
       <c r="BR8" s="504"/>
-      <c r="BS8" s="444" t="s">
+      <c r="BS8" s="451" t="s">
         <v>221</v>
       </c>
-      <c r="BT8" s="444" t="s">
+      <c r="BT8" s="451" t="s">
         <v>222</v>
       </c>
-      <c r="BU8" s="337" t="s">
+      <c r="BU8" s="392" t="s">
         <v>223</v>
       </c>
-      <c r="BV8" s="492" t="s">
+      <c r="BV8" s="490" t="s">
         <v>232</v>
       </c>
-      <c r="BW8" s="493"/>
-      <c r="BX8" s="493"/>
-      <c r="BY8" s="494"/>
-      <c r="BZ8" s="419" t="s">
+      <c r="BW8" s="491"/>
+      <c r="BX8" s="491"/>
+      <c r="BY8" s="492"/>
+      <c r="BZ8" s="396" t="s">
         <v>228</v>
       </c>
-      <c r="CA8" s="419" t="s">
+      <c r="CA8" s="396" t="s">
         <v>229</v>
       </c>
-      <c r="CB8" s="419" t="s">
+      <c r="CB8" s="396" t="s">
         <v>230</v>
       </c>
-      <c r="CF8" s="331"/>
-      <c r="CG8" s="331"/>
+      <c r="CF8" s="328"/>
+      <c r="CG8" s="328"/>
     </row>
-    <row r="9" spans="1:85" s="330" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A9" s="449"/>
-      <c r="B9" s="450"/>
-      <c r="C9" s="451"/>
-      <c r="D9" s="452"/>
-      <c r="E9" s="452"/>
-      <c r="F9" s="453"/>
-      <c r="G9" s="454"/>
-      <c r="H9" s="455"/>
-      <c r="I9" s="455"/>
-      <c r="J9" s="454"/>
-      <c r="K9" s="466" t="s">
+    <row r="9" spans="1:85" s="327" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A9" s="506"/>
+      <c r="B9" s="477"/>
+      <c r="C9" s="452"/>
+      <c r="D9" s="487"/>
+      <c r="E9" s="487"/>
+      <c r="F9" s="441"/>
+      <c r="G9" s="438"/>
+      <c r="H9" s="435"/>
+      <c r="I9" s="435"/>
+      <c r="J9" s="438"/>
+      <c r="K9" s="471" t="s">
         <v>169</v>
       </c>
-      <c r="L9" s="466" t="s">
+      <c r="L9" s="471" t="s">
         <v>170</v>
       </c>
-      <c r="M9" s="466" t="s">
+      <c r="M9" s="471" t="s">
         <v>171</v>
       </c>
-      <c r="N9" s="466" t="s">
+      <c r="N9" s="471" t="s">
         <v>172</v>
       </c>
-      <c r="O9" s="466" t="s">
+      <c r="O9" s="471" t="s">
         <v>173</v>
       </c>
-      <c r="P9" s="466" t="s">
+      <c r="P9" s="471" t="s">
         <v>174</v>
       </c>
-      <c r="Q9" s="466" t="s">
+      <c r="Q9" s="471" t="s">
         <v>175</v>
       </c>
-      <c r="R9" s="466" t="s">
+      <c r="R9" s="471" t="s">
         <v>176</v>
       </c>
-      <c r="S9" s="466" t="s">
+      <c r="S9" s="471" t="s">
         <v>177</v>
       </c>
-      <c r="T9" s="466" t="s">
+      <c r="T9" s="471" t="s">
         <v>178</v>
       </c>
-      <c r="U9" s="466" t="s">
+      <c r="U9" s="471" t="s">
         <v>179</v>
       </c>
-      <c r="V9" s="462" t="s">
+      <c r="V9" s="467" t="s">
         <v>180</v>
       </c>
-      <c r="W9" s="463"/>
-      <c r="X9" s="466" t="s">
+      <c r="W9" s="468"/>
+      <c r="X9" s="471" t="s">
         <v>183</v>
       </c>
-      <c r="Y9" s="467" t="s">
+      <c r="Y9" s="445" t="s">
         <v>47</v>
       </c>
-      <c r="Z9" s="467" t="s">
+      <c r="Z9" s="445" t="s">
         <v>184</v>
       </c>
-      <c r="AA9" s="467" t="s">
+      <c r="AA9" s="445" t="s">
         <v>185</v>
       </c>
-      <c r="AB9" s="467" t="s">
+      <c r="AB9" s="445" t="s">
         <v>186</v>
       </c>
-      <c r="AC9" s="467" t="s">
+      <c r="AC9" s="445" t="s">
         <v>187</v>
       </c>
-      <c r="AD9" s="467" t="s">
+      <c r="AD9" s="445" t="s">
         <v>188</v>
       </c>
-      <c r="AE9" s="467" t="s">
+      <c r="AE9" s="445" t="s">
         <v>189</v>
       </c>
-      <c r="AF9" s="467" t="s">
+      <c r="AF9" s="445" t="s">
         <v>190</v>
       </c>
-      <c r="AG9" s="467" t="s">
+      <c r="AG9" s="445" t="s">
         <v>191</v>
       </c>
-      <c r="AH9" s="467" t="s">
+      <c r="AH9" s="445" t="s">
         <v>192</v>
       </c>
-      <c r="AI9" s="467" t="s">
+      <c r="AI9" s="445" t="s">
         <v>193</v>
       </c>
-      <c r="AJ9" s="468" t="s">
+      <c r="AJ9" s="459" t="s">
         <v>194</v>
       </c>
-      <c r="AK9" s="469" t="s">
+      <c r="AK9" s="448" t="s">
         <v>195</v>
       </c>
-      <c r="AL9" s="470" t="s">
+      <c r="AL9" s="462" t="s">
         <v>196</v>
       </c>
-      <c r="AM9" s="467" t="s">
+      <c r="AM9" s="445" t="s">
         <v>197</v>
       </c>
-      <c r="AN9" s="444" t="s">
+      <c r="AN9" s="451" t="s">
         <v>198</v>
       </c>
-      <c r="AO9" s="444" t="s">
+      <c r="AO9" s="451" t="s">
         <v>199</v>
       </c>
-      <c r="AP9" s="454"/>
-      <c r="AQ9" s="454"/>
-      <c r="AR9" s="454"/>
-      <c r="AS9" s="454"/>
-      <c r="AT9" s="454"/>
-      <c r="AU9" s="454"/>
-      <c r="AV9" s="451"/>
-      <c r="AW9" s="475"/>
-      <c r="AX9" s="451"/>
-      <c r="AY9" s="507" t="s">
+      <c r="AP9" s="438"/>
+      <c r="AQ9" s="438"/>
+      <c r="AR9" s="438"/>
+      <c r="AS9" s="438"/>
+      <c r="AT9" s="438"/>
+      <c r="AU9" s="438"/>
+      <c r="AV9" s="452"/>
+      <c r="AW9" s="463"/>
+      <c r="AX9" s="452"/>
+      <c r="AY9" s="483" t="s">
         <v>234</v>
       </c>
-      <c r="AZ9" s="508"/>
-      <c r="BA9" s="508"/>
-      <c r="BB9" s="508"/>
-      <c r="BC9" s="508"/>
-      <c r="BD9" s="508"/>
-      <c r="BE9" s="508"/>
-      <c r="BF9" s="508"/>
-      <c r="BG9" s="508"/>
-      <c r="BH9" s="508"/>
-      <c r="BI9" s="508"/>
-      <c r="BJ9" s="509"/>
-      <c r="BK9" s="507" t="s">
+      <c r="AZ9" s="484"/>
+      <c r="BA9" s="484"/>
+      <c r="BB9" s="484"/>
+      <c r="BC9" s="484"/>
+      <c r="BD9" s="484"/>
+      <c r="BE9" s="484"/>
+      <c r="BF9" s="484"/>
+      <c r="BG9" s="484"/>
+      <c r="BH9" s="484"/>
+      <c r="BI9" s="484"/>
+      <c r="BJ9" s="485"/>
+      <c r="BK9" s="483" t="s">
         <v>233</v>
       </c>
-      <c r="BL9" s="508"/>
-      <c r="BM9" s="508"/>
-      <c r="BN9" s="508"/>
-      <c r="BO9" s="508"/>
-      <c r="BP9" s="509"/>
-      <c r="BQ9" s="451" t="s">
+      <c r="BL9" s="484"/>
+      <c r="BM9" s="484"/>
+      <c r="BN9" s="484"/>
+      <c r="BO9" s="484"/>
+      <c r="BP9" s="485"/>
+      <c r="BQ9" s="452" t="s">
         <v>65</v>
       </c>
-      <c r="BR9" s="451" t="s">
+      <c r="BR9" s="452" t="s">
         <v>219</v>
       </c>
-      <c r="BS9" s="451"/>
-      <c r="BT9" s="451"/>
+      <c r="BS9" s="452"/>
+      <c r="BT9" s="452"/>
       <c r="BU9" s="501"/>
-      <c r="BV9" s="495"/>
-      <c r="BW9" s="496"/>
-      <c r="BX9" s="496"/>
-      <c r="BY9" s="497"/>
-      <c r="BZ9" s="490"/>
-      <c r="CA9" s="490"/>
-      <c r="CB9" s="490"/>
-      <c r="CF9" s="331"/>
-      <c r="CG9" s="331"/>
+      <c r="BV9" s="493"/>
+      <c r="BW9" s="494"/>
+      <c r="BX9" s="494"/>
+      <c r="BY9" s="495"/>
+      <c r="BZ9" s="443"/>
+      <c r="CA9" s="443"/>
+      <c r="CB9" s="443"/>
+      <c r="CF9" s="328"/>
+      <c r="CG9" s="328"/>
     </row>
-    <row r="10" spans="1:85" s="332" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A10" s="449"/>
-      <c r="B10" s="450"/>
-      <c r="C10" s="451"/>
-      <c r="D10" s="452"/>
-      <c r="E10" s="452"/>
-      <c r="F10" s="453"/>
-      <c r="G10" s="454"/>
-      <c r="H10" s="455"/>
-      <c r="I10" s="455"/>
-      <c r="J10" s="454"/>
-      <c r="K10" s="471"/>
-      <c r="L10" s="471"/>
-      <c r="M10" s="471"/>
-      <c r="N10" s="471"/>
-      <c r="O10" s="471"/>
-      <c r="P10" s="471"/>
-      <c r="Q10" s="471"/>
-      <c r="R10" s="471"/>
-      <c r="S10" s="471"/>
-      <c r="T10" s="471"/>
-      <c r="U10" s="471"/>
-      <c r="V10" s="464"/>
-      <c r="W10" s="465"/>
-      <c r="X10" s="471"/>
-      <c r="Y10" s="472"/>
-      <c r="Z10" s="472"/>
-      <c r="AA10" s="472"/>
-      <c r="AB10" s="472"/>
-      <c r="AC10" s="472"/>
-      <c r="AD10" s="472"/>
-      <c r="AE10" s="472"/>
-      <c r="AF10" s="472"/>
-      <c r="AG10" s="472"/>
-      <c r="AH10" s="472"/>
-      <c r="AI10" s="472"/>
-      <c r="AJ10" s="473"/>
-      <c r="AK10" s="474"/>
-      <c r="AL10" s="475"/>
-      <c r="AM10" s="472"/>
-      <c r="AN10" s="451"/>
-      <c r="AO10" s="451"/>
-      <c r="AP10" s="454"/>
-      <c r="AQ10" s="454"/>
-      <c r="AR10" s="454"/>
-      <c r="AS10" s="454"/>
-      <c r="AT10" s="454"/>
-      <c r="AU10" s="454"/>
-      <c r="AV10" s="451"/>
-      <c r="AW10" s="475"/>
-      <c r="AX10" s="451"/>
-      <c r="AY10" s="329" t="s">
+    <row r="10" spans="1:85" s="329" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A10" s="506"/>
+      <c r="B10" s="477"/>
+      <c r="C10" s="452"/>
+      <c r="D10" s="487"/>
+      <c r="E10" s="487"/>
+      <c r="F10" s="441"/>
+      <c r="G10" s="438"/>
+      <c r="H10" s="435"/>
+      <c r="I10" s="435"/>
+      <c r="J10" s="438"/>
+      <c r="K10" s="472"/>
+      <c r="L10" s="472"/>
+      <c r="M10" s="472"/>
+      <c r="N10" s="472"/>
+      <c r="O10" s="472"/>
+      <c r="P10" s="472"/>
+      <c r="Q10" s="472"/>
+      <c r="R10" s="472"/>
+      <c r="S10" s="472"/>
+      <c r="T10" s="472"/>
+      <c r="U10" s="472"/>
+      <c r="V10" s="469"/>
+      <c r="W10" s="470"/>
+      <c r="X10" s="472"/>
+      <c r="Y10" s="446"/>
+      <c r="Z10" s="446"/>
+      <c r="AA10" s="446"/>
+      <c r="AB10" s="446"/>
+      <c r="AC10" s="446"/>
+      <c r="AD10" s="446"/>
+      <c r="AE10" s="446"/>
+      <c r="AF10" s="446"/>
+      <c r="AG10" s="446"/>
+      <c r="AH10" s="446"/>
+      <c r="AI10" s="446"/>
+      <c r="AJ10" s="460"/>
+      <c r="AK10" s="449"/>
+      <c r="AL10" s="463"/>
+      <c r="AM10" s="446"/>
+      <c r="AN10" s="452"/>
+      <c r="AO10" s="452"/>
+      <c r="AP10" s="438"/>
+      <c r="AQ10" s="438"/>
+      <c r="AR10" s="438"/>
+      <c r="AS10" s="438"/>
+      <c r="AT10" s="438"/>
+      <c r="AU10" s="438"/>
+      <c r="AV10" s="452"/>
+      <c r="AW10" s="463"/>
+      <c r="AX10" s="452"/>
+      <c r="AY10" s="326" t="s">
         <v>67</v>
       </c>
-      <c r="AZ10" s="329" t="s">
+      <c r="AZ10" s="326" t="s">
         <v>68</v>
       </c>
-      <c r="BA10" s="329" t="s">
+      <c r="BA10" s="326" t="s">
         <v>69</v>
       </c>
-      <c r="BB10" s="505" t="s">
+      <c r="BB10" s="479" t="s">
         <v>209</v>
       </c>
-      <c r="BC10" s="484" t="s">
+      <c r="BC10" s="481" t="s">
         <v>71</v>
       </c>
-      <c r="BD10" s="484" t="s">
+      <c r="BD10" s="481" t="s">
         <v>210</v>
       </c>
-      <c r="BE10" s="482" t="s">
+      <c r="BE10" s="465" t="s">
         <v>145</v>
       </c>
-      <c r="BF10" s="482" t="s">
+      <c r="BF10" s="465" t="s">
         <v>211</v>
       </c>
-      <c r="BG10" s="482" t="s">
+      <c r="BG10" s="465" t="s">
         <v>212</v>
       </c>
-      <c r="BH10" s="484" t="s">
+      <c r="BH10" s="481" t="s">
         <v>76</v>
       </c>
-      <c r="BI10" s="482" t="s">
+      <c r="BI10" s="465" t="s">
         <v>79</v>
       </c>
-      <c r="BJ10" s="488" t="s">
+      <c r="BJ10" s="457" t="s">
         <v>213</v>
       </c>
-      <c r="BK10" s="484" t="s">
+      <c r="BK10" s="481" t="s">
         <v>214</v>
       </c>
-      <c r="BL10" s="486" t="s">
+      <c r="BL10" s="499" t="s">
         <v>215</v>
       </c>
-      <c r="BM10" s="484" t="s">
+      <c r="BM10" s="481" t="s">
         <v>216</v>
       </c>
-      <c r="BN10" s="486" t="s">
+      <c r="BN10" s="499" t="s">
         <v>217</v>
       </c>
-      <c r="BO10" s="486" t="s">
+      <c r="BO10" s="499" t="s">
         <v>218</v>
       </c>
-      <c r="BP10" s="444" t="s">
+      <c r="BP10" s="451" t="s">
         <v>85</v>
       </c>
-      <c r="BQ10" s="451"/>
-      <c r="BR10" s="451"/>
-      <c r="BS10" s="451"/>
-      <c r="BT10" s="451"/>
+      <c r="BQ10" s="452"/>
+      <c r="BR10" s="452"/>
+      <c r="BS10" s="452"/>
+      <c r="BT10" s="452"/>
       <c r="BU10" s="502"/>
-      <c r="BV10" s="498"/>
-      <c r="BW10" s="499"/>
-      <c r="BX10" s="499"/>
-      <c r="BY10" s="500"/>
-      <c r="BZ10" s="491"/>
-      <c r="CA10" s="491"/>
-      <c r="CB10" s="491"/>
+      <c r="BV10" s="496"/>
+      <c r="BW10" s="497"/>
+      <c r="BX10" s="497"/>
+      <c r="BY10" s="498"/>
+      <c r="BZ10" s="444"/>
+      <c r="CA10" s="444"/>
+      <c r="CB10" s="444"/>
       <c r="CC10" s="228" t="s">
         <v>231</v>
       </c>
-      <c r="CF10" s="331"/>
-      <c r="CG10" s="331"/>
+      <c r="CF10" s="328"/>
+      <c r="CG10" s="328"/>
     </row>
-    <row r="11" spans="1:85" s="332" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A11" s="456"/>
-      <c r="B11" s="457"/>
-      <c r="C11" s="437"/>
-      <c r="D11" s="458"/>
-      <c r="E11" s="458"/>
-      <c r="F11" s="459"/>
-      <c r="G11" s="460"/>
-      <c r="H11" s="461"/>
-      <c r="I11" s="461"/>
-      <c r="J11" s="460"/>
-      <c r="K11" s="476"/>
-      <c r="L11" s="476"/>
-      <c r="M11" s="476"/>
-      <c r="N11" s="476"/>
-      <c r="O11" s="476"/>
-      <c r="P11" s="476"/>
-      <c r="Q11" s="476"/>
-      <c r="R11" s="476"/>
-      <c r="S11" s="476"/>
-      <c r="T11" s="476"/>
-      <c r="U11" s="476"/>
-      <c r="V11" s="481" t="s">
+    <row r="11" spans="1:85" s="329" customFormat="1" ht="38.25" customHeight="1">
+      <c r="A11" s="507"/>
+      <c r="B11" s="478"/>
+      <c r="C11" s="453"/>
+      <c r="D11" s="488"/>
+      <c r="E11" s="488"/>
+      <c r="F11" s="442"/>
+      <c r="G11" s="439"/>
+      <c r="H11" s="436"/>
+      <c r="I11" s="436"/>
+      <c r="J11" s="439"/>
+      <c r="K11" s="473"/>
+      <c r="L11" s="473"/>
+      <c r="M11" s="473"/>
+      <c r="N11" s="473"/>
+      <c r="O11" s="473"/>
+      <c r="P11" s="473"/>
+      <c r="Q11" s="473"/>
+      <c r="R11" s="473"/>
+      <c r="S11" s="473"/>
+      <c r="T11" s="473"/>
+      <c r="U11" s="473"/>
+      <c r="V11" s="332" t="s">
         <v>181</v>
       </c>
-      <c r="W11" s="481" t="s">
+      <c r="W11" s="332" t="s">
         <v>182</v>
       </c>
-      <c r="X11" s="476"/>
-      <c r="Y11" s="477"/>
-      <c r="Z11" s="477"/>
-      <c r="AA11" s="477"/>
-      <c r="AB11" s="477"/>
-      <c r="AC11" s="477"/>
-      <c r="AD11" s="477"/>
-      <c r="AE11" s="477"/>
-      <c r="AF11" s="477"/>
-      <c r="AG11" s="477"/>
-      <c r="AH11" s="477"/>
-      <c r="AI11" s="477"/>
-      <c r="AJ11" s="478"/>
-      <c r="AK11" s="479"/>
-      <c r="AL11" s="480"/>
-      <c r="AM11" s="477"/>
-      <c r="AN11" s="437"/>
-      <c r="AO11" s="437"/>
-      <c r="AP11" s="460"/>
-      <c r="AQ11" s="460"/>
-      <c r="AR11" s="460"/>
-      <c r="AS11" s="460"/>
-      <c r="AT11" s="460"/>
-      <c r="AU11" s="460"/>
-      <c r="AV11" s="437"/>
-      <c r="AW11" s="480"/>
-      <c r="AX11" s="437"/>
+      <c r="X11" s="473"/>
+      <c r="Y11" s="447"/>
+      <c r="Z11" s="447"/>
+      <c r="AA11" s="447"/>
+      <c r="AB11" s="447"/>
+      <c r="AC11" s="447"/>
+      <c r="AD11" s="447"/>
+      <c r="AE11" s="447"/>
+      <c r="AF11" s="447"/>
+      <c r="AG11" s="447"/>
+      <c r="AH11" s="447"/>
+      <c r="AI11" s="447"/>
+      <c r="AJ11" s="461"/>
+      <c r="AK11" s="450"/>
+      <c r="AL11" s="464"/>
+      <c r="AM11" s="447"/>
+      <c r="AN11" s="453"/>
+      <c r="AO11" s="453"/>
+      <c r="AP11" s="439"/>
+      <c r="AQ11" s="439"/>
+      <c r="AR11" s="439"/>
+      <c r="AS11" s="439"/>
+      <c r="AT11" s="439"/>
+      <c r="AU11" s="439"/>
+      <c r="AV11" s="453"/>
+      <c r="AW11" s="464"/>
+      <c r="AX11" s="453"/>
       <c r="AY11" s="229" t="s">
         <v>88</v>
       </c>
@@ -16327,25 +16431,25 @@
       <c r="BA11" s="229" t="s">
         <v>90</v>
       </c>
-      <c r="BB11" s="506"/>
-      <c r="BC11" s="485"/>
-      <c r="BD11" s="485"/>
-      <c r="BE11" s="483"/>
-      <c r="BF11" s="483"/>
-      <c r="BG11" s="483"/>
-      <c r="BH11" s="485"/>
-      <c r="BI11" s="483"/>
-      <c r="BJ11" s="489"/>
-      <c r="BK11" s="485"/>
-      <c r="BL11" s="487"/>
-      <c r="BM11" s="485"/>
-      <c r="BN11" s="487"/>
-      <c r="BO11" s="487"/>
-      <c r="BP11" s="437"/>
-      <c r="BQ11" s="437"/>
-      <c r="BR11" s="437"/>
-      <c r="BS11" s="437"/>
-      <c r="BT11" s="437"/>
+      <c r="BB11" s="480"/>
+      <c r="BC11" s="482"/>
+      <c r="BD11" s="482"/>
+      <c r="BE11" s="466"/>
+      <c r="BF11" s="466"/>
+      <c r="BG11" s="466"/>
+      <c r="BH11" s="482"/>
+      <c r="BI11" s="466"/>
+      <c r="BJ11" s="458"/>
+      <c r="BK11" s="482"/>
+      <c r="BL11" s="500"/>
+      <c r="BM11" s="482"/>
+      <c r="BN11" s="500"/>
+      <c r="BO11" s="500"/>
+      <c r="BP11" s="453"/>
+      <c r="BQ11" s="453"/>
+      <c r="BR11" s="453"/>
+      <c r="BS11" s="453"/>
+      <c r="BT11" s="453"/>
       <c r="BU11" s="502"/>
       <c r="BV11" s="237" t="s">
         <v>224</v>
@@ -16359,18 +16463,18 @@
       <c r="BY11" s="238" t="s">
         <v>227</v>
       </c>
-      <c r="BZ11" s="491"/>
-      <c r="CA11" s="491"/>
-      <c r="CB11" s="491"/>
+      <c r="BZ11" s="444"/>
+      <c r="CA11" s="444"/>
+      <c r="CB11" s="444"/>
       <c r="CC11" s="227">
         <v>25</v>
       </c>
-      <c r="CD11" s="333"/>
-      <c r="CF11" s="331"/>
-      <c r="CG11" s="331"/>
+      <c r="CD11" s="330"/>
+      <c r="CF11" s="328"/>
+      <c r="CG11" s="328"/>
     </row>
     <row r="12" spans="1:85" s="278" customFormat="1" ht="15" customHeight="1">
-      <c r="A12" s="284">
+      <c r="A12" s="281">
         <v>1</v>
       </c>
       <c r="B12" s="276">
@@ -16666,25 +16770,25 @@
       <c r="CG12" s="241"/>
     </row>
     <row r="13" spans="1:85" s="278" customFormat="1" ht="15" customHeight="1">
-      <c r="A13" s="284" t="s">
+      <c r="A13" s="281" t="s">
         <v>96</v>
       </c>
-      <c r="B13" s="284" t="s">
+      <c r="B13" s="281" t="s">
         <v>96</v>
       </c>
-      <c r="C13" s="284" t="s">
+      <c r="C13" s="281" t="s">
         <v>96</v>
       </c>
       <c r="D13" s="276"/>
       <c r="E13" s="276"/>
       <c r="F13" s="276"/>
-      <c r="G13" s="284" t="s">
+      <c r="G13" s="281" t="s">
         <v>96</v>
       </c>
-      <c r="H13" s="284" t="s">
+      <c r="H13" s="281" t="s">
         <v>96</v>
       </c>
-      <c r="I13" s="284" t="s">
+      <c r="I13" s="281" t="s">
         <v>96</v>
       </c>
       <c r="J13" s="276"/>
@@ -16782,38 +16886,38 @@
         <v>185460000</v>
       </c>
       <c r="J14" s="249"/>
-      <c r="K14" s="285">
+      <c r="K14" s="282">
         <f>SUM(K15:K21)</f>
         <v>75.5</v>
       </c>
-      <c r="L14" s="285"/>
-      <c r="M14" s="285"/>
-      <c r="N14" s="285"/>
-      <c r="O14" s="285"/>
-      <c r="P14" s="285"/>
-      <c r="Q14" s="285"/>
-      <c r="R14" s="285">
+      <c r="L14" s="282"/>
+      <c r="M14" s="282"/>
+      <c r="N14" s="282"/>
+      <c r="O14" s="282"/>
+      <c r="P14" s="282"/>
+      <c r="Q14" s="282"/>
+      <c r="R14" s="282">
         <f>SUM(R15:R21)</f>
         <v>12</v>
       </c>
-      <c r="S14" s="285">
+      <c r="S14" s="282">
         <f>SUM(S15:S21)</f>
         <v>0</v>
       </c>
-      <c r="T14" s="285"/>
-      <c r="U14" s="285">
+      <c r="T14" s="282"/>
+      <c r="U14" s="282">
         <f>SUM(U15:U21)</f>
         <v>0</v>
       </c>
-      <c r="V14" s="285">
+      <c r="V14" s="282">
         <f>SUM(V15:V21)</f>
         <v>0</v>
       </c>
-      <c r="W14" s="285">
+      <c r="W14" s="282">
         <f>SUM(W15:W21)</f>
         <v>0</v>
       </c>
-      <c r="X14" s="285">
+      <c r="X14" s="282">
         <f>SUM(X15:X21)</f>
         <v>0</v>
       </c>
@@ -16956,206 +17060,206 @@
       <c r="CB14" s="243"/>
     </row>
     <row r="15" spans="1:85" s="253" customFormat="1" ht="30.5" customHeight="1">
-      <c r="A15" s="318">
+      <c r="A15" s="315">
         <v>1</v>
       </c>
-      <c r="B15" s="319">
+      <c r="B15" s="316">
         <v>2405236</v>
       </c>
-      <c r="C15" s="320" t="s">
+      <c r="C15" s="317" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="321" t="s">
+      <c r="D15" s="318" t="s">
         <v>98</v>
       </c>
-      <c r="E15" s="322" t="s">
+      <c r="E15" s="319" t="s">
         <v>113</v>
       </c>
-      <c r="F15" s="322" t="s">
+      <c r="F15" s="319" t="s">
         <v>100</v>
       </c>
-      <c r="G15" s="323">
+      <c r="G15" s="320">
         <v>9520000</v>
       </c>
-      <c r="H15" s="323">
+      <c r="H15" s="320">
         <f t="shared" ref="H15:H21" si="4">+IF(OR(CA15="ĐT PCCC",CA15="ĐP PCCC"),780000,IF(CA15="AT-VSV",300000,0))</f>
         <v>0</v>
       </c>
-      <c r="I15" s="323">
+      <c r="I15" s="320">
         <f t="shared" ref="I15:I21" si="5">BZ15-BX15-G15-H15</f>
         <v>53480000</v>
       </c>
-      <c r="J15" s="324">
+      <c r="J15" s="321">
         <v>1</v>
       </c>
-      <c r="K15" s="325">
+      <c r="K15" s="322">
         <v>11</v>
       </c>
-      <c r="L15" s="325"/>
-      <c r="M15" s="325"/>
-      <c r="N15" s="325"/>
-      <c r="O15" s="325">
+      <c r="L15" s="322"/>
+      <c r="M15" s="322"/>
+      <c r="N15" s="322"/>
+      <c r="O15" s="322">
         <v>2</v>
       </c>
-      <c r="P15" s="325"/>
-      <c r="Q15" s="325"/>
-      <c r="R15" s="325">
-        <v>0</v>
-      </c>
-      <c r="S15" s="325">
-        <v>0</v>
-      </c>
-      <c r="T15" s="325"/>
-      <c r="U15" s="325">
-        <v>0</v>
-      </c>
-      <c r="V15" s="325">
-        <v>0</v>
-      </c>
-      <c r="W15" s="325">
-        <v>0</v>
-      </c>
-      <c r="X15" s="325">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="323">
+      <c r="P15" s="322"/>
+      <c r="Q15" s="322"/>
+      <c r="R15" s="322">
+        <v>0</v>
+      </c>
+      <c r="S15" s="322">
+        <v>0</v>
+      </c>
+      <c r="T15" s="322"/>
+      <c r="U15" s="322">
+        <v>0</v>
+      </c>
+      <c r="V15" s="322">
+        <v>0</v>
+      </c>
+      <c r="W15" s="322">
+        <v>0</v>
+      </c>
+      <c r="X15" s="322">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="320">
         <f>G15*(K15+L15)/26</f>
         <v>4027692.3076923075</v>
       </c>
-      <c r="Z15" s="323">
+      <c r="Z15" s="320">
         <f t="shared" ref="Z15:Z21" si="6">M15*G15/26</f>
         <v>0</v>
       </c>
-      <c r="AA15" s="323">
+      <c r="AA15" s="320">
         <f t="shared" ref="AA15:AA21" si="7">G15*N15/26</f>
         <v>0</v>
       </c>
-      <c r="AB15" s="323">
+      <c r="AB15" s="320">
         <f t="shared" ref="AB15:AB21" si="8">G15*O15/26</f>
         <v>732307.69230769225</v>
       </c>
-      <c r="AC15" s="323">
+      <c r="AC15" s="320">
         <f t="shared" ref="AC15:AC21" si="9">G15*P15*150%/26</f>
         <v>0</v>
       </c>
-      <c r="AD15" s="323">
+      <c r="AD15" s="320">
         <f t="shared" ref="AD15:AD21" si="10">G15*Q15/26*200%</f>
         <v>0</v>
       </c>
-      <c r="AE15" s="323">
+      <c r="AE15" s="320">
         <f t="shared" ref="AE15:AE21" si="11">G15*R15/26*300%</f>
         <v>0</v>
       </c>
-      <c r="AF15" s="323">
+      <c r="AF15" s="320">
         <f t="shared" ref="AF15:AF21" si="12">IF(F15="LT",0,(G15+H15)/26*S15*30%)</f>
         <v>0</v>
       </c>
-      <c r="AG15" s="323">
+      <c r="AG15" s="320">
         <f t="shared" ref="AG15:AG21" si="13">T15*G15/23/8</f>
         <v>0</v>
       </c>
-      <c r="AH15" s="323">
+      <c r="AH15" s="320">
         <f t="shared" ref="AH15:AH21" si="14">BZ15/26*U15</f>
         <v>0</v>
       </c>
-      <c r="AI15" s="323">
+      <c r="AI15" s="320">
         <f t="shared" ref="AI15:AI21" si="15">G15*V15/26</f>
         <v>0</v>
       </c>
-      <c r="AJ15" s="323"/>
-      <c r="AK15" s="323">
+      <c r="AJ15" s="320"/>
+      <c r="AK15" s="320">
         <f t="shared" ref="AK15:AK21" si="16">BX15*L15/26</f>
         <v>0</v>
       </c>
-      <c r="AL15" s="323"/>
-      <c r="AM15" s="323">
+      <c r="AL15" s="320"/>
+      <c r="AM15" s="320">
         <f t="shared" ref="AM15:AM21" si="17">X15*CB15</f>
         <v>0</v>
       </c>
-      <c r="AN15" s="323">
+      <c r="AN15" s="320">
         <f>H15/26*(K15+L15)</f>
         <v>0</v>
       </c>
-      <c r="AO15" s="323">
+      <c r="AO15" s="320">
         <f t="shared" ref="AO15:AO21" si="18">IF(F15="LN",I15*(K15+L15)/26+(H15+I15)*50%*M15/26+IF(F15="LT",BU15*O15/26-AB15,0)+MAX($G15*P15/26*150%,P15*$BU15/26)-AC15+MAX($G15*Q15/26*200%,Q15*$BU15/26)-AD15+MAX($G15*R15/26*300%,R15*$BU15/26)-AE15+BU15*S15/26-AF15+AH15-AG15,I15-I15*($CC$11-K15-L15)/26+(H15+I15)*50%*M15/26+IF(F15="LT",BU15*O15/26-AB15,0)+MAX($G15*P15/26*150%,P15*$BU15/26)-AC15+MAX($G15*Q15/26*200%,Q15*$BU15/26)-AD15+MAX($G15*R15/26*300%,R15*$BU15/26)-AE15+BU15*S15/26-AF15+AH15-AG15+(G15-G15*($CC$11-K15-L15)/26-Y15)+(H15-H15*($CC$11-K15-L15)/26-AN15))</f>
         <v>28932307.692307696</v>
       </c>
-      <c r="AP15" s="323"/>
-      <c r="AQ15" s="323"/>
+      <c r="AP15" s="320"/>
+      <c r="AQ15" s="320"/>
       <c r="AR15" s="184">
         <v>1000000</v>
       </c>
-      <c r="AS15" s="323"/>
-      <c r="AT15" s="323"/>
-      <c r="AU15" s="323"/>
-      <c r="AV15" s="323">
+      <c r="AS15" s="320"/>
+      <c r="AT15" s="320"/>
+      <c r="AU15" s="320"/>
+      <c r="AV15" s="320">
         <f t="shared" ref="AV15:AV21" si="19">Y15+Z15+AA15+AB15+AC15+AD15+AE15+AF15+AG15+AI15+AJ15+AK15+AL15+AM15+AN15+AO15+AP15-AQ15+AR15+AS15+AT15+AU15</f>
         <v>34692307.692307696</v>
       </c>
-      <c r="AW15" s="323"/>
-      <c r="AX15" s="323" t="s">
+      <c r="AW15" s="320"/>
+      <c r="AX15" s="320" t="s">
         <v>101</v>
       </c>
-      <c r="AY15" s="326">
+      <c r="AY15" s="323">
         <f t="shared" ref="AY15:BA21" si="20">ROUND(IF($AX15="x",($G15+$H15)*AY$11,0),0)</f>
         <v>761600</v>
       </c>
-      <c r="AZ15" s="326">
+      <c r="AZ15" s="323">
         <f t="shared" si="20"/>
         <v>142800</v>
       </c>
-      <c r="BA15" s="326">
+      <c r="BA15" s="323">
         <f t="shared" si="20"/>
         <v>95200</v>
       </c>
-      <c r="BB15" s="326">
+      <c r="BB15" s="323">
         <f t="shared" ref="BB15:BB21" si="21">SUM(AY15:BA15)</f>
         <v>999600</v>
       </c>
-      <c r="BC15" s="326"/>
-      <c r="BD15" s="326"/>
-      <c r="BE15" s="326">
+      <c r="BC15" s="323"/>
+      <c r="BD15" s="323"/>
+      <c r="BE15" s="323">
         <f t="shared" ref="BE15:BE21" si="22">IF(G15*1%&gt;=234000,234000,G15*1%)</f>
         <v>95200</v>
       </c>
-      <c r="BF15" s="326">
+      <c r="BF15" s="323">
         <f>AM15+IF(AR15&gt;=730000,730000,AR15)+IF(((AV15-AM15-IF(AR15&gt;=730000,730000,AR15)-AS15)*15%-AS15)&gt;0,((AV15-AM15-IF(AR15&gt;=730000,730000,AR15)-AS15)*15%-AS15),0)</f>
         <v>5824346.153846154</v>
       </c>
-      <c r="BG15" s="326">
+      <c r="BG15" s="323">
         <f t="shared" ref="BG15:BG21" si="23">AV15-BF15+AW15</f>
         <v>28867961.538461544</v>
       </c>
-      <c r="BH15" s="326">
+      <c r="BH15" s="323">
         <v>3</v>
       </c>
-      <c r="BI15" s="326">
+      <c r="BI15" s="323">
         <f t="shared" ref="BI15:BI21" si="24">BG15-BB15-BC15+BD15-BH15*4400000-IF(E15="CT",11000000,0)</f>
         <v>14668361.538461544</v>
       </c>
-      <c r="BJ15" s="327">
+      <c r="BJ15" s="324">
         <f t="shared" ref="BJ15:BJ21" si="25">IF(BI15&gt;0,ROUND(IF(BI15&gt;=80000000,BI15*35%-9850000,IF(BI15&gt;=52000000,BI15*30%-5850000,IF(BI15&gt;=32000000,BI15*25%-3250000,IF(BI15&gt;=18000000,BI15*20%-1650000,IF(BI15&gt;=10000000,BI15*15%-750000,IF(BI15&gt;5000000,BI15*10%-250000,BI15*5%)))))),0),0)</f>
         <v>1450254</v>
       </c>
-      <c r="BK15" s="326"/>
-      <c r="BL15" s="326"/>
-      <c r="BM15" s="326">
-        <v>0</v>
-      </c>
-      <c r="BN15" s="326"/>
-      <c r="BO15" s="326"/>
-      <c r="BP15" s="326"/>
-      <c r="BQ15" s="326"/>
-      <c r="BR15" s="326"/>
-      <c r="BS15" s="326" t="str">
+      <c r="BK15" s="323"/>
+      <c r="BL15" s="323"/>
+      <c r="BM15" s="323">
+        <v>0</v>
+      </c>
+      <c r="BN15" s="323"/>
+      <c r="BO15" s="323"/>
+      <c r="BP15" s="323"/>
+      <c r="BQ15" s="323"/>
+      <c r="BR15" s="323"/>
+      <c r="BS15" s="323" t="str">
         <f t="shared" ref="BS15:BS21" si="26">IF(AV15&gt;=11000000,"80%","100%")</f>
         <v>80%</v>
       </c>
-      <c r="BT15" s="326">
+      <c r="BT15" s="323">
         <f>AV15*BS15-BN15-BK15-BP15-BO15</f>
         <v>27753846.15384616</v>
       </c>
-      <c r="BU15" s="328">
+      <c r="BU15" s="325">
         <v>60000000</v>
       </c>
       <c r="BV15" s="188">
@@ -17165,21 +17269,21 @@
       <c r="BX15" s="188">
         <v>200000</v>
       </c>
-      <c r="BY15" s="327">
+      <c r="BY15" s="324">
         <f t="shared" ref="BY15:BY21" si="27">+BU15*5%</f>
         <v>3000000</v>
       </c>
-      <c r="BZ15" s="327">
+      <c r="BZ15" s="324">
         <f t="shared" ref="BZ15:BZ21" si="28">SUM(BU15:BY15)</f>
         <v>63200000</v>
       </c>
-      <c r="CA15" s="327" t="s">
+      <c r="CA15" s="324" t="s">
         <v>122</v>
       </c>
-      <c r="CB15" s="327"/>
-      <c r="CC15" s="287"/>
-      <c r="CD15" s="288"/>
-      <c r="CE15" s="288"/>
+      <c r="CB15" s="324"/>
+      <c r="CC15" s="284"/>
+      <c r="CD15" s="285"/>
+      <c r="CE15" s="285"/>
       <c r="CF15" s="252"/>
       <c r="CG15" s="252"/>
     </row>
@@ -17213,7 +17317,7 @@
         <f t="shared" si="5"/>
         <v>43520000</v>
       </c>
-      <c r="J16" s="286">
+      <c r="J16" s="283">
         <v>1</v>
       </c>
       <c r="K16" s="250">
@@ -17407,9 +17511,9 @@
         <v>114</v>
       </c>
       <c r="CB16" s="243"/>
-      <c r="CC16" s="287"/>
-      <c r="CD16" s="288"/>
-      <c r="CE16" s="288"/>
+      <c r="CC16" s="284"/>
+      <c r="CD16" s="285"/>
+      <c r="CE16" s="285"/>
       <c r="CF16" s="252"/>
       <c r="CG16" s="252"/>
     </row>
@@ -17443,7 +17547,7 @@
         <f t="shared" si="5"/>
         <v>33880000</v>
       </c>
-      <c r="J17" s="286">
+      <c r="J17" s="283">
         <v>1</v>
       </c>
       <c r="K17" s="250">
@@ -17635,9 +17739,9 @@
         <v>118</v>
       </c>
       <c r="CB17" s="243"/>
-      <c r="CC17" s="287"/>
-      <c r="CD17" s="288"/>
-      <c r="CE17" s="288"/>
+      <c r="CC17" s="284"/>
+      <c r="CD17" s="285"/>
+      <c r="CE17" s="285"/>
       <c r="CF17" s="252"/>
       <c r="CG17" s="252"/>
     </row>
@@ -17671,7 +17775,7 @@
         <f t="shared" si="5"/>
         <v>19160000</v>
       </c>
-      <c r="J18" s="286">
+      <c r="J18" s="283">
         <v>1</v>
       </c>
       <c r="K18" s="250">
@@ -17865,9 +17969,9 @@
         <v>114</v>
       </c>
       <c r="CB18" s="243"/>
-      <c r="CC18" s="287"/>
-      <c r="CD18" s="288"/>
-      <c r="CE18" s="288"/>
+      <c r="CC18" s="284"/>
+      <c r="CD18" s="285"/>
+      <c r="CE18" s="285"/>
       <c r="CF18" s="252"/>
       <c r="CG18" s="252"/>
     </row>
@@ -17901,7 +18005,7 @@
         <f t="shared" si="5"/>
         <v>6400000</v>
       </c>
-      <c r="J19" s="286">
+      <c r="J19" s="283">
         <v>1</v>
       </c>
       <c r="K19" s="250">
@@ -18093,9 +18197,9 @@
         <v>118</v>
       </c>
       <c r="CB19" s="243"/>
-      <c r="CC19" s="287"/>
-      <c r="CD19" s="288"/>
-      <c r="CE19" s="288"/>
+      <c r="CC19" s="284"/>
+      <c r="CD19" s="285"/>
+      <c r="CE19" s="285"/>
       <c r="CF19" s="252"/>
       <c r="CG19" s="252"/>
     </row>
@@ -18129,7 +18233,7 @@
         <f t="shared" si="5"/>
         <v>17810000</v>
       </c>
-      <c r="J20" s="286">
+      <c r="J20" s="283">
         <v>1</v>
       </c>
       <c r="K20" s="250">
@@ -18323,9 +18427,9 @@
         <v>114</v>
       </c>
       <c r="CB20" s="243"/>
-      <c r="CC20" s="287"/>
-      <c r="CD20" s="288"/>
-      <c r="CE20" s="288"/>
+      <c r="CC20" s="284"/>
+      <c r="CD20" s="285"/>
+      <c r="CE20" s="285"/>
       <c r="CF20" s="252"/>
       <c r="CG20" s="252"/>
     </row>
@@ -18359,7 +18463,7 @@
         <f t="shared" si="5"/>
         <v>11210000</v>
       </c>
-      <c r="J21" s="286">
+      <c r="J21" s="283">
         <v>1</v>
       </c>
       <c r="K21" s="250">
@@ -18551,156 +18655,220 @@
         <v>118</v>
       </c>
       <c r="CB21" s="243"/>
-      <c r="CC21" s="287"/>
-      <c r="CD21" s="288"/>
-      <c r="CE21" s="288"/>
+      <c r="CC21" s="284"/>
+      <c r="CD21" s="285"/>
+      <c r="CE21" s="285"/>
       <c r="CF21" s="252"/>
       <c r="CG21" s="252"/>
     </row>
-    <row r="22" spans="1:85" s="289" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B22" s="290"/>
-      <c r="I22" s="291"/>
-      <c r="J22" s="291"/>
-      <c r="K22" s="292"/>
-      <c r="L22" s="292"/>
-      <c r="M22" s="292"/>
-      <c r="N22" s="292"/>
-      <c r="O22" s="292"/>
-      <c r="P22" s="292"/>
-      <c r="Q22" s="292"/>
-      <c r="R22" s="292"/>
-      <c r="S22" s="292"/>
-      <c r="T22" s="292"/>
-      <c r="U22" s="293"/>
-      <c r="V22" s="293"/>
-      <c r="W22" s="294"/>
-      <c r="X22" s="294"/>
-      <c r="AC22" s="295"/>
-      <c r="BJ22" s="296"/>
-      <c r="BN22" s="296"/>
-      <c r="BO22" s="296"/>
-      <c r="BP22" s="296"/>
-      <c r="BQ22" s="296"/>
-      <c r="BR22" s="296"/>
-      <c r="BS22" s="296"/>
-      <c r="BT22" s="296"/>
-      <c r="BU22" s="297"/>
-      <c r="BV22" s="297"/>
-      <c r="BW22" s="297"/>
-      <c r="BX22" s="297"/>
-      <c r="BY22" s="297"/>
-      <c r="CD22" s="298"/>
+    <row r="22" spans="1:85" s="286" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B22" s="287"/>
+      <c r="I22" s="288"/>
+      <c r="J22" s="288"/>
+      <c r="K22" s="289"/>
+      <c r="L22" s="289"/>
+      <c r="M22" s="289"/>
+      <c r="N22" s="289"/>
+      <c r="O22" s="289"/>
+      <c r="P22" s="289"/>
+      <c r="Q22" s="289"/>
+      <c r="R22" s="289"/>
+      <c r="S22" s="289"/>
+      <c r="T22" s="289"/>
+      <c r="U22" s="290"/>
+      <c r="V22" s="290"/>
+      <c r="W22" s="291"/>
+      <c r="X22" s="291"/>
+      <c r="AC22" s="292"/>
+      <c r="BJ22" s="293"/>
+      <c r="BN22" s="293"/>
+      <c r="BO22" s="293"/>
+      <c r="BP22" s="293"/>
+      <c r="BQ22" s="293"/>
+      <c r="BR22" s="293"/>
+      <c r="BS22" s="293"/>
+      <c r="BT22" s="293"/>
+      <c r="BU22" s="294"/>
+      <c r="BV22" s="294"/>
+      <c r="BW22" s="294"/>
+      <c r="BX22" s="294"/>
+      <c r="BY22" s="294"/>
+      <c r="CD22" s="295"/>
     </row>
-    <row r="23" spans="1:85" s="299" customFormat="1" ht="21" customHeight="1">
-      <c r="B23" s="300"/>
-      <c r="C23" s="300"/>
-      <c r="D23" s="300"/>
-      <c r="E23" s="300"/>
-      <c r="F23" s="300"/>
-      <c r="G23" s="300"/>
-      <c r="H23" s="300"/>
-      <c r="I23" s="300"/>
-      <c r="J23" s="301"/>
-      <c r="K23" s="302"/>
-      <c r="L23" s="302"/>
-      <c r="M23" s="302"/>
-      <c r="N23" s="302"/>
-      <c r="O23" s="302"/>
-      <c r="P23" s="302"/>
-      <c r="Q23" s="302"/>
-      <c r="U23" s="303"/>
-      <c r="V23" s="302"/>
-      <c r="W23" s="300"/>
-      <c r="X23" s="300"/>
-      <c r="Y23" s="300"/>
-      <c r="Z23" s="300"/>
-      <c r="AA23" s="300"/>
-      <c r="AB23" s="300"/>
-      <c r="AC23" s="300"/>
-      <c r="AK23" s="300"/>
-      <c r="AM23" s="300"/>
-      <c r="AN23" s="300"/>
-      <c r="AO23" s="300"/>
-      <c r="AP23" s="300"/>
-      <c r="AQ23" s="300"/>
-      <c r="AR23" s="300"/>
-      <c r="AS23" s="300"/>
-      <c r="AT23" s="300"/>
-      <c r="AU23" s="300"/>
-      <c r="AV23" s="300"/>
-      <c r="AW23" s="300"/>
-      <c r="AX23" s="300"/>
-      <c r="BC23" s="304"/>
-      <c r="BD23" s="304"/>
-      <c r="BJ23" s="300"/>
-      <c r="BL23" s="300"/>
-      <c r="BM23" s="300"/>
-      <c r="BN23" s="300" t="s">
+    <row r="23" spans="1:85" s="296" customFormat="1" ht="21" customHeight="1">
+      <c r="B23" s="297"/>
+      <c r="C23" s="297"/>
+      <c r="D23" s="297"/>
+      <c r="E23" s="297"/>
+      <c r="F23" s="297"/>
+      <c r="G23" s="297"/>
+      <c r="H23" s="297"/>
+      <c r="I23" s="297"/>
+      <c r="J23" s="298"/>
+      <c r="K23" s="299"/>
+      <c r="L23" s="299"/>
+      <c r="M23" s="299"/>
+      <c r="N23" s="299"/>
+      <c r="O23" s="299"/>
+      <c r="P23" s="299"/>
+      <c r="Q23" s="299"/>
+      <c r="U23" s="300"/>
+      <c r="V23" s="299"/>
+      <c r="W23" s="297"/>
+      <c r="X23" s="297"/>
+      <c r="Y23" s="297"/>
+      <c r="Z23" s="297"/>
+      <c r="AA23" s="297"/>
+      <c r="AB23" s="297"/>
+      <c r="AC23" s="297"/>
+      <c r="AK23" s="297"/>
+      <c r="AM23" s="297"/>
+      <c r="AN23" s="297"/>
+      <c r="AO23" s="297"/>
+      <c r="AP23" s="297"/>
+      <c r="AQ23" s="297"/>
+      <c r="AR23" s="297"/>
+      <c r="AS23" s="297"/>
+      <c r="AT23" s="297"/>
+      <c r="AU23" s="297"/>
+      <c r="AV23" s="297"/>
+      <c r="AW23" s="297"/>
+      <c r="AX23" s="297"/>
+      <c r="BC23" s="301"/>
+      <c r="BD23" s="301"/>
+      <c r="BJ23" s="297"/>
+      <c r="BL23" s="297"/>
+      <c r="BM23" s="297"/>
+      <c r="BN23" s="297" t="s">
         <v>119</v>
       </c>
-      <c r="BO23" s="300"/>
-      <c r="BP23" s="300"/>
-      <c r="BQ23" s="300"/>
-      <c r="BR23" s="300"/>
-      <c r="BS23" s="300"/>
-      <c r="BT23" s="300"/>
-      <c r="BU23" s="305"/>
-      <c r="BV23" s="305"/>
-      <c r="BW23" s="305"/>
-      <c r="BX23" s="305"/>
-      <c r="BY23" s="305"/>
+      <c r="BO23" s="297"/>
+      <c r="BP23" s="297"/>
+      <c r="BQ23" s="297"/>
+      <c r="BR23" s="297"/>
+      <c r="BS23" s="297"/>
+      <c r="BT23" s="297"/>
+      <c r="BU23" s="302"/>
+      <c r="BV23" s="302"/>
+      <c r="BW23" s="302"/>
+      <c r="BX23" s="302"/>
+      <c r="BY23" s="302"/>
     </row>
-    <row r="24" spans="1:85" s="299" customFormat="1" ht="18" customHeight="1">
-      <c r="B24" s="306"/>
-      <c r="I24" s="301"/>
-      <c r="J24" s="301"/>
-      <c r="K24" s="303"/>
-      <c r="L24" s="303"/>
-      <c r="M24" s="303"/>
-      <c r="N24" s="303"/>
-      <c r="O24" s="303"/>
-      <c r="P24" s="303"/>
-      <c r="Q24" s="303"/>
-      <c r="R24" s="302"/>
-      <c r="U24" s="303"/>
-      <c r="V24" s="303"/>
-      <c r="W24" s="307"/>
-      <c r="X24" s="307"/>
-      <c r="AN24" s="305"/>
-      <c r="AV24" s="300"/>
-      <c r="AW24" s="300"/>
-      <c r="AX24" s="300"/>
-      <c r="AY24" s="305"/>
-      <c r="AZ24" s="305"/>
-      <c r="BA24" s="305"/>
-      <c r="BB24" s="305"/>
-      <c r="BL24" s="300"/>
-      <c r="BM24" s="304"/>
-      <c r="BU24" s="305"/>
-      <c r="BV24" s="305"/>
-      <c r="BW24" s="305"/>
-      <c r="BX24" s="305"/>
-      <c r="BY24" s="305"/>
-      <c r="CD24" s="308"/>
+    <row r="24" spans="1:85" s="296" customFormat="1" ht="18" customHeight="1">
+      <c r="B24" s="303"/>
+      <c r="I24" s="298"/>
+      <c r="J24" s="298"/>
+      <c r="K24" s="300"/>
+      <c r="L24" s="300"/>
+      <c r="M24" s="300"/>
+      <c r="N24" s="300"/>
+      <c r="O24" s="300"/>
+      <c r="P24" s="300"/>
+      <c r="Q24" s="300"/>
+      <c r="R24" s="299"/>
+      <c r="U24" s="300"/>
+      <c r="V24" s="300"/>
+      <c r="W24" s="304"/>
+      <c r="X24" s="304"/>
+      <c r="AN24" s="302"/>
+      <c r="AV24" s="297"/>
+      <c r="AW24" s="297"/>
+      <c r="AX24" s="297"/>
+      <c r="AY24" s="302"/>
+      <c r="AZ24" s="302"/>
+      <c r="BA24" s="302"/>
+      <c r="BB24" s="302"/>
+      <c r="BL24" s="297"/>
+      <c r="BM24" s="301"/>
+      <c r="BU24" s="302"/>
+      <c r="BV24" s="302"/>
+      <c r="BW24" s="302"/>
+      <c r="BX24" s="302"/>
+      <c r="BY24" s="302"/>
+      <c r="CD24" s="305"/>
     </row>
     <row r="25" spans="1:85" ht="15" customHeight="1">
-      <c r="D25" s="312" t="s">
+      <c r="D25" s="309" t="s">
         <v>152</v>
       </c>
-      <c r="I25" s="313"/>
+      <c r="I25" s="310"/>
       <c r="X25" s="258"/>
       <c r="BX25" s="258" t="s">
         <v>147</v>
       </c>
-      <c r="CD25" s="317"/>
+      <c r="CD25" s="314"/>
     </row>
     <row r="26" spans="1:85" ht="73.5" customHeight="1">
       <c r="J26" s="257"/>
       <c r="X26" s="258"/>
     </row>
   </sheetData>
-  <autoFilter ref="A12:CG21" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <mergeCells count="81">
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="AS8:AS11"/>
+    <mergeCell ref="K8:X8"/>
+    <mergeCell ref="BC10:BC11"/>
+    <mergeCell ref="BE10:BE11"/>
+    <mergeCell ref="T9:T11"/>
+    <mergeCell ref="P9:P11"/>
+    <mergeCell ref="AB9:AB11"/>
+    <mergeCell ref="AY8:BP8"/>
+    <mergeCell ref="AF9:AF11"/>
+    <mergeCell ref="AH9:AH11"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="N9:N11"/>
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="AQ8:AQ11"/>
+    <mergeCell ref="U9:U11"/>
+    <mergeCell ref="D8:D11"/>
+    <mergeCell ref="BF10:BF11"/>
+    <mergeCell ref="BO10:BO11"/>
+    <mergeCell ref="Q9:Q11"/>
+    <mergeCell ref="S9:S11"/>
+    <mergeCell ref="BL10:BL11"/>
+    <mergeCell ref="AC9:AC11"/>
+    <mergeCell ref="AR8:AR11"/>
+    <mergeCell ref="I8:I11"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="AP8:AP11"/>
+    <mergeCell ref="R9:R11"/>
+    <mergeCell ref="BU3:BZ6"/>
+    <mergeCell ref="AU8:AU11"/>
+    <mergeCell ref="BS8:BS11"/>
+    <mergeCell ref="BK9:BP9"/>
+    <mergeCell ref="BV8:BY10"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="AV8:AV11"/>
+    <mergeCell ref="BR9:BR11"/>
+    <mergeCell ref="BM10:BM11"/>
+    <mergeCell ref="BN10:BN11"/>
+    <mergeCell ref="BP10:BP11"/>
+    <mergeCell ref="BU8:BU11"/>
+    <mergeCell ref="BQ8:BR8"/>
+    <mergeCell ref="BQ9:BQ11"/>
+    <mergeCell ref="CA8:CA11"/>
+    <mergeCell ref="AW8:AW11"/>
+    <mergeCell ref="A3:BT3"/>
+    <mergeCell ref="AE9:AE11"/>
+    <mergeCell ref="AO9:AO11"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BD10:BD11"/>
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="M9:M11"/>
+    <mergeCell ref="O9:O11"/>
+    <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="AY9:BJ9"/>
+    <mergeCell ref="BT8:BT11"/>
+    <mergeCell ref="E8:E11"/>
+    <mergeCell ref="G8:G11"/>
+    <mergeCell ref="AG9:AG11"/>
+    <mergeCell ref="Z9:Z11"/>
+    <mergeCell ref="AD9:AD11"/>
+    <mergeCell ref="BG10:BG11"/>
+    <mergeCell ref="V9:W10"/>
+    <mergeCell ref="X9:X11"/>
+    <mergeCell ref="AI9:AI11"/>
     <mergeCell ref="H8:H11"/>
     <mergeCell ref="J8:J11"/>
     <mergeCell ref="AT8:AT11"/>
@@ -18717,91 +18885,31 @@
     <mergeCell ref="AJ9:AJ11"/>
     <mergeCell ref="AL9:AL11"/>
     <mergeCell ref="AN9:AN11"/>
-    <mergeCell ref="AG9:AG11"/>
-    <mergeCell ref="Z9:Z11"/>
-    <mergeCell ref="AD9:AD11"/>
-    <mergeCell ref="BG10:BG11"/>
-    <mergeCell ref="V9:W10"/>
-    <mergeCell ref="X9:X11"/>
-    <mergeCell ref="CA8:CA11"/>
-    <mergeCell ref="AW8:AW11"/>
-    <mergeCell ref="A3:BT3"/>
-    <mergeCell ref="AE9:AE11"/>
-    <mergeCell ref="AO9:AO11"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="M9:M11"/>
-    <mergeCell ref="O9:O11"/>
-    <mergeCell ref="BH10:BH11"/>
-    <mergeCell ref="AY9:BJ9"/>
-    <mergeCell ref="BT8:BT11"/>
-    <mergeCell ref="E8:E11"/>
-    <mergeCell ref="G8:G11"/>
-    <mergeCell ref="BU3:BZ6"/>
-    <mergeCell ref="AU8:AU11"/>
-    <mergeCell ref="BS8:BS11"/>
-    <mergeCell ref="BK9:BP9"/>
-    <mergeCell ref="BV8:BY10"/>
-    <mergeCell ref="BI10:BI11"/>
-    <mergeCell ref="AV8:AV11"/>
-    <mergeCell ref="BR9:BR11"/>
-    <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="BN10:BN11"/>
-    <mergeCell ref="BP10:BP11"/>
-    <mergeCell ref="BU8:BU11"/>
-    <mergeCell ref="AI9:AI11"/>
-    <mergeCell ref="BQ8:BR8"/>
-    <mergeCell ref="D8:D11"/>
-    <mergeCell ref="BF10:BF11"/>
-    <mergeCell ref="BO10:BO11"/>
-    <mergeCell ref="Q9:Q11"/>
-    <mergeCell ref="S9:S11"/>
-    <mergeCell ref="BL10:BL11"/>
-    <mergeCell ref="AC9:AC11"/>
-    <mergeCell ref="BQ9:BQ11"/>
-    <mergeCell ref="AR8:AR11"/>
-    <mergeCell ref="I8:I11"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="AP8:AP11"/>
-    <mergeCell ref="R9:R11"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="AS8:AS11"/>
-    <mergeCell ref="K8:X8"/>
-    <mergeCell ref="BC10:BC11"/>
-    <mergeCell ref="BE10:BE11"/>
-    <mergeCell ref="T9:T11"/>
-    <mergeCell ref="P9:P11"/>
-    <mergeCell ref="AB9:AB11"/>
-    <mergeCell ref="AY8:BP8"/>
-    <mergeCell ref="AF9:AF11"/>
-    <mergeCell ref="AH9:AH11"/>
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="N9:N11"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="AQ8:AQ11"/>
-    <mergeCell ref="U9:U11"/>
   </mergeCells>
-  <conditionalFormatting sqref="B1:B7 B22:B1048576 B12:BT12">
-    <cfRule type="duplicateValues" dxfId="14" priority="98"/>
+  <conditionalFormatting sqref="B1:B6 B22:B1048576 B12:BT12">
+    <cfRule type="duplicateValues" dxfId="17" priority="101"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B7 B22:B1048576 D13:F13 J13:BI13 BK13:CB13 B12:CB12">
-    <cfRule type="duplicateValues" dxfId="13" priority="101"/>
+  <conditionalFormatting sqref="B1:B6 B22:B1048576 D13:F13 J13:BI13 BK13:CB13 B12:CB12">
+    <cfRule type="duplicateValues" dxfId="16" priority="104"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8:B11">
+    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:B21">
-    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="BJ13">
-    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B8:B11">
+  <conditionalFormatting sqref="B7">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B8:B11">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="B7">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.21" bottom="0.17" header="0.196850393700787" footer="0.196850393700787"/>
@@ -19017,87 +19125,87 @@
       <c r="CD2" s="41"/>
     </row>
     <row r="3" spans="1:87" s="43" customFormat="1" ht="11" outlineLevel="1">
-      <c r="A3" s="430"/>
-      <c r="B3" s="418"/>
-      <c r="C3" s="418"/>
-      <c r="D3" s="418"/>
-      <c r="E3" s="418"/>
-      <c r="F3" s="418"/>
-      <c r="G3" s="418"/>
-      <c r="H3" s="418"/>
-      <c r="I3" s="418"/>
-      <c r="J3" s="418"/>
-      <c r="K3" s="418"/>
-      <c r="L3" s="418"/>
-      <c r="M3" s="418"/>
-      <c r="N3" s="418"/>
-      <c r="O3" s="418"/>
-      <c r="P3" s="418"/>
-      <c r="Q3" s="418"/>
-      <c r="R3" s="418"/>
-      <c r="S3" s="418"/>
-      <c r="T3" s="418"/>
-      <c r="U3" s="418"/>
-      <c r="V3" s="418"/>
-      <c r="W3" s="418"/>
-      <c r="X3" s="418"/>
-      <c r="Y3" s="418"/>
-      <c r="Z3" s="418"/>
-      <c r="AA3" s="418"/>
-      <c r="AB3" s="418"/>
-      <c r="AC3" s="418"/>
-      <c r="AD3" s="418"/>
-      <c r="AE3" s="418"/>
-      <c r="AF3" s="418"/>
-      <c r="AG3" s="418"/>
-      <c r="AH3" s="418"/>
-      <c r="AI3" s="418"/>
-      <c r="AJ3" s="418"/>
-      <c r="AK3" s="418"/>
-      <c r="AL3" s="418"/>
-      <c r="AM3" s="418"/>
-      <c r="AN3" s="418"/>
-      <c r="AO3" s="418"/>
-      <c r="AP3" s="418"/>
-      <c r="AQ3" s="418"/>
-      <c r="AR3" s="418"/>
-      <c r="AS3" s="418"/>
-      <c r="AT3" s="418"/>
-      <c r="AU3" s="418"/>
-      <c r="AV3" s="418"/>
-      <c r="AW3" s="418"/>
-      <c r="AX3" s="418"/>
-      <c r="AY3" s="418"/>
-      <c r="AZ3" s="418"/>
-      <c r="BA3" s="418"/>
-      <c r="BB3" s="418"/>
-      <c r="BC3" s="418"/>
-      <c r="BD3" s="418"/>
-      <c r="BE3" s="418"/>
-      <c r="BF3" s="418"/>
-      <c r="BG3" s="418"/>
-      <c r="BH3" s="418"/>
-      <c r="BI3" s="418"/>
-      <c r="BJ3" s="418"/>
-      <c r="BK3" s="418"/>
-      <c r="BL3" s="418"/>
-      <c r="BM3" s="418"/>
-      <c r="BN3" s="418"/>
-      <c r="BO3" s="418"/>
-      <c r="BP3" s="418"/>
-      <c r="BQ3" s="418"/>
-      <c r="BR3" s="418"/>
-      <c r="BS3" s="418"/>
-      <c r="BT3" s="418"/>
-      <c r="BU3" s="418"/>
-      <c r="BW3" s="417" t="s">
+      <c r="A3" s="425"/>
+      <c r="B3" s="416"/>
+      <c r="C3" s="416"/>
+      <c r="D3" s="416"/>
+      <c r="E3" s="416"/>
+      <c r="F3" s="416"/>
+      <c r="G3" s="416"/>
+      <c r="H3" s="416"/>
+      <c r="I3" s="416"/>
+      <c r="J3" s="416"/>
+      <c r="K3" s="416"/>
+      <c r="L3" s="416"/>
+      <c r="M3" s="416"/>
+      <c r="N3" s="416"/>
+      <c r="O3" s="416"/>
+      <c r="P3" s="416"/>
+      <c r="Q3" s="416"/>
+      <c r="R3" s="416"/>
+      <c r="S3" s="416"/>
+      <c r="T3" s="416"/>
+      <c r="U3" s="416"/>
+      <c r="V3" s="416"/>
+      <c r="W3" s="416"/>
+      <c r="X3" s="416"/>
+      <c r="Y3" s="416"/>
+      <c r="Z3" s="416"/>
+      <c r="AA3" s="416"/>
+      <c r="AB3" s="416"/>
+      <c r="AC3" s="416"/>
+      <c r="AD3" s="416"/>
+      <c r="AE3" s="416"/>
+      <c r="AF3" s="416"/>
+      <c r="AG3" s="416"/>
+      <c r="AH3" s="416"/>
+      <c r="AI3" s="416"/>
+      <c r="AJ3" s="416"/>
+      <c r="AK3" s="416"/>
+      <c r="AL3" s="416"/>
+      <c r="AM3" s="416"/>
+      <c r="AN3" s="416"/>
+      <c r="AO3" s="416"/>
+      <c r="AP3" s="416"/>
+      <c r="AQ3" s="416"/>
+      <c r="AR3" s="416"/>
+      <c r="AS3" s="416"/>
+      <c r="AT3" s="416"/>
+      <c r="AU3" s="416"/>
+      <c r="AV3" s="416"/>
+      <c r="AW3" s="416"/>
+      <c r="AX3" s="416"/>
+      <c r="AY3" s="416"/>
+      <c r="AZ3" s="416"/>
+      <c r="BA3" s="416"/>
+      <c r="BB3" s="416"/>
+      <c r="BC3" s="416"/>
+      <c r="BD3" s="416"/>
+      <c r="BE3" s="416"/>
+      <c r="BF3" s="416"/>
+      <c r="BG3" s="416"/>
+      <c r="BH3" s="416"/>
+      <c r="BI3" s="416"/>
+      <c r="BJ3" s="416"/>
+      <c r="BK3" s="416"/>
+      <c r="BL3" s="416"/>
+      <c r="BM3" s="416"/>
+      <c r="BN3" s="416"/>
+      <c r="BO3" s="416"/>
+      <c r="BP3" s="416"/>
+      <c r="BQ3" s="416"/>
+      <c r="BR3" s="416"/>
+      <c r="BS3" s="416"/>
+      <c r="BT3" s="416"/>
+      <c r="BU3" s="416"/>
+      <c r="BW3" s="415" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="418"/>
-      <c r="BY3" s="418"/>
-      <c r="BZ3" s="418"/>
-      <c r="CA3" s="418"/>
-      <c r="CB3" s="418"/>
+      <c r="BX3" s="416"/>
+      <c r="BY3" s="416"/>
+      <c r="BZ3" s="416"/>
+      <c r="CA3" s="416"/>
+      <c r="CB3" s="416"/>
       <c r="CC3" s="42"/>
       <c r="CD3" s="42"/>
       <c r="CE3" s="43" t="s">
@@ -19180,366 +19288,366 @@
       <c r="BS4" s="44"/>
       <c r="BT4" s="44"/>
       <c r="BU4" s="44"/>
-      <c r="BW4" s="418"/>
-      <c r="BX4" s="418"/>
-      <c r="BY4" s="418"/>
-      <c r="BZ4" s="418"/>
-      <c r="CA4" s="418"/>
-      <c r="CB4" s="418"/>
+      <c r="BW4" s="416"/>
+      <c r="BX4" s="416"/>
+      <c r="BY4" s="416"/>
+      <c r="BZ4" s="416"/>
+      <c r="CA4" s="416"/>
+      <c r="CB4" s="416"/>
       <c r="CC4" s="42"/>
       <c r="CD4" s="42"/>
     </row>
     <row r="5" spans="1:87" s="45" customFormat="1">
-      <c r="A5" s="405" t="s">
+      <c r="A5" s="428" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="416" t="s">
+      <c r="B5" s="427" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="404" t="s">
+      <c r="C5" s="401" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="411" t="s">
+      <c r="D5" s="426" t="s">
         <v>141</v>
       </c>
-      <c r="E5" s="411" t="s">
+      <c r="E5" s="426" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="441" t="s">
+      <c r="F5" s="513" t="s">
         <v>142</v>
       </c>
-      <c r="G5" s="404" t="s">
+      <c r="G5" s="401" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="334" t="s">
+      <c r="H5" s="352" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="334" t="s">
+      <c r="I5" s="352" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="404" t="s">
+      <c r="J5" s="401" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="409" t="s">
+      <c r="K5" s="430" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="401"/>
-      <c r="M5" s="401"/>
-      <c r="N5" s="401"/>
-      <c r="O5" s="401"/>
-      <c r="P5" s="401"/>
-      <c r="Q5" s="401"/>
-      <c r="R5" s="401"/>
-      <c r="S5" s="401"/>
-      <c r="T5" s="401"/>
-      <c r="U5" s="401"/>
-      <c r="V5" s="401"/>
-      <c r="W5" s="401"/>
-      <c r="X5" s="401"/>
-      <c r="Y5" s="404" t="s">
+      <c r="L5" s="412"/>
+      <c r="M5" s="412"/>
+      <c r="N5" s="412"/>
+      <c r="O5" s="412"/>
+      <c r="P5" s="412"/>
+      <c r="Q5" s="412"/>
+      <c r="R5" s="412"/>
+      <c r="S5" s="412"/>
+      <c r="T5" s="412"/>
+      <c r="U5" s="412"/>
+      <c r="V5" s="412"/>
+      <c r="W5" s="412"/>
+      <c r="X5" s="412"/>
+      <c r="Y5" s="401" t="s">
         <v>15</v>
       </c>
-      <c r="Z5" s="401"/>
-      <c r="AA5" s="401"/>
-      <c r="AB5" s="401"/>
-      <c r="AC5" s="401"/>
-      <c r="AD5" s="401"/>
-      <c r="AE5" s="401"/>
-      <c r="AF5" s="401"/>
-      <c r="AG5" s="401"/>
-      <c r="AH5" s="401"/>
-      <c r="AI5" s="401"/>
-      <c r="AJ5" s="401"/>
-      <c r="AK5" s="401"/>
-      <c r="AL5" s="401"/>
-      <c r="AM5" s="401"/>
-      <c r="AN5" s="401"/>
-      <c r="AO5" s="402"/>
-      <c r="AP5" s="404" t="s">
+      <c r="Z5" s="412"/>
+      <c r="AA5" s="412"/>
+      <c r="AB5" s="412"/>
+      <c r="AC5" s="412"/>
+      <c r="AD5" s="412"/>
+      <c r="AE5" s="412"/>
+      <c r="AF5" s="412"/>
+      <c r="AG5" s="412"/>
+      <c r="AH5" s="412"/>
+      <c r="AI5" s="412"/>
+      <c r="AJ5" s="412"/>
+      <c r="AK5" s="412"/>
+      <c r="AL5" s="412"/>
+      <c r="AM5" s="412"/>
+      <c r="AN5" s="412"/>
+      <c r="AO5" s="413"/>
+      <c r="AP5" s="401" t="s">
         <v>16</v>
       </c>
-      <c r="AQ5" s="404" t="s">
+      <c r="AQ5" s="401" t="s">
         <v>17</v>
       </c>
-      <c r="AR5" s="404" t="s">
+      <c r="AR5" s="401" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="404" t="s">
+      <c r="AS5" s="401" t="s">
         <v>19</v>
       </c>
-      <c r="AT5" s="404" t="s">
+      <c r="AT5" s="401" t="s">
         <v>20</v>
       </c>
-      <c r="AU5" s="404" t="s">
+      <c r="AU5" s="401" t="s">
         <v>21</v>
       </c>
-      <c r="AV5" s="404" t="s">
+      <c r="AV5" s="401" t="s">
         <v>22</v>
       </c>
-      <c r="AW5" s="404" t="s">
+      <c r="AW5" s="401" t="s">
         <v>23</v>
       </c>
-      <c r="AX5" s="404" t="s">
+      <c r="AX5" s="401" t="s">
         <v>24</v>
       </c>
-      <c r="AY5" s="400" t="s">
+      <c r="AY5" s="411" t="s">
         <v>25</v>
       </c>
-      <c r="AZ5" s="401"/>
-      <c r="BA5" s="401"/>
-      <c r="BB5" s="401"/>
-      <c r="BC5" s="401"/>
-      <c r="BD5" s="401"/>
-      <c r="BE5" s="401"/>
-      <c r="BF5" s="401"/>
-      <c r="BG5" s="401"/>
-      <c r="BH5" s="401"/>
-      <c r="BI5" s="401"/>
-      <c r="BJ5" s="401"/>
-      <c r="BK5" s="401"/>
-      <c r="BL5" s="401"/>
-      <c r="BM5" s="401"/>
-      <c r="BN5" s="401"/>
-      <c r="BO5" s="401"/>
-      <c r="BP5" s="402"/>
-      <c r="BQ5" s="421" t="s">
+      <c r="AZ5" s="412"/>
+      <c r="BA5" s="412"/>
+      <c r="BB5" s="412"/>
+      <c r="BC5" s="412"/>
+      <c r="BD5" s="412"/>
+      <c r="BE5" s="412"/>
+      <c r="BF5" s="412"/>
+      <c r="BG5" s="412"/>
+      <c r="BH5" s="412"/>
+      <c r="BI5" s="412"/>
+      <c r="BJ5" s="412"/>
+      <c r="BK5" s="412"/>
+      <c r="BL5" s="412"/>
+      <c r="BM5" s="412"/>
+      <c r="BN5" s="412"/>
+      <c r="BO5" s="412"/>
+      <c r="BP5" s="413"/>
+      <c r="BQ5" s="417" t="s">
         <v>26</v>
       </c>
-      <c r="BR5" s="414"/>
-      <c r="BS5" s="400" t="s">
+      <c r="BR5" s="418"/>
+      <c r="BS5" s="411" t="s">
         <v>143</v>
       </c>
-      <c r="BT5" s="400" t="s">
+      <c r="BT5" s="411" t="s">
         <v>27</v>
       </c>
-      <c r="BU5" s="432" t="s">
+      <c r="BU5" s="405" t="s">
         <v>28</v>
       </c>
-      <c r="BW5" s="433" t="s">
+      <c r="BW5" s="408" t="s">
         <v>29</v>
       </c>
-      <c r="BX5" s="422" t="s">
+      <c r="BX5" s="419" t="s">
         <v>30</v>
       </c>
-      <c r="BY5" s="423"/>
-      <c r="BZ5" s="423"/>
-      <c r="CA5" s="414"/>
-      <c r="CB5" s="434" t="s">
+      <c r="BY5" s="420"/>
+      <c r="BZ5" s="420"/>
+      <c r="CA5" s="418"/>
+      <c r="CB5" s="414" t="s">
         <v>31</v>
       </c>
-      <c r="CC5" s="419" t="s">
+      <c r="CC5" s="396" t="s">
         <v>32</v>
       </c>
-      <c r="CD5" s="419" t="s">
+      <c r="CD5" s="396" t="s">
         <v>33</v>
       </c>
       <c r="CH5" s="46"/>
       <c r="CI5" s="47"/>
     </row>
     <row r="6" spans="1:87" s="45" customFormat="1">
-      <c r="A6" s="398"/>
-      <c r="B6" s="398"/>
-      <c r="C6" s="398"/>
-      <c r="D6" s="398"/>
-      <c r="E6" s="398"/>
-      <c r="F6" s="398"/>
-      <c r="G6" s="398"/>
-      <c r="H6" s="398"/>
-      <c r="I6" s="398"/>
-      <c r="J6" s="398"/>
-      <c r="K6" s="412" t="s">
+      <c r="A6" s="397"/>
+      <c r="B6" s="397"/>
+      <c r="C6" s="397"/>
+      <c r="D6" s="397"/>
+      <c r="E6" s="397"/>
+      <c r="F6" s="397"/>
+      <c r="G6" s="397"/>
+      <c r="H6" s="397"/>
+      <c r="I6" s="397"/>
+      <c r="J6" s="397"/>
+      <c r="K6" s="402" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="412" t="s">
+      <c r="L6" s="402" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="412" t="s">
+      <c r="M6" s="402" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="412" t="s">
+      <c r="N6" s="402" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="412" t="s">
+      <c r="O6" s="402" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="412" t="s">
+      <c r="P6" s="402" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="412" t="s">
+      <c r="Q6" s="402" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="412" t="s">
+      <c r="R6" s="402" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="412" t="s">
+      <c r="S6" s="402" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="412" t="s">
+      <c r="T6" s="402" t="s">
         <v>43</v>
       </c>
-      <c r="U6" s="412" t="s">
+      <c r="U6" s="402" t="s">
         <v>44</v>
       </c>
-      <c r="V6" s="413" t="s">
+      <c r="V6" s="432" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="414"/>
-      <c r="X6" s="412" t="s">
+      <c r="W6" s="418"/>
+      <c r="X6" s="402" t="s">
         <v>46</v>
       </c>
-      <c r="Y6" s="404" t="s">
+      <c r="Y6" s="401" t="s">
         <v>47</v>
       </c>
-      <c r="Z6" s="404" t="s">
+      <c r="Z6" s="401" t="s">
         <v>48</v>
       </c>
-      <c r="AA6" s="404" t="s">
+      <c r="AA6" s="401" t="s">
         <v>49</v>
       </c>
-      <c r="AB6" s="404" t="s">
+      <c r="AB6" s="401" t="s">
         <v>50</v>
       </c>
-      <c r="AC6" s="334" t="s">
+      <c r="AC6" s="352" t="s">
         <v>51</v>
       </c>
-      <c r="AD6" s="334" t="s">
+      <c r="AD6" s="352" t="s">
         <v>144</v>
       </c>
-      <c r="AE6" s="334" t="s">
+      <c r="AE6" s="352" t="s">
         <v>53</v>
       </c>
-      <c r="AF6" s="334" t="s">
+      <c r="AF6" s="352" t="s">
         <v>54</v>
       </c>
-      <c r="AG6" s="404" t="s">
+      <c r="AG6" s="401" t="s">
         <v>55</v>
       </c>
-      <c r="AH6" s="334" t="s">
+      <c r="AH6" s="352" t="s">
         <v>56</v>
       </c>
-      <c r="AI6" s="334" t="s">
+      <c r="AI6" s="352" t="s">
         <v>57</v>
       </c>
-      <c r="AJ6" s="404" t="s">
+      <c r="AJ6" s="401" t="s">
         <v>58</v>
       </c>
-      <c r="AK6" s="406" t="s">
+      <c r="AK6" s="429" t="s">
         <v>59</v>
       </c>
-      <c r="AL6" s="404" t="s">
+      <c r="AL6" s="401" t="s">
         <v>60</v>
       </c>
-      <c r="AM6" s="404" t="s">
+      <c r="AM6" s="401" t="s">
         <v>61</v>
       </c>
-      <c r="AN6" s="410" t="s">
+      <c r="AN6" s="431" t="s">
         <v>62</v>
       </c>
-      <c r="AO6" s="404" t="s">
+      <c r="AO6" s="401" t="s">
         <v>63</v>
       </c>
-      <c r="AP6" s="398"/>
-      <c r="AQ6" s="398"/>
-      <c r="AR6" s="398"/>
-      <c r="AS6" s="398"/>
-      <c r="AT6" s="398"/>
-      <c r="AU6" s="398"/>
-      <c r="AV6" s="398"/>
-      <c r="AW6" s="398"/>
-      <c r="AX6" s="398"/>
-      <c r="AY6" s="400" t="s">
+      <c r="AP6" s="397"/>
+      <c r="AQ6" s="397"/>
+      <c r="AR6" s="397"/>
+      <c r="AS6" s="397"/>
+      <c r="AT6" s="397"/>
+      <c r="AU6" s="397"/>
+      <c r="AV6" s="397"/>
+      <c r="AW6" s="397"/>
+      <c r="AX6" s="397"/>
+      <c r="AY6" s="411" t="s">
         <v>25</v>
       </c>
-      <c r="AZ6" s="401"/>
-      <c r="BA6" s="401"/>
-      <c r="BB6" s="401"/>
-      <c r="BC6" s="401"/>
-      <c r="BD6" s="401"/>
-      <c r="BE6" s="401"/>
-      <c r="BF6" s="401"/>
-      <c r="BG6" s="401"/>
-      <c r="BH6" s="401"/>
-      <c r="BI6" s="401"/>
-      <c r="BJ6" s="402"/>
-      <c r="BK6" s="400" t="s">
+      <c r="AZ6" s="412"/>
+      <c r="BA6" s="412"/>
+      <c r="BB6" s="412"/>
+      <c r="BC6" s="412"/>
+      <c r="BD6" s="412"/>
+      <c r="BE6" s="412"/>
+      <c r="BF6" s="412"/>
+      <c r="BG6" s="412"/>
+      <c r="BH6" s="412"/>
+      <c r="BI6" s="412"/>
+      <c r="BJ6" s="413"/>
+      <c r="BK6" s="411" t="s">
         <v>64</v>
       </c>
-      <c r="BL6" s="401"/>
-      <c r="BM6" s="401"/>
-      <c r="BN6" s="401"/>
-      <c r="BO6" s="401"/>
-      <c r="BP6" s="402"/>
-      <c r="BQ6" s="397" t="s">
+      <c r="BL6" s="412"/>
+      <c r="BM6" s="412"/>
+      <c r="BN6" s="412"/>
+      <c r="BO6" s="412"/>
+      <c r="BP6" s="413"/>
+      <c r="BQ6" s="399" t="s">
         <v>65</v>
       </c>
-      <c r="BR6" s="397" t="s">
+      <c r="BR6" s="399" t="s">
         <v>66</v>
       </c>
-      <c r="BS6" s="398"/>
-      <c r="BT6" s="398"/>
-      <c r="BU6" s="407"/>
-      <c r="BW6" s="425"/>
-      <c r="BX6" s="407"/>
-      <c r="BY6" s="424"/>
-      <c r="BZ6" s="424"/>
-      <c r="CA6" s="425"/>
-      <c r="CB6" s="398"/>
-      <c r="CC6" s="398"/>
-      <c r="CD6" s="398"/>
+      <c r="BS6" s="397"/>
+      <c r="BT6" s="397"/>
+      <c r="BU6" s="406"/>
+      <c r="BW6" s="409"/>
+      <c r="BX6" s="406"/>
+      <c r="BY6" s="421"/>
+      <c r="BZ6" s="421"/>
+      <c r="CA6" s="409"/>
+      <c r="CB6" s="397"/>
+      <c r="CC6" s="397"/>
+      <c r="CD6" s="397"/>
       <c r="CH6" s="46"/>
       <c r="CI6" s="47"/>
     </row>
     <row r="7" spans="1:87" s="45" customFormat="1" ht="12">
-      <c r="A7" s="398"/>
-      <c r="B7" s="398"/>
-      <c r="C7" s="398"/>
-      <c r="D7" s="398"/>
-      <c r="E7" s="398"/>
-      <c r="F7" s="398"/>
-      <c r="G7" s="398"/>
-      <c r="H7" s="398"/>
-      <c r="I7" s="398"/>
-      <c r="J7" s="398"/>
-      <c r="K7" s="398"/>
-      <c r="L7" s="398"/>
-      <c r="M7" s="398"/>
-      <c r="N7" s="398"/>
-      <c r="O7" s="398"/>
-      <c r="P7" s="398"/>
-      <c r="Q7" s="398"/>
-      <c r="R7" s="398"/>
-      <c r="S7" s="398"/>
-      <c r="T7" s="398"/>
-      <c r="U7" s="398"/>
-      <c r="V7" s="408"/>
-      <c r="W7" s="415"/>
-      <c r="X7" s="398"/>
-      <c r="Y7" s="398"/>
-      <c r="Z7" s="398"/>
-      <c r="AA7" s="398"/>
-      <c r="AB7" s="398"/>
-      <c r="AC7" s="398"/>
-      <c r="AD7" s="398"/>
-      <c r="AE7" s="398"/>
-      <c r="AF7" s="398"/>
-      <c r="AG7" s="398"/>
-      <c r="AH7" s="398"/>
-      <c r="AI7" s="398"/>
-      <c r="AJ7" s="398"/>
-      <c r="AK7" s="407"/>
-      <c r="AL7" s="398"/>
-      <c r="AM7" s="398"/>
-      <c r="AN7" s="398"/>
-      <c r="AO7" s="398"/>
-      <c r="AP7" s="398"/>
-      <c r="AQ7" s="398"/>
-      <c r="AR7" s="398"/>
-      <c r="AS7" s="398"/>
-      <c r="AT7" s="398"/>
-      <c r="AU7" s="398"/>
-      <c r="AV7" s="398"/>
-      <c r="AW7" s="398"/>
-      <c r="AX7" s="398"/>
+      <c r="A7" s="397"/>
+      <c r="B7" s="397"/>
+      <c r="C7" s="397"/>
+      <c r="D7" s="397"/>
+      <c r="E7" s="397"/>
+      <c r="F7" s="397"/>
+      <c r="G7" s="397"/>
+      <c r="H7" s="397"/>
+      <c r="I7" s="397"/>
+      <c r="J7" s="397"/>
+      <c r="K7" s="397"/>
+      <c r="L7" s="397"/>
+      <c r="M7" s="397"/>
+      <c r="N7" s="397"/>
+      <c r="O7" s="397"/>
+      <c r="P7" s="397"/>
+      <c r="Q7" s="397"/>
+      <c r="R7" s="397"/>
+      <c r="S7" s="397"/>
+      <c r="T7" s="397"/>
+      <c r="U7" s="397"/>
+      <c r="V7" s="407"/>
+      <c r="W7" s="433"/>
+      <c r="X7" s="397"/>
+      <c r="Y7" s="397"/>
+      <c r="Z7" s="397"/>
+      <c r="AA7" s="397"/>
+      <c r="AB7" s="397"/>
+      <c r="AC7" s="397"/>
+      <c r="AD7" s="397"/>
+      <c r="AE7" s="397"/>
+      <c r="AF7" s="397"/>
+      <c r="AG7" s="397"/>
+      <c r="AH7" s="397"/>
+      <c r="AI7" s="397"/>
+      <c r="AJ7" s="397"/>
+      <c r="AK7" s="406"/>
+      <c r="AL7" s="397"/>
+      <c r="AM7" s="397"/>
+      <c r="AN7" s="397"/>
+      <c r="AO7" s="397"/>
+      <c r="AP7" s="397"/>
+      <c r="AQ7" s="397"/>
+      <c r="AR7" s="397"/>
+      <c r="AS7" s="397"/>
+      <c r="AT7" s="397"/>
+      <c r="AU7" s="397"/>
+      <c r="AV7" s="397"/>
+      <c r="AW7" s="397"/>
+      <c r="AX7" s="397"/>
       <c r="AY7" s="29" t="s">
         <v>67</v>
       </c>
@@ -19549,7 +19657,7 @@
       <c r="BA7" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="BB7" s="400" t="s">
+      <c r="BB7" s="411" t="s">
         <v>70</v>
       </c>
       <c r="BC7" s="403" t="s">
@@ -19573,98 +19681,98 @@
       <c r="BI7" s="403" t="s">
         <v>79</v>
       </c>
-      <c r="BJ7" s="431" t="s">
+      <c r="BJ7" s="404" t="s">
         <v>80</v>
       </c>
       <c r="BK7" s="403" t="s">
         <v>81</v>
       </c>
-      <c r="BL7" s="400" t="s">
+      <c r="BL7" s="411" t="s">
         <v>82</v>
       </c>
       <c r="BM7" s="403" t="s">
         <v>83</v>
       </c>
-      <c r="BN7" s="400" t="s">
+      <c r="BN7" s="411" t="s">
         <v>84</v>
       </c>
-      <c r="BO7" s="400" t="s">
+      <c r="BO7" s="411" t="s">
         <v>146</v>
       </c>
-      <c r="BP7" s="400" t="s">
+      <c r="BP7" s="411" t="s">
         <v>85</v>
       </c>
-      <c r="BQ7" s="398"/>
-      <c r="BR7" s="398"/>
-      <c r="BS7" s="398"/>
-      <c r="BT7" s="398"/>
-      <c r="BU7" s="407"/>
-      <c r="BW7" s="425"/>
-      <c r="BX7" s="426"/>
-      <c r="BY7" s="427"/>
-      <c r="BZ7" s="427"/>
-      <c r="CA7" s="428"/>
-      <c r="CB7" s="398"/>
-      <c r="CC7" s="398"/>
-      <c r="CD7" s="398"/>
+      <c r="BQ7" s="397"/>
+      <c r="BR7" s="397"/>
+      <c r="BS7" s="397"/>
+      <c r="BT7" s="397"/>
+      <c r="BU7" s="406"/>
+      <c r="BW7" s="409"/>
+      <c r="BX7" s="422"/>
+      <c r="BY7" s="423"/>
+      <c r="BZ7" s="423"/>
+      <c r="CA7" s="410"/>
+      <c r="CB7" s="397"/>
+      <c r="CC7" s="397"/>
+      <c r="CD7" s="397"/>
       <c r="CH7" s="46"/>
       <c r="CI7" s="47"/>
     </row>
     <row r="8" spans="1:87" s="45" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A8" s="399"/>
-      <c r="B8" s="399"/>
-      <c r="C8" s="399"/>
-      <c r="D8" s="399"/>
-      <c r="E8" s="399"/>
-      <c r="F8" s="399"/>
-      <c r="G8" s="399"/>
-      <c r="H8" s="399"/>
-      <c r="I8" s="399"/>
-      <c r="J8" s="399"/>
-      <c r="K8" s="399"/>
-      <c r="L8" s="399"/>
-      <c r="M8" s="399"/>
-      <c r="N8" s="399"/>
-      <c r="O8" s="399"/>
-      <c r="P8" s="399"/>
-      <c r="Q8" s="399"/>
-      <c r="R8" s="399"/>
-      <c r="S8" s="399"/>
-      <c r="T8" s="399"/>
-      <c r="U8" s="399"/>
+      <c r="A8" s="400"/>
+      <c r="B8" s="400"/>
+      <c r="C8" s="400"/>
+      <c r="D8" s="400"/>
+      <c r="E8" s="400"/>
+      <c r="F8" s="400"/>
+      <c r="G8" s="400"/>
+      <c r="H8" s="400"/>
+      <c r="I8" s="400"/>
+      <c r="J8" s="400"/>
+      <c r="K8" s="400"/>
+      <c r="L8" s="400"/>
+      <c r="M8" s="400"/>
+      <c r="N8" s="400"/>
+      <c r="O8" s="400"/>
+      <c r="P8" s="400"/>
+      <c r="Q8" s="400"/>
+      <c r="R8" s="400"/>
+      <c r="S8" s="400"/>
+      <c r="T8" s="400"/>
+      <c r="U8" s="400"/>
       <c r="V8" s="49" t="s">
         <v>86</v>
       </c>
       <c r="W8" s="49" t="s">
         <v>87</v>
       </c>
-      <c r="X8" s="399"/>
-      <c r="Y8" s="399"/>
-      <c r="Z8" s="399"/>
-      <c r="AA8" s="399"/>
-      <c r="AB8" s="399"/>
-      <c r="AC8" s="399"/>
-      <c r="AD8" s="399"/>
-      <c r="AE8" s="399"/>
-      <c r="AF8" s="399"/>
-      <c r="AG8" s="399"/>
-      <c r="AH8" s="399"/>
-      <c r="AI8" s="399"/>
-      <c r="AJ8" s="399"/>
-      <c r="AK8" s="408"/>
-      <c r="AL8" s="399"/>
-      <c r="AM8" s="399"/>
-      <c r="AN8" s="399"/>
-      <c r="AO8" s="399"/>
-      <c r="AP8" s="399"/>
-      <c r="AQ8" s="399"/>
-      <c r="AR8" s="399"/>
-      <c r="AS8" s="399"/>
-      <c r="AT8" s="399"/>
-      <c r="AU8" s="399"/>
-      <c r="AV8" s="399"/>
-      <c r="AW8" s="399"/>
-      <c r="AX8" s="399"/>
+      <c r="X8" s="400"/>
+      <c r="Y8" s="400"/>
+      <c r="Z8" s="400"/>
+      <c r="AA8" s="400"/>
+      <c r="AB8" s="400"/>
+      <c r="AC8" s="400"/>
+      <c r="AD8" s="400"/>
+      <c r="AE8" s="400"/>
+      <c r="AF8" s="400"/>
+      <c r="AG8" s="400"/>
+      <c r="AH8" s="400"/>
+      <c r="AI8" s="400"/>
+      <c r="AJ8" s="400"/>
+      <c r="AK8" s="407"/>
+      <c r="AL8" s="400"/>
+      <c r="AM8" s="400"/>
+      <c r="AN8" s="400"/>
+      <c r="AO8" s="400"/>
+      <c r="AP8" s="400"/>
+      <c r="AQ8" s="400"/>
+      <c r="AR8" s="400"/>
+      <c r="AS8" s="400"/>
+      <c r="AT8" s="400"/>
+      <c r="AU8" s="400"/>
+      <c r="AV8" s="400"/>
+      <c r="AW8" s="400"/>
+      <c r="AX8" s="400"/>
       <c r="AY8" s="30" t="s">
         <v>88</v>
       </c>
@@ -19674,27 +19782,27 @@
       <c r="BA8" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="BB8" s="399"/>
-      <c r="BC8" s="399"/>
-      <c r="BD8" s="399"/>
-      <c r="BE8" s="399"/>
-      <c r="BF8" s="399"/>
-      <c r="BG8" s="399"/>
-      <c r="BH8" s="399"/>
-      <c r="BI8" s="399"/>
-      <c r="BJ8" s="399"/>
-      <c r="BK8" s="399"/>
-      <c r="BL8" s="399"/>
-      <c r="BM8" s="399"/>
-      <c r="BN8" s="399"/>
-      <c r="BO8" s="399"/>
-      <c r="BP8" s="399"/>
-      <c r="BQ8" s="399"/>
-      <c r="BR8" s="399"/>
-      <c r="BS8" s="399"/>
-      <c r="BT8" s="399"/>
-      <c r="BU8" s="408"/>
-      <c r="BW8" s="428"/>
+      <c r="BB8" s="400"/>
+      <c r="BC8" s="400"/>
+      <c r="BD8" s="400"/>
+      <c r="BE8" s="400"/>
+      <c r="BF8" s="400"/>
+      <c r="BG8" s="400"/>
+      <c r="BH8" s="400"/>
+      <c r="BI8" s="400"/>
+      <c r="BJ8" s="400"/>
+      <c r="BK8" s="400"/>
+      <c r="BL8" s="400"/>
+      <c r="BM8" s="400"/>
+      <c r="BN8" s="400"/>
+      <c r="BO8" s="400"/>
+      <c r="BP8" s="400"/>
+      <c r="BQ8" s="400"/>
+      <c r="BR8" s="400"/>
+      <c r="BS8" s="400"/>
+      <c r="BT8" s="400"/>
+      <c r="BU8" s="407"/>
+      <c r="BW8" s="410"/>
       <c r="BX8" s="23" t="s">
         <v>91</v>
       </c>
@@ -19707,9 +19815,9 @@
       <c r="CA8" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="CB8" s="420"/>
-      <c r="CC8" s="420"/>
-      <c r="CD8" s="420"/>
+      <c r="CB8" s="398"/>
+      <c r="CC8" s="398"/>
+      <c r="CD8" s="398"/>
       <c r="CF8" s="50"/>
       <c r="CH8" s="46"/>
       <c r="CI8" s="47"/>
@@ -21716,6 +21824,72 @@
   </sheetData>
   <autoFilter ref="A9:CI14" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <mergeCells count="82">
+    <mergeCell ref="BX5:CA7"/>
+    <mergeCell ref="BQ6:BQ8"/>
+    <mergeCell ref="Y5:AO5"/>
+    <mergeCell ref="AN6:AN8"/>
+    <mergeCell ref="BG7:BG8"/>
+    <mergeCell ref="BQ5:BR5"/>
+    <mergeCell ref="BK7:BK8"/>
+    <mergeCell ref="BK6:BP6"/>
+    <mergeCell ref="BN7:BN8"/>
+    <mergeCell ref="BP7:BP8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="AU5:AU8"/>
+    <mergeCell ref="BH7:BH8"/>
+    <mergeCell ref="BI7:BI8"/>
+    <mergeCell ref="K5:X5"/>
+    <mergeCell ref="Q6:Q8"/>
+    <mergeCell ref="AC6:AC8"/>
+    <mergeCell ref="AL6:AL8"/>
+    <mergeCell ref="F5:F8"/>
+    <mergeCell ref="AP5:AP8"/>
+    <mergeCell ref="AB6:AB8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="AH6:AH8"/>
+    <mergeCell ref="AJ6:AJ8"/>
+    <mergeCell ref="T6:T8"/>
+    <mergeCell ref="AA6:AA8"/>
+    <mergeCell ref="P6:P8"/>
+    <mergeCell ref="S6:S8"/>
+    <mergeCell ref="AM6:AM8"/>
+    <mergeCell ref="U6:U8"/>
+    <mergeCell ref="AG6:AG8"/>
+    <mergeCell ref="AK6:AK8"/>
+    <mergeCell ref="AD6:AD8"/>
+    <mergeCell ref="AF6:AF8"/>
+    <mergeCell ref="CC5:CC8"/>
+    <mergeCell ref="H5:H8"/>
+    <mergeCell ref="J5:J8"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="BS5:BS8"/>
+    <mergeCell ref="O6:O8"/>
+    <mergeCell ref="G5:G8"/>
+    <mergeCell ref="I5:I8"/>
+    <mergeCell ref="AQ5:AQ8"/>
+    <mergeCell ref="R6:R8"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="BC7:BC8"/>
+    <mergeCell ref="AE6:AE8"/>
+    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="BW3:CB4"/>
+    <mergeCell ref="X6:X8"/>
+    <mergeCell ref="AV5:AV8"/>
+    <mergeCell ref="AX5:AX8"/>
+    <mergeCell ref="V6:W7"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="AR5:AR8"/>
+    <mergeCell ref="BB7:BB8"/>
+    <mergeCell ref="BD7:BD8"/>
+    <mergeCell ref="AS5:AS8"/>
+    <mergeCell ref="AY6:BJ6"/>
+    <mergeCell ref="BE7:BE8"/>
+    <mergeCell ref="AO6:AO8"/>
+    <mergeCell ref="BF7:BF8"/>
+    <mergeCell ref="CB5:CB8"/>
+    <mergeCell ref="BT5:BT8"/>
     <mergeCell ref="A5:A8"/>
     <mergeCell ref="C5:C8"/>
     <mergeCell ref="CD5:CD8"/>
@@ -21732,87 +21906,21 @@
     <mergeCell ref="BW5:BW8"/>
     <mergeCell ref="BO7:BO8"/>
     <mergeCell ref="AY5:BP5"/>
-    <mergeCell ref="BW3:CB4"/>
-    <mergeCell ref="X6:X8"/>
-    <mergeCell ref="AV5:AV8"/>
-    <mergeCell ref="AX5:AX8"/>
-    <mergeCell ref="V6:W7"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="AR5:AR8"/>
-    <mergeCell ref="BB7:BB8"/>
-    <mergeCell ref="BD7:BD8"/>
-    <mergeCell ref="AS5:AS8"/>
-    <mergeCell ref="AY6:BJ6"/>
-    <mergeCell ref="BE7:BE8"/>
-    <mergeCell ref="AO6:AO8"/>
-    <mergeCell ref="BF7:BF8"/>
-    <mergeCell ref="CB5:CB8"/>
-    <mergeCell ref="BT5:BT8"/>
-    <mergeCell ref="CC5:CC8"/>
-    <mergeCell ref="H5:H8"/>
-    <mergeCell ref="J5:J8"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="E5:E8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="BS5:BS8"/>
-    <mergeCell ref="O6:O8"/>
-    <mergeCell ref="G5:G8"/>
-    <mergeCell ref="I5:I8"/>
-    <mergeCell ref="AQ5:AQ8"/>
-    <mergeCell ref="R6:R8"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="BC7:BC8"/>
-    <mergeCell ref="AE6:AE8"/>
-    <mergeCell ref="D5:D8"/>
-    <mergeCell ref="F5:F8"/>
-    <mergeCell ref="AP5:AP8"/>
-    <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="AH6:AH8"/>
-    <mergeCell ref="AJ6:AJ8"/>
-    <mergeCell ref="T6:T8"/>
-    <mergeCell ref="AA6:AA8"/>
-    <mergeCell ref="P6:P8"/>
-    <mergeCell ref="S6:S8"/>
-    <mergeCell ref="AM6:AM8"/>
-    <mergeCell ref="U6:U8"/>
-    <mergeCell ref="AG6:AG8"/>
-    <mergeCell ref="AK6:AK8"/>
-    <mergeCell ref="AD6:AD8"/>
-    <mergeCell ref="AF6:AF8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="AU5:AU8"/>
-    <mergeCell ref="BH7:BH8"/>
-    <mergeCell ref="BI7:BI8"/>
-    <mergeCell ref="K5:X5"/>
-    <mergeCell ref="Q6:Q8"/>
-    <mergeCell ref="AC6:AC8"/>
-    <mergeCell ref="AL6:AL8"/>
-    <mergeCell ref="BX5:CA7"/>
-    <mergeCell ref="BQ6:BQ8"/>
-    <mergeCell ref="Y5:AO5"/>
-    <mergeCell ref="AN6:AN8"/>
-    <mergeCell ref="BG7:BG8"/>
-    <mergeCell ref="BQ5:BR5"/>
-    <mergeCell ref="BK7:BK8"/>
-    <mergeCell ref="BK6:BP6"/>
-    <mergeCell ref="BN7:BN8"/>
-    <mergeCell ref="BP7:BP8"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B9 B12:B16 B20:B1048576 C9:BU9 D10:F10 J10:BI10 BK10:BU10 BW9:CD10">
-    <cfRule type="duplicateValues" dxfId="8" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B9 B12:B16 B20:B1048576 C9:BU9">
-    <cfRule type="duplicateValues" dxfId="7" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19">
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="BJ10">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.21" bottom="0.17" header="0.196850393700787" footer="0.196850393700787"/>
